--- a/data/facteurs de caractérisation.xlsx
+++ b/data/facteurs de caractérisation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\CIRED\PlaneFR\Code\Module_PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E4FCA9-7B3D-42CC-BA59-BA7BE6094FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEB5B22-DDBF-4B3A-9BE7-4009525AAB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3988" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4224" uniqueCount="498">
   <si>
     <t>Processus du système Terre</t>
   </si>
@@ -1425,6 +1425,114 @@
   </si>
   <si>
     <t>air_emissions</t>
+  </si>
+  <si>
+    <t>Paddy rice</t>
+  </si>
+  <si>
+    <t>Wheat</t>
+  </si>
+  <si>
+    <t>Cereal grains nec</t>
+  </si>
+  <si>
+    <t>Vegetables, fruit, nuts</t>
+  </si>
+  <si>
+    <t>Oil seeds</t>
+  </si>
+  <si>
+    <t>Sugar cane, sugar beet</t>
+  </si>
+  <si>
+    <t>Plant-based fibers</t>
+  </si>
+  <si>
+    <t>Crops nec</t>
+  </si>
+  <si>
+    <t>Cattle</t>
+  </si>
+  <si>
+    <t>Pigs</t>
+  </si>
+  <si>
+    <t>Poultry</t>
+  </si>
+  <si>
+    <t>Meat animals nec</t>
+  </si>
+  <si>
+    <t>Animal products nec</t>
+  </si>
+  <si>
+    <t>Raw milk</t>
+  </si>
+  <si>
+    <t>Products of forestry, logging and related services (02)</t>
+  </si>
+  <si>
+    <t>Biodiversity loss - HANPP</t>
+  </si>
+  <si>
+    <t>Biodiversity loss - PDF</t>
+  </si>
+  <si>
+    <t>Primary Crops - Rice</t>
+  </si>
+  <si>
+    <t>Primary Crops - Wheat</t>
+  </si>
+  <si>
+    <t>Primary Crops - Cereals n.e.c.</t>
+  </si>
+  <si>
+    <t>Primary Crops - Roots and tubers</t>
+  </si>
+  <si>
+    <t>Primary Crops - Pulses</t>
+  </si>
+  <si>
+    <t>Primary Crops - Nuts</t>
+  </si>
+  <si>
+    <t>Primary Crops - Vegetables</t>
+  </si>
+  <si>
+    <t>Primary Crops - Fruits</t>
+  </si>
+  <si>
+    <t>Primary Crops - Oil bearing crops</t>
+  </si>
+  <si>
+    <t>Primary Crops - Sugar crops</t>
+  </si>
+  <si>
+    <t>Primary Crops - Fibres</t>
+  </si>
+  <si>
+    <t>Primary Crops - Spice - beverage - pharmaceutical crops</t>
+  </si>
+  <si>
+    <t>Primary Crops - Tobacco</t>
+  </si>
+  <si>
+    <t>Crop residues - Straw</t>
+  </si>
+  <si>
+    <t>Crop residues - Other crop residues (sugar and fodder beet leaves etc)</t>
+  </si>
+  <si>
+    <t>Grazed biomass</t>
+  </si>
+  <si>
+    <t>Forestry - Other crops n.e.c</t>
+  </si>
+  <si>
+    <t>Forestry - Timber (Industrial roundwood)</t>
+  </si>
+  <si>
+    <t>Forestry - Wood fuel and other extraction</t>
   </si>
 </sst>
 </file>
@@ -1456,6 +1564,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1471,7 +1580,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1520,8 +1629,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9999FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1553,13 +1668,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1714,15 +1838,33 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1735,6 +1877,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF9999FF"/>
       <color rgb="FFA568D2"/>
     </mruColors>
   </colors>
@@ -2012,7 +2155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F520"/>
+  <dimension ref="A1:G579"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24.6640625" style="6" customWidth="1"/>
@@ -2024,7 +2167,7 @@
     <col min="7" max="16384" width="9.19921875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="38.200000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2041,7 +2184,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="39" t="s">
         <v>5</v>
       </c>
@@ -4376,7 +4519,7 @@
         <v>145</v>
       </c>
       <c r="B139" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C139" s="19" t="s">
         <v>147</v>
@@ -4394,7 +4537,7 @@
         <v>149</v>
       </c>
       <c r="B140" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C140" s="19" t="s">
         <v>147</v>
@@ -4412,7 +4555,7 @@
         <v>149</v>
       </c>
       <c r="B141" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C141" s="19" t="s">
         <v>150</v>
@@ -4430,7 +4573,7 @@
         <v>149</v>
       </c>
       <c r="B142" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C142" s="22" t="s">
         <v>151</v>
@@ -4448,7 +4591,7 @@
         <v>149</v>
       </c>
       <c r="B143" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C143" s="22" t="s">
         <v>152</v>
@@ -4466,7 +4609,7 @@
         <v>149</v>
       </c>
       <c r="B144" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C144" s="22" t="s">
         <v>153</v>
@@ -4484,7 +4627,7 @@
         <v>149</v>
       </c>
       <c r="B145" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C145" s="22" t="s">
         <v>154</v>
@@ -4502,7 +4645,7 @@
         <v>121</v>
       </c>
       <c r="B146" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C146" s="23" t="s">
         <v>157</v>
@@ -4519,7 +4662,7 @@
         <v>121</v>
       </c>
       <c r="B147" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C147" s="23" t="s">
         <v>123</v>
@@ -4536,7 +4679,7 @@
         <v>121</v>
       </c>
       <c r="B148" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C148" s="23" t="s">
         <v>125</v>
@@ -4553,7 +4696,7 @@
         <v>121</v>
       </c>
       <c r="B149" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C149" s="23" t="s">
         <v>126</v>
@@ -4570,7 +4713,7 @@
         <v>121</v>
       </c>
       <c r="B150" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C150" s="23" t="s">
         <v>127</v>
@@ -4587,7 +4730,7 @@
         <v>121</v>
       </c>
       <c r="B151" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C151" s="23" t="s">
         <v>128</v>
@@ -4604,7 +4747,7 @@
         <v>121</v>
       </c>
       <c r="B152" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C152" s="23" t="s">
         <v>129</v>
@@ -4621,7 +4764,7 @@
         <v>121</v>
       </c>
       <c r="B153" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C153" s="23" t="s">
         <v>130</v>
@@ -4638,7 +4781,7 @@
         <v>121</v>
       </c>
       <c r="B154" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C154" s="23" t="s">
         <v>131</v>
@@ -4655,7 +4798,7 @@
         <v>121</v>
       </c>
       <c r="B155" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C155" s="23" t="s">
         <v>132</v>
@@ -4672,7 +4815,7 @@
         <v>121</v>
       </c>
       <c r="B156" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C156" s="23" t="s">
         <v>133</v>
@@ -4689,7 +4832,7 @@
         <v>121</v>
       </c>
       <c r="B157" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C157" s="23" t="s">
         <v>134</v>
@@ -4706,7 +4849,7 @@
         <v>121</v>
       </c>
       <c r="B158" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C158" s="23" t="s">
         <v>135</v>
@@ -4723,7 +4866,7 @@
         <v>121</v>
       </c>
       <c r="B159" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C159" s="23" t="s">
         <v>136</v>
@@ -4740,7 +4883,7 @@
         <v>121</v>
       </c>
       <c r="B160" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C160" s="23" t="s">
         <v>137</v>
@@ -4757,7 +4900,7 @@
         <v>121</v>
       </c>
       <c r="B161" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C161" s="23" t="s">
         <v>138</v>
@@ -4774,7 +4917,7 @@
         <v>121</v>
       </c>
       <c r="B162" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C162" s="23" t="s">
         <v>139</v>
@@ -4791,7 +4934,7 @@
         <v>121</v>
       </c>
       <c r="B163" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C163" s="23" t="s">
         <v>140</v>
@@ -4808,7 +4951,7 @@
         <v>121</v>
       </c>
       <c r="B164" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C164" s="23" t="s">
         <v>141</v>
@@ -4825,7 +4968,7 @@
         <v>121</v>
       </c>
       <c r="B165" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C165" s="23" t="s">
         <v>142</v>
@@ -4842,7 +4985,7 @@
         <v>121</v>
       </c>
       <c r="B166" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C166" s="23" t="s">
         <v>143</v>
@@ -4859,7 +5002,7 @@
         <v>121</v>
       </c>
       <c r="B167" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C167" s="23" t="s">
         <v>144</v>
@@ -4876,7 +5019,7 @@
         <v>121</v>
       </c>
       <c r="B168" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C168" s="23" t="s">
         <v>158</v>
@@ -4893,7 +5036,7 @@
         <v>121</v>
       </c>
       <c r="B169" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C169" s="23" t="s">
         <v>159</v>
@@ -4910,7 +5053,7 @@
         <v>121</v>
       </c>
       <c r="B170" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C170" s="23" t="s">
         <v>160</v>
@@ -4927,7 +5070,7 @@
         <v>121</v>
       </c>
       <c r="B171" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C171" s="23" t="s">
         <v>161</v>
@@ -4944,7 +5087,7 @@
         <v>15</v>
       </c>
       <c r="B172" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C172" s="22" t="s">
         <v>17</v>
@@ -4961,7 +5104,7 @@
         <v>15</v>
       </c>
       <c r="B173" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C173" s="22" t="s">
         <v>19</v>
@@ -4978,7 +5121,7 @@
         <v>15</v>
       </c>
       <c r="B174" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C174" s="22" t="s">
         <v>20</v>
@@ -4995,7 +5138,7 @@
         <v>15</v>
       </c>
       <c r="B175" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C175" s="22" t="s">
         <v>21</v>
@@ -5012,7 +5155,7 @@
         <v>15</v>
       </c>
       <c r="B176" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C176" s="22" t="s">
         <v>22</v>
@@ -5029,7 +5172,7 @@
         <v>15</v>
       </c>
       <c r="B177" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C177" s="22" t="s">
         <v>23</v>
@@ -5046,7 +5189,7 @@
         <v>15</v>
       </c>
       <c r="B178" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C178" s="22" t="s">
         <v>24</v>
@@ -5063,7 +5206,7 @@
         <v>15</v>
       </c>
       <c r="B179" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C179" s="22" t="s">
         <v>25</v>
@@ -5080,7 +5223,7 @@
         <v>15</v>
       </c>
       <c r="B180" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C180" s="22" t="s">
         <v>26</v>
@@ -5097,7 +5240,7 @@
         <v>15</v>
       </c>
       <c r="B181" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C181" s="22" t="s">
         <v>27</v>
@@ -5114,7 +5257,7 @@
         <v>15</v>
       </c>
       <c r="B182" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C182" s="22" t="s">
         <v>28</v>
@@ -5131,7 +5274,7 @@
         <v>15</v>
       </c>
       <c r="B183" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C183" s="22" t="s">
         <v>29</v>
@@ -5148,7 +5291,7 @@
         <v>15</v>
       </c>
       <c r="B184" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C184" s="22" t="s">
         <v>30</v>
@@ -5165,7 +5308,7 @@
         <v>15</v>
       </c>
       <c r="B185" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C185" s="22" t="s">
         <v>31</v>
@@ -5182,7 +5325,7 @@
         <v>15</v>
       </c>
       <c r="B186" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C186" s="22" t="s">
         <v>32</v>
@@ -5199,7 +5342,7 @@
         <v>15</v>
       </c>
       <c r="B187" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C187" s="22" t="s">
         <v>33</v>
@@ -5216,7 +5359,7 @@
         <v>15</v>
       </c>
       <c r="B188" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C188" s="22" t="s">
         <v>34</v>
@@ -5233,7 +5376,7 @@
         <v>15</v>
       </c>
       <c r="B189" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C189" s="22" t="s">
         <v>35</v>
@@ -5250,7 +5393,7 @@
         <v>15</v>
       </c>
       <c r="B190" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C190" s="22" t="s">
         <v>36</v>
@@ -5267,7 +5410,7 @@
         <v>15</v>
       </c>
       <c r="B191" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C191" s="22" t="s">
         <v>37</v>
@@ -5284,7 +5427,7 @@
         <v>15</v>
       </c>
       <c r="B192" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C192" s="22" t="s">
         <v>38</v>
@@ -5301,7 +5444,7 @@
         <v>15</v>
       </c>
       <c r="B193" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C193" s="22" t="s">
         <v>39</v>
@@ -5318,7 +5461,7 @@
         <v>15</v>
       </c>
       <c r="B194" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C194" s="22" t="s">
         <v>40</v>
@@ -5335,7 +5478,7 @@
         <v>15</v>
       </c>
       <c r="B195" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C195" s="22" t="s">
         <v>41</v>
@@ -5352,7 +5495,7 @@
         <v>15</v>
       </c>
       <c r="B196" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C196" s="22" t="s">
         <v>42</v>
@@ -5369,7 +5512,7 @@
         <v>15</v>
       </c>
       <c r="B197" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C197" s="22" t="s">
         <v>43</v>
@@ -5386,7 +5529,7 @@
         <v>15</v>
       </c>
       <c r="B198" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C198" s="22" t="s">
         <v>44</v>
@@ -5403,7 +5546,7 @@
         <v>15</v>
       </c>
       <c r="B199" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C199" s="22" t="s">
         <v>45</v>
@@ -5420,7 +5563,7 @@
         <v>15</v>
       </c>
       <c r="B200" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C200" s="22" t="s">
         <v>46</v>
@@ -5437,7 +5580,7 @@
         <v>15</v>
       </c>
       <c r="B201" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C201" s="22" t="s">
         <v>47</v>
@@ -5454,7 +5597,7 @@
         <v>15</v>
       </c>
       <c r="B202" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C202" s="22" t="s">
         <v>48</v>
@@ -5471,7 +5614,7 @@
         <v>15</v>
       </c>
       <c r="B203" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C203" s="22" t="s">
         <v>49</v>
@@ -5488,7 +5631,7 @@
         <v>15</v>
       </c>
       <c r="B204" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C204" s="22" t="s">
         <v>50</v>
@@ -5505,7 +5648,7 @@
         <v>15</v>
       </c>
       <c r="B205" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C205" s="22" t="s">
         <v>51</v>
@@ -5522,7 +5665,7 @@
         <v>15</v>
       </c>
       <c r="B206" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C206" s="22" t="s">
         <v>52</v>
@@ -5539,7 +5682,7 @@
         <v>15</v>
       </c>
       <c r="B207" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C207" s="22" t="s">
         <v>53</v>
@@ -5556,7 +5699,7 @@
         <v>15</v>
       </c>
       <c r="B208" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C208" s="22" t="s">
         <v>54</v>
@@ -5573,7 +5716,7 @@
         <v>15</v>
       </c>
       <c r="B209" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C209" s="22" t="s">
         <v>55</v>
@@ -5590,7 +5733,7 @@
         <v>15</v>
       </c>
       <c r="B210" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C210" s="22" t="s">
         <v>56</v>
@@ -5607,7 +5750,7 @@
         <v>15</v>
       </c>
       <c r="B211" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C211" s="22" t="s">
         <v>57</v>
@@ -5624,7 +5767,7 @@
         <v>15</v>
       </c>
       <c r="B212" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C212" s="22" t="s">
         <v>58</v>
@@ -5641,7 +5784,7 @@
         <v>15</v>
       </c>
       <c r="B213" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C213" s="22" t="s">
         <v>59</v>
@@ -5658,7 +5801,7 @@
         <v>15</v>
       </c>
       <c r="B214" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C214" s="22" t="s">
         <v>60</v>
@@ -5675,7 +5818,7 @@
         <v>15</v>
       </c>
       <c r="B215" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C215" s="22" t="s">
         <v>61</v>
@@ -5692,7 +5835,7 @@
         <v>15</v>
       </c>
       <c r="B216" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C216" s="22" t="s">
         <v>62</v>
@@ -5709,7 +5852,7 @@
         <v>15</v>
       </c>
       <c r="B217" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C217" s="22" t="s">
         <v>63</v>
@@ -5726,7 +5869,7 @@
         <v>15</v>
       </c>
       <c r="B218" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C218" s="22" t="s">
         <v>64</v>
@@ -5743,7 +5886,7 @@
         <v>15</v>
       </c>
       <c r="B219" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C219" s="22" t="s">
         <v>65</v>
@@ -5760,7 +5903,7 @@
         <v>15</v>
       </c>
       <c r="B220" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C220" s="22" t="s">
         <v>66</v>
@@ -5777,7 +5920,7 @@
         <v>15</v>
       </c>
       <c r="B221" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C221" s="22" t="s">
         <v>67</v>
@@ -5794,7 +5937,7 @@
         <v>15</v>
       </c>
       <c r="B222" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C222" s="22" t="s">
         <v>68</v>
@@ -5811,7 +5954,7 @@
         <v>15</v>
       </c>
       <c r="B223" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C223" s="22" t="s">
         <v>69</v>
@@ -5828,7 +5971,7 @@
         <v>15</v>
       </c>
       <c r="B224" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C224" s="22" t="s">
         <v>70</v>
@@ -5845,7 +5988,7 @@
         <v>15</v>
       </c>
       <c r="B225" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C225" s="22" t="s">
         <v>71</v>
@@ -5862,7 +6005,7 @@
         <v>15</v>
       </c>
       <c r="B226" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C226" s="22" t="s">
         <v>72</v>
@@ -5879,7 +6022,7 @@
         <v>15</v>
       </c>
       <c r="B227" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C227" s="22" t="s">
         <v>73</v>
@@ -5896,7 +6039,7 @@
         <v>15</v>
       </c>
       <c r="B228" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C228" s="22" t="s">
         <v>74</v>
@@ -5913,7 +6056,7 @@
         <v>15</v>
       </c>
       <c r="B229" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C229" s="22" t="s">
         <v>75</v>
@@ -5930,7 +6073,7 @@
         <v>15</v>
       </c>
       <c r="B230" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C230" s="22" t="s">
         <v>76</v>
@@ -5947,7 +6090,7 @@
         <v>15</v>
       </c>
       <c r="B231" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C231" s="22" t="s">
         <v>77</v>
@@ -5964,7 +6107,7 @@
         <v>15</v>
       </c>
       <c r="B232" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C232" s="22" t="s">
         <v>78</v>
@@ -5981,7 +6124,7 @@
         <v>15</v>
       </c>
       <c r="B233" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C233" s="22" t="s">
         <v>79</v>
@@ -5998,7 +6141,7 @@
         <v>15</v>
       </c>
       <c r="B234" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C234" s="22" t="s">
         <v>80</v>
@@ -6015,7 +6158,7 @@
         <v>15</v>
       </c>
       <c r="B235" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C235" s="22" t="s">
         <v>81</v>
@@ -6032,7 +6175,7 @@
         <v>15</v>
       </c>
       <c r="B236" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C236" s="22" t="s">
         <v>82</v>
@@ -6049,7 +6192,7 @@
         <v>15</v>
       </c>
       <c r="B237" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C237" s="22" t="s">
         <v>83</v>
@@ -6066,7 +6209,7 @@
         <v>15</v>
       </c>
       <c r="B238" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C238" s="22" t="s">
         <v>84</v>
@@ -6084,7 +6227,7 @@
         <v>15</v>
       </c>
       <c r="B239" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C239" s="22" t="s">
         <v>85</v>
@@ -6101,7 +6244,7 @@
         <v>15</v>
       </c>
       <c r="B240" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C240" s="22" t="s">
         <v>86</v>
@@ -6118,7 +6261,7 @@
         <v>15</v>
       </c>
       <c r="B241" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C241" s="22" t="s">
         <v>87</v>
@@ -6135,7 +6278,7 @@
         <v>15</v>
       </c>
       <c r="B242" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C242" s="22" t="s">
         <v>88</v>
@@ -6152,7 +6295,7 @@
         <v>15</v>
       </c>
       <c r="B243" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C243" s="22" t="s">
         <v>89</v>
@@ -6169,7 +6312,7 @@
         <v>15</v>
       </c>
       <c r="B244" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C244" s="22" t="s">
         <v>90</v>
@@ -6186,7 +6329,7 @@
         <v>15</v>
       </c>
       <c r="B245" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C245" s="22" t="s">
         <v>91</v>
@@ -6203,7 +6346,7 @@
         <v>15</v>
       </c>
       <c r="B246" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C246" s="22" t="s">
         <v>92</v>
@@ -6220,7 +6363,7 @@
         <v>15</v>
       </c>
       <c r="B247" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C247" s="22" t="s">
         <v>93</v>
@@ -6237,7 +6380,7 @@
         <v>15</v>
       </c>
       <c r="B248" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C248" s="22" t="s">
         <v>94</v>
@@ -6254,7 +6397,7 @@
         <v>15</v>
       </c>
       <c r="B249" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C249" s="22" t="s">
         <v>95</v>
@@ -6271,7 +6414,7 @@
         <v>15</v>
       </c>
       <c r="B250" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C250" s="22" t="s">
         <v>96</v>
@@ -6288,7 +6431,7 @@
         <v>15</v>
       </c>
       <c r="B251" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C251" s="22" t="s">
         <v>97</v>
@@ -6305,7 +6448,7 @@
         <v>15</v>
       </c>
       <c r="B252" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C252" s="22" t="s">
         <v>98</v>
@@ -6322,7 +6465,7 @@
         <v>15</v>
       </c>
       <c r="B253" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C253" s="22" t="s">
         <v>99</v>
@@ -6339,7 +6482,7 @@
         <v>15</v>
       </c>
       <c r="B254" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C254" s="22" t="s">
         <v>100</v>
@@ -6356,7 +6499,7 @@
         <v>15</v>
       </c>
       <c r="B255" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C255" s="22" t="s">
         <v>101</v>
@@ -6373,7 +6516,7 @@
         <v>15</v>
       </c>
       <c r="B256" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C256" s="22" t="s">
         <v>102</v>
@@ -6390,7 +6533,7 @@
         <v>15</v>
       </c>
       <c r="B257" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C257" s="22" t="s">
         <v>103</v>
@@ -6407,7 +6550,7 @@
         <v>15</v>
       </c>
       <c r="B258" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C258" s="22" t="s">
         <v>104</v>
@@ -6424,7 +6567,7 @@
         <v>15</v>
       </c>
       <c r="B259" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C259" s="22" t="s">
         <v>105</v>
@@ -6441,7 +6584,7 @@
         <v>15</v>
       </c>
       <c r="B260" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C260" s="22" t="s">
         <v>106</v>
@@ -6458,7 +6601,7 @@
         <v>15</v>
       </c>
       <c r="B261" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C261" s="22" t="s">
         <v>107</v>
@@ -6475,7 +6618,7 @@
         <v>15</v>
       </c>
       <c r="B262" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C262" s="22" t="s">
         <v>108</v>
@@ -6492,7 +6635,7 @@
         <v>15</v>
       </c>
       <c r="B263" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C263" s="22" t="s">
         <v>109</v>
@@ -6509,7 +6652,7 @@
         <v>15</v>
       </c>
       <c r="B264" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C264" s="22" t="s">
         <v>110</v>
@@ -6526,7 +6669,7 @@
         <v>15</v>
       </c>
       <c r="B265" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C265" s="22" t="s">
         <v>111</v>
@@ -6543,7 +6686,7 @@
         <v>15</v>
       </c>
       <c r="B266" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C266" s="22" t="s">
         <v>112</v>
@@ -6560,7 +6703,7 @@
         <v>15</v>
       </c>
       <c r="B267" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C267" s="22" t="s">
         <v>113</v>
@@ -6577,7 +6720,7 @@
         <v>15</v>
       </c>
       <c r="B268" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C268" s="22" t="s">
         <v>114</v>
@@ -6594,7 +6737,7 @@
         <v>15</v>
       </c>
       <c r="B269" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C269" s="22" t="s">
         <v>115</v>
@@ -6611,7 +6754,7 @@
         <v>15</v>
       </c>
       <c r="B270" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C270" s="22" t="s">
         <v>116</v>
@@ -6628,7 +6771,7 @@
         <v>15</v>
       </c>
       <c r="B271" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C271" s="22" t="s">
         <v>117</v>
@@ -6645,7 +6788,7 @@
         <v>15</v>
       </c>
       <c r="B272" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C272" s="22" t="s">
         <v>118</v>
@@ -6662,7 +6805,7 @@
         <v>15</v>
       </c>
       <c r="B273" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C273" s="22" t="s">
         <v>119</v>
@@ -6679,7 +6822,7 @@
         <v>15</v>
       </c>
       <c r="B274" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C274" s="22" t="s">
         <v>120</v>
@@ -6691,12 +6834,12 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="14.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A275" s="24" t="s">
         <v>5</v>
       </c>
       <c r="B275" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C275" s="22" t="s">
         <v>7</v>
@@ -6713,7 +6856,7 @@
         <v>5</v>
       </c>
       <c r="B276" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C276" s="23" t="s">
         <v>9</v>
@@ -6726,12 +6869,12 @@
         <v>26.228608007767363</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="14.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A277" s="24" t="s">
         <v>5</v>
       </c>
       <c r="B277" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C277" s="23" t="s">
         <v>11</v>
@@ -6744,30 +6887,30 @@
         <v>16.306359141081622</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="278" spans="1:5" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A278" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B278" s="53" t="s">
-        <v>155</v>
-      </c>
-      <c r="C278" s="54" t="s">
+      <c r="B278" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C278" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="D278" s="55" t="s">
-        <v>8</v>
-      </c>
-      <c r="E278" s="56">
+      <c r="D278" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="E278" s="55">
         <f>9.31371545207318</f>
         <v>9.3137154520731809</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:5" ht="14.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A279" s="24" t="s">
         <v>5</v>
       </c>
       <c r="B279" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C279" s="22" t="s">
         <v>162</v>
@@ -6784,7 +6927,7 @@
         <v>5</v>
       </c>
       <c r="B280" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C280" s="23" t="s">
         <v>163</v>
@@ -6802,7 +6945,7 @@
         <v>5</v>
       </c>
       <c r="B281" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C281" s="23" t="s">
         <v>164</v>
@@ -6820,7 +6963,7 @@
         <v>5</v>
       </c>
       <c r="B282" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C282" s="23" t="s">
         <v>165</v>
@@ -6838,7 +6981,7 @@
         <v>5</v>
       </c>
       <c r="B283" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C283" s="23" t="s">
         <v>166</v>
@@ -6851,12 +6994,12 @@
         <v>26.228608007767363</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="14.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A284" s="24" t="s">
         <v>5</v>
       </c>
       <c r="B284" s="19" t="s">
-        <v>155</v>
+        <v>478</v>
       </c>
       <c r="C284" s="23" t="s">
         <v>167</v>
@@ -6873,8 +7016,8 @@
       <c r="A285" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B285" s="24" t="s">
-        <v>155</v>
+      <c r="B285" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C285" s="24" t="s">
         <v>212</v>
@@ -6890,8 +7033,8 @@
       <c r="A286" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B286" s="24" t="s">
-        <v>155</v>
+      <c r="B286" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C286" s="24" t="s">
         <v>213</v>
@@ -6907,8 +7050,8 @@
       <c r="A287" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B287" s="24" t="s">
-        <v>155</v>
+      <c r="B287" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C287" s="24" t="s">
         <v>214</v>
@@ -6924,8 +7067,8 @@
       <c r="A288" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B288" s="24" t="s">
-        <v>155</v>
+      <c r="B288" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C288" s="24" t="s">
         <v>215</v>
@@ -6941,8 +7084,8 @@
       <c r="A289" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B289" s="24" t="s">
-        <v>155</v>
+      <c r="B289" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C289" s="24" t="s">
         <v>216</v>
@@ -6958,8 +7101,8 @@
       <c r="A290" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B290" s="24" t="s">
-        <v>155</v>
+      <c r="B290" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C290" s="24" t="s">
         <v>217</v>
@@ -6975,8 +7118,8 @@
       <c r="A291" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B291" s="24" t="s">
-        <v>155</v>
+      <c r="B291" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C291" s="24" t="s">
         <v>218</v>
@@ -6992,8 +7135,8 @@
       <c r="A292" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B292" s="24" t="s">
-        <v>155</v>
+      <c r="B292" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C292" s="24" t="s">
         <v>219</v>
@@ -7009,8 +7152,8 @@
       <c r="A293" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B293" s="24" t="s">
-        <v>155</v>
+      <c r="B293" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C293" s="24" t="s">
         <v>220</v>
@@ -7026,8 +7169,8 @@
       <c r="A294" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B294" s="24" t="s">
-        <v>155</v>
+      <c r="B294" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C294" s="24" t="s">
         <v>221</v>
@@ -7043,8 +7186,8 @@
       <c r="A295" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B295" s="24" t="s">
-        <v>155</v>
+      <c r="B295" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C295" s="24" t="s">
         <v>222</v>
@@ -7060,8 +7203,8 @@
       <c r="A296" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B296" s="24" t="s">
-        <v>155</v>
+      <c r="B296" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C296" s="24" t="s">
         <v>223</v>
@@ -7077,8 +7220,8 @@
       <c r="A297" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B297" s="24" t="s">
-        <v>155</v>
+      <c r="B297" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C297" s="24" t="s">
         <v>224</v>
@@ -7094,8 +7237,8 @@
       <c r="A298" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B298" s="24" t="s">
-        <v>155</v>
+      <c r="B298" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C298" s="24" t="s">
         <v>236</v>
@@ -7111,8 +7254,8 @@
       <c r="A299" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B299" s="24" t="s">
-        <v>155</v>
+      <c r="B299" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C299" s="24" t="s">
         <v>237</v>
@@ -7128,8 +7271,8 @@
       <c r="A300" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B300" s="24" t="s">
-        <v>155</v>
+      <c r="B300" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C300" s="24" t="s">
         <v>238</v>
@@ -7145,8 +7288,8 @@
       <c r="A301" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B301" s="24" t="s">
-        <v>155</v>
+      <c r="B301" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C301" s="24" t="s">
         <v>239</v>
@@ -7162,8 +7305,8 @@
       <c r="A302" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B302" s="24" t="s">
-        <v>155</v>
+      <c r="B302" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C302" s="24" t="s">
         <v>240</v>
@@ -7179,8 +7322,8 @@
       <c r="A303" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B303" s="24" t="s">
-        <v>155</v>
+      <c r="B303" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C303" s="24" t="s">
         <v>241</v>
@@ -7196,8 +7339,8 @@
       <c r="A304" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B304" s="24" t="s">
-        <v>155</v>
+      <c r="B304" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C304" s="24" t="s">
         <v>242</v>
@@ -7213,8 +7356,8 @@
       <c r="A305" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B305" s="24" t="s">
-        <v>155</v>
+      <c r="B305" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C305" s="24" t="s">
         <v>243</v>
@@ -7230,8 +7373,8 @@
       <c r="A306" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B306" s="24" t="s">
-        <v>155</v>
+      <c r="B306" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C306" s="24" t="s">
         <v>244</v>
@@ -7247,8 +7390,8 @@
       <c r="A307" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B307" s="24" t="s">
-        <v>155</v>
+      <c r="B307" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C307" s="24" t="s">
         <v>245</v>
@@ -7264,8 +7407,8 @@
       <c r="A308" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B308" s="24" t="s">
-        <v>155</v>
+      <c r="B308" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C308" s="24" t="s">
         <v>246</v>
@@ -7281,8 +7424,8 @@
       <c r="A309" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B309" s="24" t="s">
-        <v>155</v>
+      <c r="B309" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C309" s="24" t="s">
         <v>247</v>
@@ -7298,8 +7441,8 @@
       <c r="A310" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B310" s="24" t="s">
-        <v>155</v>
+      <c r="B310" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C310" s="24" t="s">
         <v>248</v>
@@ -7315,8 +7458,8 @@
       <c r="A311" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B311" s="24" t="s">
-        <v>155</v>
+      <c r="B311" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C311" s="24" t="s">
         <v>249</v>
@@ -7332,8 +7475,8 @@
       <c r="A312" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B312" s="24" t="s">
-        <v>155</v>
+      <c r="B312" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C312" s="24" t="s">
         <v>250</v>
@@ -7349,8 +7492,8 @@
       <c r="A313" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B313" s="24" t="s">
-        <v>155</v>
+      <c r="B313" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C313" s="24" t="s">
         <v>251</v>
@@ -7366,8 +7509,8 @@
       <c r="A314" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B314" s="24" t="s">
-        <v>155</v>
+      <c r="B314" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C314" s="24" t="s">
         <v>252</v>
@@ -7383,8 +7526,8 @@
       <c r="A315" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B315" s="24" t="s">
-        <v>155</v>
+      <c r="B315" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C315" s="24" t="s">
         <v>253</v>
@@ -7400,8 +7543,8 @@
       <c r="A316" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B316" s="24" t="s">
-        <v>155</v>
+      <c r="B316" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C316" s="24" t="s">
         <v>254</v>
@@ -7417,8 +7560,8 @@
       <c r="A317" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B317" s="24" t="s">
-        <v>155</v>
+      <c r="B317" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C317" s="24" t="s">
         <v>260</v>
@@ -7434,8 +7577,8 @@
       <c r="A318" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B318" s="24" t="s">
-        <v>155</v>
+      <c r="B318" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C318" s="24" t="s">
         <v>261</v>
@@ -7451,8 +7594,8 @@
       <c r="A319" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B319" s="24" t="s">
-        <v>155</v>
+      <c r="B319" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C319" s="24" t="s">
         <v>262</v>
@@ -7468,8 +7611,8 @@
       <c r="A320" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B320" s="24" t="s">
-        <v>155</v>
+      <c r="B320" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C320" s="24" t="s">
         <v>263</v>
@@ -7485,8 +7628,8 @@
       <c r="A321" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B321" s="24" t="s">
-        <v>155</v>
+      <c r="B321" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C321" s="24" t="s">
         <v>264</v>
@@ -7502,8 +7645,8 @@
       <c r="A322" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B322" s="24" t="s">
-        <v>155</v>
+      <c r="B322" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C322" s="24" t="s">
         <v>265</v>
@@ -7519,8 +7662,8 @@
       <c r="A323" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B323" s="24" t="s">
-        <v>155</v>
+      <c r="B323" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C323" s="24" t="s">
         <v>266</v>
@@ -7536,8 +7679,8 @@
       <c r="A324" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B324" s="24" t="s">
-        <v>155</v>
+      <c r="B324" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C324" s="24" t="s">
         <v>267</v>
@@ -7553,8 +7696,8 @@
       <c r="A325" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B325" s="24" t="s">
-        <v>155</v>
+      <c r="B325" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C325" s="24" t="s">
         <v>268</v>
@@ -7570,8 +7713,8 @@
       <c r="A326" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B326" s="24" t="s">
-        <v>155</v>
+      <c r="B326" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C326" s="24" t="s">
         <v>269</v>
@@ -7587,8 +7730,8 @@
       <c r="A327" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B327" s="24" t="s">
-        <v>155</v>
+      <c r="B327" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C327" s="24" t="s">
         <v>270</v>
@@ -7604,8 +7747,8 @@
       <c r="A328" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B328" s="24" t="s">
-        <v>155</v>
+      <c r="B328" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C328" s="24" t="s">
         <v>271</v>
@@ -7621,8 +7764,8 @@
       <c r="A329" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B329" s="24" t="s">
-        <v>155</v>
+      <c r="B329" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C329" s="24" t="s">
         <v>272</v>
@@ -7638,8 +7781,8 @@
       <c r="A330" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B330" s="24" t="s">
-        <v>155</v>
+      <c r="B330" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C330" s="24" t="s">
         <v>273</v>
@@ -7655,8 +7798,8 @@
       <c r="A331" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B331" s="24" t="s">
-        <v>155</v>
+      <c r="B331" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C331" s="24" t="s">
         <v>274</v>
@@ -7672,8 +7815,8 @@
       <c r="A332" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B332" s="24" t="s">
-        <v>155</v>
+      <c r="B332" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C332" s="24" t="s">
         <v>275</v>
@@ -7689,8 +7832,8 @@
       <c r="A333" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B333" s="24" t="s">
-        <v>155</v>
+      <c r="B333" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C333" s="24" t="s">
         <v>276</v>
@@ -7706,8 +7849,8 @@
       <c r="A334" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B334" s="24" t="s">
-        <v>155</v>
+      <c r="B334" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C334" s="24" t="s">
         <v>277</v>
@@ -7723,8 +7866,8 @@
       <c r="A335" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B335" s="24" t="s">
-        <v>155</v>
+      <c r="B335" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C335" s="24" t="s">
         <v>278</v>
@@ -7740,8 +7883,8 @@
       <c r="A336" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B336" s="24" t="s">
-        <v>155</v>
+      <c r="B336" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C336" s="24" t="s">
         <v>279</v>
@@ -7757,8 +7900,8 @@
       <c r="A337" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B337" s="24" t="s">
-        <v>155</v>
+      <c r="B337" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C337" s="24" t="s">
         <v>280</v>
@@ -7774,8 +7917,8 @@
       <c r="A338" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B338" s="24" t="s">
-        <v>155</v>
+      <c r="B338" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C338" s="24" t="s">
         <v>281</v>
@@ -7791,8 +7934,8 @@
       <c r="A339" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B339" s="24" t="s">
-        <v>155</v>
+      <c r="B339" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C339" s="24" t="s">
         <v>282</v>
@@ -7808,8 +7951,8 @@
       <c r="A340" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B340" s="24" t="s">
-        <v>155</v>
+      <c r="B340" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C340" s="24" t="s">
         <v>283</v>
@@ -7825,8 +7968,8 @@
       <c r="A341" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B341" s="24" t="s">
-        <v>155</v>
+      <c r="B341" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C341" s="24" t="s">
         <v>284</v>
@@ -7842,8 +7985,8 @@
       <c r="A342" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B342" s="24" t="s">
-        <v>155</v>
+      <c r="B342" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C342" s="24" t="s">
         <v>285</v>
@@ -7859,8 +8002,8 @@
       <c r="A343" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B343" s="24" t="s">
-        <v>155</v>
+      <c r="B343" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C343" s="24" t="s">
         <v>286</v>
@@ -7876,8 +8019,8 @@
       <c r="A344" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B344" s="24" t="s">
-        <v>155</v>
+      <c r="B344" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C344" s="24" t="s">
         <v>287</v>
@@ -7893,8 +8036,8 @@
       <c r="A345" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B345" s="24" t="s">
-        <v>155</v>
+      <c r="B345" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C345" s="24" t="s">
         <v>288</v>
@@ -7910,8 +8053,8 @@
       <c r="A346" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B346" s="24" t="s">
-        <v>155</v>
+      <c r="B346" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C346" s="24" t="s">
         <v>289</v>
@@ -7927,8 +8070,8 @@
       <c r="A347" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B347" s="24" t="s">
-        <v>155</v>
+      <c r="B347" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C347" s="24" t="s">
         <v>290</v>
@@ -7944,8 +8087,8 @@
       <c r="A348" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B348" s="24" t="s">
-        <v>155</v>
+      <c r="B348" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C348" s="24" t="s">
         <v>291</v>
@@ -7961,8 +8104,8 @@
       <c r="A349" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B349" s="24" t="s">
-        <v>155</v>
+      <c r="B349" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C349" s="24" t="s">
         <v>292</v>
@@ -7978,8 +8121,8 @@
       <c r="A350" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B350" s="24" t="s">
-        <v>155</v>
+      <c r="B350" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C350" s="24" t="s">
         <v>293</v>
@@ -7995,8 +8138,8 @@
       <c r="A351" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B351" s="24" t="s">
-        <v>155</v>
+      <c r="B351" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C351" s="24" t="s">
         <v>295</v>
@@ -8012,8 +8155,8 @@
       <c r="A352" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B352" s="24" t="s">
-        <v>155</v>
+      <c r="B352" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C352" s="24" t="s">
         <v>296</v>
@@ -8029,8 +8172,8 @@
       <c r="A353" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B353" s="24" t="s">
-        <v>155</v>
+      <c r="B353" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C353" s="24" t="s">
         <v>297</v>
@@ -8046,8 +8189,8 @@
       <c r="A354" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B354" s="24" t="s">
-        <v>155</v>
+      <c r="B354" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C354" s="24" t="s">
         <v>298</v>
@@ -8063,8 +8206,8 @@
       <c r="A355" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B355" s="24" t="s">
-        <v>155</v>
+      <c r="B355" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C355" s="24" t="s">
         <v>299</v>
@@ -8080,8 +8223,8 @@
       <c r="A356" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B356" s="24" t="s">
-        <v>155</v>
+      <c r="B356" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C356" s="24" t="s">
         <v>300</v>
@@ -8097,8 +8240,8 @@
       <c r="A357" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B357" s="24" t="s">
-        <v>155</v>
+      <c r="B357" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C357" s="24" t="s">
         <v>301</v>
@@ -8114,8 +8257,8 @@
       <c r="A358" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B358" s="24" t="s">
-        <v>155</v>
+      <c r="B358" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C358" s="24" t="s">
         <v>302</v>
@@ -8131,8 +8274,8 @@
       <c r="A359" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B359" s="24" t="s">
-        <v>155</v>
+      <c r="B359" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C359" s="24" t="s">
         <v>303</v>
@@ -8148,8 +8291,8 @@
       <c r="A360" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B360" s="24" t="s">
-        <v>155</v>
+      <c r="B360" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C360" s="24" t="s">
         <v>304</v>
@@ -8165,8 +8308,8 @@
       <c r="A361" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B361" s="24" t="s">
-        <v>155</v>
+      <c r="B361" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C361" s="24" t="s">
         <v>305</v>
@@ -8182,8 +8325,8 @@
       <c r="A362" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B362" s="24" t="s">
-        <v>155</v>
+      <c r="B362" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C362" s="24" t="s">
         <v>306</v>
@@ -8199,8 +8342,8 @@
       <c r="A363" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B363" s="24" t="s">
-        <v>155</v>
+      <c r="B363" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C363" s="24" t="s">
         <v>307</v>
@@ -8216,8 +8359,8 @@
       <c r="A364" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B364" s="24" t="s">
-        <v>155</v>
+      <c r="B364" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C364" s="24" t="s">
         <v>308</v>
@@ -8233,8 +8376,8 @@
       <c r="A365" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B365" s="24" t="s">
-        <v>155</v>
+      <c r="B365" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C365" s="24" t="s">
         <v>310</v>
@@ -8250,8 +8393,8 @@
       <c r="A366" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B366" s="24" t="s">
-        <v>155</v>
+      <c r="B366" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C366" s="24" t="s">
         <v>311</v>
@@ -8267,8 +8410,8 @@
       <c r="A367" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B367" s="24" t="s">
-        <v>155</v>
+      <c r="B367" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C367" s="24" t="s">
         <v>312</v>
@@ -8284,8 +8427,8 @@
       <c r="A368" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B368" s="24" t="s">
-        <v>155</v>
+      <c r="B368" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C368" s="24" t="s">
         <v>313</v>
@@ -8301,8 +8444,8 @@
       <c r="A369" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B369" s="24" t="s">
-        <v>155</v>
+      <c r="B369" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C369" s="24" t="s">
         <v>314</v>
@@ -8318,8 +8461,8 @@
       <c r="A370" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B370" s="24" t="s">
-        <v>155</v>
+      <c r="B370" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C370" s="24" t="s">
         <v>315</v>
@@ -8335,8 +8478,8 @@
       <c r="A371" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B371" s="24" t="s">
-        <v>155</v>
+      <c r="B371" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C371" s="24" t="s">
         <v>316</v>
@@ -8352,8 +8495,8 @@
       <c r="A372" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B372" s="24" t="s">
-        <v>155</v>
+      <c r="B372" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C372" s="24" t="s">
         <v>317</v>
@@ -8369,8 +8512,8 @@
       <c r="A373" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B373" s="24" t="s">
-        <v>155</v>
+      <c r="B373" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C373" s="24" t="s">
         <v>318</v>
@@ -8386,8 +8529,8 @@
       <c r="A374" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B374" s="24" t="s">
-        <v>155</v>
+      <c r="B374" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C374" s="24" t="s">
         <v>319</v>
@@ -8403,8 +8546,8 @@
       <c r="A375" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B375" s="24" t="s">
-        <v>155</v>
+      <c r="B375" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C375" s="24" t="s">
         <v>320</v>
@@ -8420,8 +8563,8 @@
       <c r="A376" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B376" s="24" t="s">
-        <v>155</v>
+      <c r="B376" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C376" s="24" t="s">
         <v>321</v>
@@ -8437,8 +8580,8 @@
       <c r="A377" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B377" s="24" t="s">
-        <v>155</v>
+      <c r="B377" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C377" s="24" t="s">
         <v>322</v>
@@ -8454,8 +8597,8 @@
       <c r="A378" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B378" s="24" t="s">
-        <v>155</v>
+      <c r="B378" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C378" s="24" t="s">
         <v>323</v>
@@ -8471,8 +8614,8 @@
       <c r="A379" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B379" s="24" t="s">
-        <v>155</v>
+      <c r="B379" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C379" s="24" t="s">
         <v>324</v>
@@ -8488,8 +8631,8 @@
       <c r="A380" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B380" s="24" t="s">
-        <v>155</v>
+      <c r="B380" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C380" s="24" t="s">
         <v>325</v>
@@ -8505,8 +8648,8 @@
       <c r="A381" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B381" s="24" t="s">
-        <v>155</v>
+      <c r="B381" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C381" s="24" t="s">
         <v>326</v>
@@ -8522,8 +8665,8 @@
       <c r="A382" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B382" s="24" t="s">
-        <v>155</v>
+      <c r="B382" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C382" s="24" t="s">
         <v>327</v>
@@ -8539,8 +8682,8 @@
       <c r="A383" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B383" s="24" t="s">
-        <v>155</v>
+      <c r="B383" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C383" s="24" t="s">
         <v>328</v>
@@ -8556,8 +8699,8 @@
       <c r="A384" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B384" s="24" t="s">
-        <v>155</v>
+      <c r="B384" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C384" s="24" t="s">
         <v>329</v>
@@ -8573,8 +8716,8 @@
       <c r="A385" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B385" s="24" t="s">
-        <v>155</v>
+      <c r="B385" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C385" s="24" t="s">
         <v>330</v>
@@ -8590,8 +8733,8 @@
       <c r="A386" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B386" s="24" t="s">
-        <v>155</v>
+      <c r="B386" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C386" s="24" t="s">
         <v>331</v>
@@ -8607,8 +8750,8 @@
       <c r="A387" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B387" s="24" t="s">
-        <v>155</v>
+      <c r="B387" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C387" s="24" t="s">
         <v>332</v>
@@ -8624,8 +8767,8 @@
       <c r="A388" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B388" s="24" t="s">
-        <v>155</v>
+      <c r="B388" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C388" s="24" t="s">
         <v>333</v>
@@ -8641,8 +8784,8 @@
       <c r="A389" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B389" s="24" t="s">
-        <v>155</v>
+      <c r="B389" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C389" s="24" t="s">
         <v>334</v>
@@ -8658,8 +8801,8 @@
       <c r="A390" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B390" s="24" t="s">
-        <v>155</v>
+      <c r="B390" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C390" s="24" t="s">
         <v>335</v>
@@ -8675,8 +8818,8 @@
       <c r="A391" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B391" s="24" t="s">
-        <v>155</v>
+      <c r="B391" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C391" s="24" t="s">
         <v>336</v>
@@ -8692,8 +8835,8 @@
       <c r="A392" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B392" s="24" t="s">
-        <v>155</v>
+      <c r="B392" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C392" s="24" t="s">
         <v>337</v>
@@ -8709,8 +8852,8 @@
       <c r="A393" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B393" s="24" t="s">
-        <v>155</v>
+      <c r="B393" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C393" s="24" t="s">
         <v>338</v>
@@ -8726,8 +8869,8 @@
       <c r="A394" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B394" s="24" t="s">
-        <v>155</v>
+      <c r="B394" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C394" s="24" t="s">
         <v>339</v>
@@ -8743,8 +8886,8 @@
       <c r="A395" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B395" s="24" t="s">
-        <v>155</v>
+      <c r="B395" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C395" s="24" t="s">
         <v>340</v>
@@ -8760,8 +8903,8 @@
       <c r="A396" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B396" s="24" t="s">
-        <v>155</v>
+      <c r="B396" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C396" s="24" t="s">
         <v>341</v>
@@ -8777,8 +8920,8 @@
       <c r="A397" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B397" s="24" t="s">
-        <v>155</v>
+      <c r="B397" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C397" s="24" t="s">
         <v>342</v>
@@ -8794,8 +8937,8 @@
       <c r="A398" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B398" s="24" t="s">
-        <v>155</v>
+      <c r="B398" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C398" s="24" t="s">
         <v>343</v>
@@ -8811,8 +8954,8 @@
       <c r="A399" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B399" s="24" t="s">
-        <v>155</v>
+      <c r="B399" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C399" s="24" t="s">
         <v>344</v>
@@ -8828,8 +8971,8 @@
       <c r="A400" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B400" s="24" t="s">
-        <v>155</v>
+      <c r="B400" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C400" s="24" t="s">
         <v>345</v>
@@ -8845,8 +8988,8 @@
       <c r="A401" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B401" s="24" t="s">
-        <v>155</v>
+      <c r="B401" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C401" s="24" t="s">
         <v>346</v>
@@ -8862,8 +9005,8 @@
       <c r="A402" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B402" s="24" t="s">
-        <v>155</v>
+      <c r="B402" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C402" s="24" t="s">
         <v>347</v>
@@ -8879,8 +9022,8 @@
       <c r="A403" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B403" s="24" t="s">
-        <v>155</v>
+      <c r="B403" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C403" s="24" t="s">
         <v>348</v>
@@ -8896,8 +9039,8 @@
       <c r="A404" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B404" s="24" t="s">
-        <v>155</v>
+      <c r="B404" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C404" s="24" t="s">
         <v>349</v>
@@ -8913,8 +9056,8 @@
       <c r="A405" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B405" s="24" t="s">
-        <v>155</v>
+      <c r="B405" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C405" s="24" t="s">
         <v>350</v>
@@ -8930,8 +9073,8 @@
       <c r="A406" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B406" s="24" t="s">
-        <v>155</v>
+      <c r="B406" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C406" s="24" t="s">
         <v>351</v>
@@ -8947,8 +9090,8 @@
       <c r="A407" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B407" s="24" t="s">
-        <v>155</v>
+      <c r="B407" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C407" s="24" t="s">
         <v>352</v>
@@ -8964,8 +9107,8 @@
       <c r="A408" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B408" s="24" t="s">
-        <v>155</v>
+      <c r="B408" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C408" s="24" t="s">
         <v>353</v>
@@ -8981,8 +9124,8 @@
       <c r="A409" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B409" s="24" t="s">
-        <v>155</v>
+      <c r="B409" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C409" s="24" t="s">
         <v>354</v>
@@ -8998,8 +9141,8 @@
       <c r="A410" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B410" s="24" t="s">
-        <v>155</v>
+      <c r="B410" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C410" s="24" t="s">
         <v>355</v>
@@ -9015,8 +9158,8 @@
       <c r="A411" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B411" s="24" t="s">
-        <v>155</v>
+      <c r="B411" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C411" s="24" t="s">
         <v>356</v>
@@ -9032,8 +9175,8 @@
       <c r="A412" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B412" s="24" t="s">
-        <v>155</v>
+      <c r="B412" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C412" s="24" t="s">
         <v>357</v>
@@ -9049,8 +9192,8 @@
       <c r="A413" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B413" s="24" t="s">
-        <v>155</v>
+      <c r="B413" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C413" s="24" t="s">
         <v>168</v>
@@ -9066,8 +9209,8 @@
       <c r="A414" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B414" s="24" t="s">
-        <v>155</v>
+      <c r="B414" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C414" s="24" t="s">
         <v>169</v>
@@ -9083,8 +9226,8 @@
       <c r="A415" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B415" s="24" t="s">
-        <v>155</v>
+      <c r="B415" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C415" s="24" t="s">
         <v>170</v>
@@ -9100,8 +9243,8 @@
       <c r="A416" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B416" s="24" t="s">
-        <v>155</v>
+      <c r="B416" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C416" s="24" t="s">
         <v>171</v>
@@ -9117,8 +9260,8 @@
       <c r="A417" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B417" s="24" t="s">
-        <v>155</v>
+      <c r="B417" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C417" s="24" t="s">
         <v>172</v>
@@ -9134,8 +9277,8 @@
       <c r="A418" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B418" s="24" t="s">
-        <v>155</v>
+      <c r="B418" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C418" s="24" t="s">
         <v>173</v>
@@ -9151,8 +9294,8 @@
       <c r="A419" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B419" s="24" t="s">
-        <v>155</v>
+      <c r="B419" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C419" s="24" t="s">
         <v>174</v>
@@ -9168,8 +9311,8 @@
       <c r="A420" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B420" s="24" t="s">
-        <v>155</v>
+      <c r="B420" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C420" s="24" t="s">
         <v>175</v>
@@ -9185,8 +9328,8 @@
       <c r="A421" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B421" s="24" t="s">
-        <v>155</v>
+      <c r="B421" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C421" s="24" t="s">
         <v>176</v>
@@ -9202,8 +9345,8 @@
       <c r="A422" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B422" s="24" t="s">
-        <v>155</v>
+      <c r="B422" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C422" s="24" t="s">
         <v>177</v>
@@ -9219,8 +9362,8 @@
       <c r="A423" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B423" s="24" t="s">
-        <v>155</v>
+      <c r="B423" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C423" s="24" t="s">
         <v>178</v>
@@ -9236,8 +9379,8 @@
       <c r="A424" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B424" s="24" t="s">
-        <v>155</v>
+      <c r="B424" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C424" s="24" t="s">
         <v>179</v>
@@ -9253,8 +9396,8 @@
       <c r="A425" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B425" s="24" t="s">
-        <v>155</v>
+      <c r="B425" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C425" s="24" t="s">
         <v>180</v>
@@ -9270,8 +9413,8 @@
       <c r="A426" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B426" s="24" t="s">
-        <v>155</v>
+      <c r="B426" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C426" s="24" t="s">
         <v>181</v>
@@ -9287,8 +9430,8 @@
       <c r="A427" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B427" s="24" t="s">
-        <v>155</v>
+      <c r="B427" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C427" s="24" t="s">
         <v>182</v>
@@ -9304,8 +9447,8 @@
       <c r="A428" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B428" s="24" t="s">
-        <v>155</v>
+      <c r="B428" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C428" s="24" t="s">
         <v>183</v>
@@ -9321,8 +9464,8 @@
       <c r="A429" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B429" s="24" t="s">
-        <v>155</v>
+      <c r="B429" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C429" s="24" t="s">
         <v>184</v>
@@ -9338,8 +9481,8 @@
       <c r="A430" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B430" s="24" t="s">
-        <v>155</v>
+      <c r="B430" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C430" s="24" t="s">
         <v>185</v>
@@ -9355,8 +9498,8 @@
       <c r="A431" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B431" s="24" t="s">
-        <v>155</v>
+      <c r="B431" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C431" s="24" t="s">
         <v>186</v>
@@ -9372,8 +9515,8 @@
       <c r="A432" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B432" s="24" t="s">
-        <v>155</v>
+      <c r="B432" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C432" s="24" t="s">
         <v>358</v>
@@ -9389,8 +9532,8 @@
       <c r="A433" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B433" s="24" t="s">
-        <v>155</v>
+      <c r="B433" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C433" s="24" t="s">
         <v>187</v>
@@ -9406,8 +9549,8 @@
       <c r="A434" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B434" s="24" t="s">
-        <v>155</v>
+      <c r="B434" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C434" s="24" t="s">
         <v>188</v>
@@ -9423,8 +9566,8 @@
       <c r="A435" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B435" s="24" t="s">
-        <v>155</v>
+      <c r="B435" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C435" s="24" t="s">
         <v>189</v>
@@ -9440,8 +9583,8 @@
       <c r="A436" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B436" s="24" t="s">
-        <v>155</v>
+      <c r="B436" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C436" s="24" t="s">
         <v>359</v>
@@ -9457,8 +9600,8 @@
       <c r="A437" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B437" s="24" t="s">
-        <v>155</v>
+      <c r="B437" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C437" s="24" t="s">
         <v>360</v>
@@ -9474,8 +9617,8 @@
       <c r="A438" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B438" s="24" t="s">
-        <v>155</v>
+      <c r="B438" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C438" s="24" t="s">
         <v>361</v>
@@ -9491,8 +9634,8 @@
       <c r="A439" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B439" s="24" t="s">
-        <v>155</v>
+      <c r="B439" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C439" s="24" t="s">
         <v>362</v>
@@ -9508,8 +9651,8 @@
       <c r="A440" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B440" s="24" t="s">
-        <v>155</v>
+      <c r="B440" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C440" s="24" t="s">
         <v>363</v>
@@ -9525,8 +9668,8 @@
       <c r="A441" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B441" s="24" t="s">
-        <v>155</v>
+      <c r="B441" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C441" s="24" t="s">
         <v>364</v>
@@ -9542,8 +9685,8 @@
       <c r="A442" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B442" s="24" t="s">
-        <v>155</v>
+      <c r="B442" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C442" s="24" t="s">
         <v>365</v>
@@ -9559,8 +9702,8 @@
       <c r="A443" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B443" s="24" t="s">
-        <v>155</v>
+      <c r="B443" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C443" s="24" t="s">
         <v>366</v>
@@ -9576,8 +9719,8 @@
       <c r="A444" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B444" s="24" t="s">
-        <v>155</v>
+      <c r="B444" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C444" s="24" t="s">
         <v>367</v>
@@ -9593,8 +9736,8 @@
       <c r="A445" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B445" s="24" t="s">
-        <v>155</v>
+      <c r="B445" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C445" s="24" t="s">
         <v>368</v>
@@ -9610,8 +9753,8 @@
       <c r="A446" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B446" s="24" t="s">
-        <v>155</v>
+      <c r="B446" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C446" s="24" t="s">
         <v>369</v>
@@ -9627,8 +9770,8 @@
       <c r="A447" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B447" s="24" t="s">
-        <v>155</v>
+      <c r="B447" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C447" s="24" t="s">
         <v>370</v>
@@ -9644,8 +9787,8 @@
       <c r="A448" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B448" s="24" t="s">
-        <v>155</v>
+      <c r="B448" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C448" s="24" t="s">
         <v>371</v>
@@ -9661,8 +9804,8 @@
       <c r="A449" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B449" s="24" t="s">
-        <v>155</v>
+      <c r="B449" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C449" s="24" t="s">
         <v>372</v>
@@ -9678,8 +9821,8 @@
       <c r="A450" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B450" s="24" t="s">
-        <v>155</v>
+      <c r="B450" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C450" s="24" t="s">
         <v>373</v>
@@ -9695,8 +9838,8 @@
       <c r="A451" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B451" s="24" t="s">
-        <v>155</v>
+      <c r="B451" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C451" s="24" t="s">
         <v>374</v>
@@ -9712,8 +9855,8 @@
       <c r="A452" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B452" s="24" t="s">
-        <v>155</v>
+      <c r="B452" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C452" s="24" t="s">
         <v>375</v>
@@ -9729,8 +9872,8 @@
       <c r="A453" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B453" s="24" t="s">
-        <v>155</v>
+      <c r="B453" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C453" s="24" t="s">
         <v>376</v>
@@ -9746,8 +9889,8 @@
       <c r="A454" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B454" s="24" t="s">
-        <v>155</v>
+      <c r="B454" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C454" s="24" t="s">
         <v>377</v>
@@ -9763,8 +9906,8 @@
       <c r="A455" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B455" s="24" t="s">
-        <v>155</v>
+      <c r="B455" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C455" s="24" t="s">
         <v>378</v>
@@ -9780,8 +9923,8 @@
       <c r="A456" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B456" s="24" t="s">
-        <v>155</v>
+      <c r="B456" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C456" s="24" t="s">
         <v>379</v>
@@ -9797,8 +9940,8 @@
       <c r="A457" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B457" s="24" t="s">
-        <v>155</v>
+      <c r="B457" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C457" s="24" t="s">
         <v>380</v>
@@ -9814,8 +9957,8 @@
       <c r="A458" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B458" s="24" t="s">
-        <v>155</v>
+      <c r="B458" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C458" s="24" t="s">
         <v>381</v>
@@ -9831,8 +9974,8 @@
       <c r="A459" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B459" s="24" t="s">
-        <v>155</v>
+      <c r="B459" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C459" s="24" t="s">
         <v>382</v>
@@ -9848,8 +9991,8 @@
       <c r="A460" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B460" s="24" t="s">
-        <v>155</v>
+      <c r="B460" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C460" s="24" t="s">
         <v>383</v>
@@ -9865,8 +10008,8 @@
       <c r="A461" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B461" s="24" t="s">
-        <v>155</v>
+      <c r="B461" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C461" s="24" t="s">
         <v>384</v>
@@ -9882,8 +10025,8 @@
       <c r="A462" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B462" s="24" t="s">
-        <v>155</v>
+      <c r="B462" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C462" s="24" t="s">
         <v>385</v>
@@ -9899,8 +10042,8 @@
       <c r="A463" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B463" s="24" t="s">
-        <v>155</v>
+      <c r="B463" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C463" s="24" t="s">
         <v>386</v>
@@ -9916,8 +10059,8 @@
       <c r="A464" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B464" s="24" t="s">
-        <v>155</v>
+      <c r="B464" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C464" s="24" t="s">
         <v>387</v>
@@ -9933,8 +10076,8 @@
       <c r="A465" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B465" s="24" t="s">
-        <v>155</v>
+      <c r="B465" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C465" s="24" t="s">
         <v>389</v>
@@ -9950,8 +10093,8 @@
       <c r="A466" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B466" s="24" t="s">
-        <v>155</v>
+      <c r="B466" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C466" s="24" t="s">
         <v>390</v>
@@ -9967,8 +10110,8 @@
       <c r="A467" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B467" s="24" t="s">
-        <v>155</v>
+      <c r="B467" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C467" s="24" t="s">
         <v>391</v>
@@ -9984,8 +10127,8 @@
       <c r="A468" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B468" s="24" t="s">
-        <v>155</v>
+      <c r="B468" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C468" s="24" t="s">
         <v>392</v>
@@ -10001,8 +10144,8 @@
       <c r="A469" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B469" s="24" t="s">
-        <v>155</v>
+      <c r="B469" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C469" s="24" t="s">
         <v>393</v>
@@ -10018,8 +10161,8 @@
       <c r="A470" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B470" s="24" t="s">
-        <v>155</v>
+      <c r="B470" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C470" s="24" t="s">
         <v>394</v>
@@ -10035,8 +10178,8 @@
       <c r="A471" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B471" s="24" t="s">
-        <v>155</v>
+      <c r="B471" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C471" s="24" t="s">
         <v>395</v>
@@ -10052,8 +10195,8 @@
       <c r="A472" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B472" s="24" t="s">
-        <v>155</v>
+      <c r="B472" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C472" s="24" t="s">
         <v>396</v>
@@ -10069,8 +10212,8 @@
       <c r="A473" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B473" s="24" t="s">
-        <v>155</v>
+      <c r="B473" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C473" s="24" t="s">
         <v>397</v>
@@ -10086,8 +10229,8 @@
       <c r="A474" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B474" s="24" t="s">
-        <v>155</v>
+      <c r="B474" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C474" s="24" t="s">
         <v>398</v>
@@ -10103,8 +10246,8 @@
       <c r="A475" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B475" s="24" t="s">
-        <v>155</v>
+      <c r="B475" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C475" s="24" t="s">
         <v>399</v>
@@ -10120,8 +10263,8 @@
       <c r="A476" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B476" s="24" t="s">
-        <v>155</v>
+      <c r="B476" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C476" s="24" t="s">
         <v>400</v>
@@ -10137,8 +10280,8 @@
       <c r="A477" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B477" s="24" t="s">
-        <v>155</v>
+      <c r="B477" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C477" s="24" t="s">
         <v>401</v>
@@ -10154,8 +10297,8 @@
       <c r="A478" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B478" s="24" t="s">
-        <v>155</v>
+      <c r="B478" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C478" s="24" t="s">
         <v>402</v>
@@ -10171,8 +10314,8 @@
       <c r="A479" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B479" s="24" t="s">
-        <v>155</v>
+      <c r="B479" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C479" s="24" t="s">
         <v>403</v>
@@ -10188,8 +10331,8 @@
       <c r="A480" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B480" s="24" t="s">
-        <v>155</v>
+      <c r="B480" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C480" s="24" t="s">
         <v>190</v>
@@ -10205,8 +10348,8 @@
       <c r="A481" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B481" s="24" t="s">
-        <v>155</v>
+      <c r="B481" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C481" s="24" t="s">
         <v>191</v>
@@ -10222,8 +10365,8 @@
       <c r="A482" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B482" s="24" t="s">
-        <v>155</v>
+      <c r="B482" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C482" s="24" t="s">
         <v>192</v>
@@ -10239,8 +10382,8 @@
       <c r="A483" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B483" s="24" t="s">
-        <v>155</v>
+      <c r="B483" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C483" s="24" t="s">
         <v>193</v>
@@ -10256,8 +10399,8 @@
       <c r="A484" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B484" s="24" t="s">
-        <v>155</v>
+      <c r="B484" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C484" s="24" t="s">
         <v>194</v>
@@ -10273,8 +10416,8 @@
       <c r="A485" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B485" s="24" t="s">
-        <v>155</v>
+      <c r="B485" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C485" s="24" t="s">
         <v>195</v>
@@ -10290,8 +10433,8 @@
       <c r="A486" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B486" s="24" t="s">
-        <v>155</v>
+      <c r="B486" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C486" s="24" t="s">
         <v>196</v>
@@ -10307,8 +10450,8 @@
       <c r="A487" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B487" s="24" t="s">
-        <v>155</v>
+      <c r="B487" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C487" s="24" t="s">
         <v>197</v>
@@ -10324,8 +10467,8 @@
       <c r="A488" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B488" s="24" t="s">
-        <v>155</v>
+      <c r="B488" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C488" s="24" t="s">
         <v>198</v>
@@ -10341,8 +10484,8 @@
       <c r="A489" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B489" s="24" t="s">
-        <v>155</v>
+      <c r="B489" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C489" s="24" t="s">
         <v>199</v>
@@ -10358,8 +10501,8 @@
       <c r="A490" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B490" s="24" t="s">
-        <v>155</v>
+      <c r="B490" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C490" s="24" t="s">
         <v>200</v>
@@ -10375,8 +10518,8 @@
       <c r="A491" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B491" s="24" t="s">
-        <v>155</v>
+      <c r="B491" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C491" s="24" t="s">
         <v>201</v>
@@ -10392,8 +10535,8 @@
       <c r="A492" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B492" s="24" t="s">
-        <v>155</v>
+      <c r="B492" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C492" s="24" t="s">
         <v>202</v>
@@ -10409,8 +10552,8 @@
       <c r="A493" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B493" s="24" t="s">
-        <v>155</v>
+      <c r="B493" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C493" s="24" t="s">
         <v>203</v>
@@ -10426,8 +10569,8 @@
       <c r="A494" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B494" s="24" t="s">
-        <v>155</v>
+      <c r="B494" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C494" s="24" t="s">
         <v>204</v>
@@ -10443,8 +10586,8 @@
       <c r="A495" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B495" s="24" t="s">
-        <v>155</v>
+      <c r="B495" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C495" s="24" t="s">
         <v>205</v>
@@ -10460,8 +10603,8 @@
       <c r="A496" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B496" s="24" t="s">
-        <v>155</v>
+      <c r="B496" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C496" s="24" t="s">
         <v>206</v>
@@ -10477,8 +10620,8 @@
       <c r="A497" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B497" s="24" t="s">
-        <v>155</v>
+      <c r="B497" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C497" s="24" t="s">
         <v>207</v>
@@ -10494,8 +10637,8 @@
       <c r="A498" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B498" s="24" t="s">
-        <v>155</v>
+      <c r="B498" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C498" s="24" t="s">
         <v>208</v>
@@ -10511,8 +10654,8 @@
       <c r="A499" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B499" s="24" t="s">
-        <v>155</v>
+      <c r="B499" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C499" s="24" t="s">
         <v>209</v>
@@ -10528,8 +10671,8 @@
       <c r="A500" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B500" s="24" t="s">
-        <v>155</v>
+      <c r="B500" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C500" s="24" t="s">
         <v>210</v>
@@ -10545,8 +10688,8 @@
       <c r="A501" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B501" s="24" t="s">
-        <v>155</v>
+      <c r="B501" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C501" s="24" t="s">
         <v>211</v>
@@ -10562,8 +10705,8 @@
       <c r="A502" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B502" s="24" t="s">
-        <v>155</v>
+      <c r="B502" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C502" s="24" t="s">
         <v>405</v>
@@ -10579,8 +10722,8 @@
       <c r="A503" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B503" s="24" t="s">
-        <v>155</v>
+      <c r="B503" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C503" s="24" t="s">
         <v>406</v>
@@ -10596,8 +10739,8 @@
       <c r="A504" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B504" s="24" t="s">
-        <v>155</v>
+      <c r="B504" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C504" s="24" t="s">
         <v>407</v>
@@ -10613,8 +10756,8 @@
       <c r="A505" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B505" s="24" t="s">
-        <v>155</v>
+      <c r="B505" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C505" s="24" t="s">
         <v>408</v>
@@ -10630,8 +10773,8 @@
       <c r="A506" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B506" s="24" t="s">
-        <v>155</v>
+      <c r="B506" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C506" s="24" t="s">
         <v>409</v>
@@ -10647,8 +10790,8 @@
       <c r="A507" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B507" s="24" t="s">
-        <v>155</v>
+      <c r="B507" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C507" s="24" t="s">
         <v>410</v>
@@ -10664,8 +10807,8 @@
       <c r="A508" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B508" s="24" t="s">
-        <v>155</v>
+      <c r="B508" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C508" s="24" t="s">
         <v>411</v>
@@ -10681,8 +10824,8 @@
       <c r="A509" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B509" s="24" t="s">
-        <v>155</v>
+      <c r="B509" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C509" s="24" t="s">
         <v>412</v>
@@ -10698,8 +10841,8 @@
       <c r="A510" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B510" s="24" t="s">
-        <v>155</v>
+      <c r="B510" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C510" s="24" t="s">
         <v>413</v>
@@ -10715,8 +10858,8 @@
       <c r="A511" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B511" s="24" t="s">
-        <v>155</v>
+      <c r="B511" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C511" s="24" t="s">
         <v>414</v>
@@ -10732,8 +10875,8 @@
       <c r="A512" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B512" s="24" t="s">
-        <v>155</v>
+      <c r="B512" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C512" s="24" t="s">
         <v>415</v>
@@ -10749,8 +10892,8 @@
       <c r="A513" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B513" s="24" t="s">
-        <v>155</v>
+      <c r="B513" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C513" s="24" t="s">
         <v>416</v>
@@ -10766,8 +10909,8 @@
       <c r="A514" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B514" s="24" t="s">
-        <v>155</v>
+      <c r="B514" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C514" s="24" t="s">
         <v>417</v>
@@ -10783,8 +10926,8 @@
       <c r="A515" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B515" s="24" t="s">
-        <v>155</v>
+      <c r="B515" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C515" s="24" t="s">
         <v>418</v>
@@ -10800,8 +10943,8 @@
       <c r="A516" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B516" s="24" t="s">
-        <v>155</v>
+      <c r="B516" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C516" s="24" t="s">
         <v>419</v>
@@ -10817,8 +10960,8 @@
       <c r="A517" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B517" s="24" t="s">
-        <v>155</v>
+      <c r="B517" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C517" s="24" t="s">
         <v>420</v>
@@ -10834,8 +10977,8 @@
       <c r="A518" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B518" s="24" t="s">
-        <v>155</v>
+      <c r="B518" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C518" s="24" t="s">
         <v>421</v>
@@ -10851,8 +10994,8 @@
       <c r="A519" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B519" s="24" t="s">
-        <v>155</v>
+      <c r="B519" s="19" t="s">
+        <v>478</v>
       </c>
       <c r="C519" s="24" t="s">
         <v>422</v>
@@ -10865,19 +11008,1047 @@
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A520" s="48" t="s">
+      <c r="A520" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B520" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C520" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="D520" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E520" s="60">
+        <v>3.65E-7</v>
+      </c>
+    </row>
+    <row r="521" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A521" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B521" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C521" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="D521" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E521" s="60">
+        <v>2.28E-7</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A522" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B522" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C522" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="D522" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E522" s="60">
+        <v>2.28E-7</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A523" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B523" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C523" s="58" t="s">
+        <v>127</v>
+      </c>
+      <c r="D523" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E523" s="60">
+        <v>2.28E-7</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A524" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B524" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C524" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="D524" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E524" s="60">
+        <v>2.28E-7</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A525" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B525" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C525" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="D525" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E525" s="60">
+        <v>2.28E-7</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A526" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B526" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C526" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="D526" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E526" s="60">
+        <v>2.28E-7</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A527" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B527" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C527" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="D527" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E527" s="60">
+        <v>2.28E-7</v>
+      </c>
+    </row>
+    <row r="528" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A528" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B528" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C528" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="D528" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E528" s="60">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A529" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B529" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C529" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="D529" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E529" s="60">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A530" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B530" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C530" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="D530" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E530" s="60">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A531" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B531" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C531" s="58" t="s">
+        <v>135</v>
+      </c>
+      <c r="D531" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E531" s="60">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A532" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B532" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C532" s="58" t="s">
+        <v>136</v>
+      </c>
+      <c r="D532" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E532" s="60">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A533" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B533" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C533" s="58" t="s">
+        <v>137</v>
+      </c>
+      <c r="D533" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E533" s="60">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A534" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B534" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C534" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="D534" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E534" s="60">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A535" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B535" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C535" s="58" t="s">
+        <v>139</v>
+      </c>
+      <c r="D535" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E535" s="60">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A536" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B536" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C536" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="D536" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E536" s="60">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A537" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B537" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C537" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="D537" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E537" s="60">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A538" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B538" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C538" s="58" t="s">
+        <v>142</v>
+      </c>
+      <c r="D538" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E538" s="60">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A539" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B539" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C539" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="D539" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E539" s="60">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A540" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B540" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C540" s="58" t="s">
+        <v>144</v>
+      </c>
+      <c r="D540" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E540" s="60">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A541" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B541" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C541" s="58" t="s">
+        <v>158</v>
+      </c>
+      <c r="D541" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E541" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A542" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B542" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C542" s="58" t="s">
+        <v>159</v>
+      </c>
+      <c r="D542" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E542" s="60">
+        <v>5.2999999999999998E-8</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A543" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B543" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C543" s="58" t="s">
+        <v>160</v>
+      </c>
+      <c r="D543" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E543" s="60">
+        <v>5.2999999999999998E-8</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A544" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B544" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C544" s="58" t="s">
+        <v>161</v>
+      </c>
+      <c r="D544" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E544" s="60">
+        <v>5.2999999999999998E-8</v>
+      </c>
+    </row>
+    <row r="545" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A545" s="61" t="s">
         <v>427</v>
       </c>
-      <c r="B520" s="48" t="s">
+      <c r="B545" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C545" s="61" t="s">
+        <v>462</v>
+      </c>
+      <c r="D545" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E545" s="60">
+        <v>5.4624999999999996E-7</v>
+      </c>
+    </row>
+    <row r="546" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A546" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B546" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C546" s="61" t="s">
+        <v>463</v>
+      </c>
+      <c r="D546" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E546" s="60">
+        <v>4.3700000000000001E-7</v>
+      </c>
+    </row>
+    <row r="547" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A547" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B547" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C547" s="61" t="s">
+        <v>464</v>
+      </c>
+      <c r="D547" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E547" s="60">
+        <v>4.752375E-7</v>
+      </c>
+    </row>
+    <row r="548" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A548" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B548" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C548" s="61" t="s">
+        <v>465</v>
+      </c>
+      <c r="D548" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E548" s="60">
+        <v>1.0105625E-7</v>
+      </c>
+    </row>
+    <row r="549" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A549" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B549" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C549" s="61" t="s">
+        <v>466</v>
+      </c>
+      <c r="D549" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E549" s="60">
+        <v>1.0105625E-7</v>
+      </c>
+      <c r="F549" s="63"/>
+    </row>
+    <row r="550" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A550" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B550" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C550" s="61" t="s">
+        <v>467</v>
+      </c>
+      <c r="D550" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E550" s="60">
+        <v>1.3656249999999999E-7</v>
+      </c>
+      <c r="F550" s="63"/>
+    </row>
+    <row r="551" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A551" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B551" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C551" s="61" t="s">
+        <v>468</v>
+      </c>
+      <c r="D551" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E551" s="60">
+        <v>5.0254999999999996E-7</v>
+      </c>
+      <c r="F551" s="63"/>
+    </row>
+    <row r="552" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A552" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B552" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C552" s="61" t="s">
+        <v>469</v>
+      </c>
+      <c r="D552" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E552" s="60">
+        <v>4.9162500000000004E-7</v>
+      </c>
+      <c r="F552" s="63"/>
+    </row>
+    <row r="553" spans="1:6" s="63" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A553" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B553" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C553" s="61" t="s">
+        <v>470</v>
+      </c>
+      <c r="D553" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E553" s="60">
+        <v>4.0375E-7</v>
+      </c>
+    </row>
+    <row r="554" spans="1:6" s="63" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A554" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B554" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C554" s="61" t="s">
+        <v>471</v>
+      </c>
+      <c r="D554" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E554" s="60">
+        <v>4.0375E-7</v>
+      </c>
+    </row>
+    <row r="555" spans="1:6" s="63" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A555" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B555" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C555" s="61" t="s">
+        <v>472</v>
+      </c>
+      <c r="D555" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E555" s="60">
+        <v>4.0375E-7</v>
+      </c>
+      <c r="F555" s="6"/>
+    </row>
+    <row r="556" spans="1:6" s="63" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A556" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B556" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C556" s="61" t="s">
+        <v>473</v>
+      </c>
+      <c r="D556" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E556" s="60">
+        <v>4.0375E-7</v>
+      </c>
+      <c r="F556" s="6"/>
+    </row>
+    <row r="557" spans="1:6" s="63" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A557" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B557" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C557" s="61" t="s">
+        <v>474</v>
+      </c>
+      <c r="D557" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E557" s="60">
+        <v>4.0375E-7</v>
+      </c>
+      <c r="F557" s="6"/>
+    </row>
+    <row r="558" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A558" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B558" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C558" s="61" t="s">
+        <v>475</v>
+      </c>
+      <c r="D558" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E558" s="60">
+        <v>4.0375E-7</v>
+      </c>
+    </row>
+    <row r="559" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A559" s="62" t="s">
+        <v>427</v>
+      </c>
+      <c r="B559" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C559" s="62" t="s">
+        <v>476</v>
+      </c>
+      <c r="D559" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E559" s="64">
+        <v>3.8000000000000001E-7</v>
+      </c>
+    </row>
+    <row r="560" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A560" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B560" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C560" s="61" t="s">
+        <v>479</v>
+      </c>
+      <c r="D560" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E560" s="60">
+        <v>5.4624999999999996E-7</v>
+      </c>
+    </row>
+    <row r="561" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A561" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B561" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C561" s="61" t="s">
+        <v>480</v>
+      </c>
+      <c r="D561" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E561" s="60">
+        <v>4.369999999999999E-7</v>
+      </c>
+      <c r="G561" s="9"/>
+    </row>
+    <row r="562" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A562" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B562" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C562" s="61" t="s">
+        <v>481</v>
+      </c>
+      <c r="D562" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E562" s="60">
+        <v>4.7523749999999994E-7</v>
+      </c>
+      <c r="G562" s="9"/>
+    </row>
+    <row r="563" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A563" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B563" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C563" s="61" t="s">
+        <v>482</v>
+      </c>
+      <c r="D563" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E563" s="60">
+        <v>1.0105625000000002E-7</v>
+      </c>
+      <c r="G563" s="9"/>
+    </row>
+    <row r="564" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A564" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B564" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C564" s="61" t="s">
+        <v>483</v>
+      </c>
+      <c r="D564" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E564" s="60">
+        <v>5.4624999999999996E-7</v>
+      </c>
+      <c r="G564" s="9"/>
+    </row>
+    <row r="565" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A565" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B565" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C565" s="61" t="s">
+        <v>484</v>
+      </c>
+      <c r="D565" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E565" s="60">
+        <v>5.2002999999999987E-7</v>
+      </c>
+      <c r="G565" s="9"/>
+    </row>
+    <row r="566" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A566" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B566" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C566" s="61" t="s">
+        <v>485</v>
+      </c>
+      <c r="D566" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E566" s="60">
+        <v>6.6642499999999983E-8</v>
+      </c>
+      <c r="G566" s="9"/>
+    </row>
+    <row r="567" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A567" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B567" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C567" s="62" t="s">
+        <v>486</v>
+      </c>
+      <c r="D567" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E567" s="60">
+        <v>1.0105625000000002E-7</v>
+      </c>
+      <c r="G567" s="9"/>
+    </row>
+    <row r="568" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A568" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B568" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C568" s="61" t="s">
+        <v>487</v>
+      </c>
+      <c r="D568" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E568" s="60">
+        <v>1.0105625000000002E-7</v>
+      </c>
+      <c r="G568" s="9"/>
+    </row>
+    <row r="569" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A569" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B569" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C569" s="61" t="s">
+        <v>488</v>
+      </c>
+      <c r="D569" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E569" s="60">
+        <v>1.3656249999999996E-7</v>
+      </c>
+      <c r="G569" s="9"/>
+    </row>
+    <row r="570" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A570" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B570" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C570" s="61" t="s">
+        <v>489</v>
+      </c>
+      <c r="D570" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E570" s="60">
+        <v>5.0254999999999996E-7</v>
+      </c>
+      <c r="G570" s="9"/>
+    </row>
+    <row r="571" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A571" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B571" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C571" s="61" t="s">
+        <v>490</v>
+      </c>
+      <c r="D571" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E571" s="60">
+        <v>2.7312499999999993E-7</v>
+      </c>
+      <c r="G571" s="9"/>
+    </row>
+    <row r="572" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A572" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B572" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C572" s="61" t="s">
+        <v>491</v>
+      </c>
+      <c r="D572" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E572" s="60">
+        <v>4.9162499999999993E-7</v>
+      </c>
+      <c r="G572" s="9"/>
+    </row>
+    <row r="573" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A573" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B573" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C573" s="61" t="s">
+        <v>492</v>
+      </c>
+      <c r="D573" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E573" s="60">
+        <v>4.6431249999999992E-7</v>
+      </c>
+      <c r="G573" s="9"/>
+    </row>
+    <row r="574" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A574" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B574" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C574" s="61" t="s">
+        <v>493</v>
+      </c>
+      <c r="D574" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E574" s="60">
+        <v>4.6431249999999992E-7</v>
+      </c>
+      <c r="G574" s="9"/>
+    </row>
+    <row r="575" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A575" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B575" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C575" s="61" t="s">
+        <v>494</v>
+      </c>
+      <c r="D575" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E575" s="60">
+        <v>4.0374999999999995E-7</v>
+      </c>
+      <c r="G575" s="9"/>
+    </row>
+    <row r="576" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A576" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B576" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C576" s="61" t="s">
+        <v>495</v>
+      </c>
+      <c r="D576" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E576" s="60">
+        <v>3.7999999999999996E-7</v>
+      </c>
+      <c r="G576" s="9"/>
+    </row>
+    <row r="577" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A577" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B577" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C577" s="61" t="s">
+        <v>496</v>
+      </c>
+      <c r="D577" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E577" s="60">
+        <v>3.7999999999999996E-7</v>
+      </c>
+      <c r="G577" s="9"/>
+    </row>
+    <row r="578" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A578" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="B578" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C578" s="61" t="s">
+        <v>497</v>
+      </c>
+      <c r="D578" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="E578" s="60">
+        <v>3.7999999999999996E-7</v>
+      </c>
+      <c r="G578" s="9"/>
+    </row>
+    <row r="579" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A579" s="48" t="s">
+        <v>427</v>
+      </c>
+      <c r="B579" s="48" t="s">
         <v>428</v>
       </c>
-      <c r="C520" s="49" t="s">
+      <c r="C579" s="49" t="s">
         <v>429</v>
       </c>
-      <c r="D520" s="50" t="s">
+      <c r="D579" s="50" t="s">
         <v>430</v>
       </c>
-      <c r="E520" s="51">
+      <c r="E579" s="51">
         <v>1</v>
       </c>
     </row>
@@ -10901,7 +12072,7 @@
     <col min="7" max="16384" width="9.19921875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="38.200000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -10918,7 +12089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -13896,7 +15067,7 @@
     <col min="7" max="16384" width="9.19921875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="38.200000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -13913,7 +15084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -17470,7 +18641,7 @@
     <col min="5" max="5" width="13.19921875" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="38.200000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -17487,7 +18658,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>

--- a/data/facteurs de caractérisation.xlsx
+++ b/data/facteurs de caractérisation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\CIRED\PlaneFR\Code\Module_PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEB5B22-DDBF-4B3A-9BE7-4009525AAB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E29DC9A-A5E9-466C-A448-135899F0180C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Feuil1" sheetId="5" r:id="rId5"/>
     <sheet name="Feuil2" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1539,7 +1539,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1578,6 +1578,12 @@
       <color theme="1"/>
       <name val="Helvetica"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -2159,7 +2165,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24.6640625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="17" style="6" customWidth="1"/>
+    <col min="2" max="2" width="23.3984375" style="6" customWidth="1"/>
     <col min="3" max="3" width="72.9296875" style="15" customWidth="1"/>
     <col min="4" max="4" width="9" style="6" customWidth="1"/>
     <col min="5" max="5" width="13.19921875" style="16" customWidth="1"/>
@@ -4528,8 +4534,8 @@
         <v>148</v>
       </c>
       <c r="E139" s="21">
-        <f t="shared" ref="E139:E145" si="0">(0.772897890121685+0.110407441507011+0.0165)*1000000000</f>
-        <v>899805331.62869596</v>
+        <f t="shared" ref="E139:E145" si="0">(0.110407441507011+0.0165)*1000000000</f>
+        <v>126907441.507011</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
@@ -4547,7 +4553,7 @@
       </c>
       <c r="E140" s="21">
         <f t="shared" si="0"/>
-        <v>899805331.62869596</v>
+        <v>126907441.507011</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.45">
@@ -4565,7 +4571,7 @@
       </c>
       <c r="E141" s="21">
         <f t="shared" si="0"/>
-        <v>899805331.62869596</v>
+        <v>126907441.507011</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.45">
@@ -4583,7 +4589,7 @@
       </c>
       <c r="E142" s="21">
         <f t="shared" si="0"/>
-        <v>899805331.62869596</v>
+        <v>126907441.507011</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
@@ -4601,7 +4607,7 @@
       </c>
       <c r="E143" s="21">
         <f t="shared" si="0"/>
-        <v>899805331.62869596</v>
+        <v>126907441.507011</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
@@ -4619,7 +4625,7 @@
       </c>
       <c r="E144" s="21">
         <f t="shared" si="0"/>
-        <v>899805331.62869596</v>
+        <v>126907441.507011</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
@@ -4637,7 +4643,7 @@
       </c>
       <c r="E145" s="21">
         <f t="shared" si="0"/>
-        <v>899805331.62869596</v>
+        <v>126907441.507011</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
@@ -12053,6 +12059,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
 </worksheet>

--- a/data/facteurs de caractérisation.xlsx
+++ b/data/facteurs de caractérisation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\CIRED\PlaneFR\Code\Module_PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E29DC9A-A5E9-466C-A448-135899F0180C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593C9AF9-A693-4768-A589-F129895F6C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Feuil1" sheetId="5" r:id="rId5"/>
     <sheet name="Feuil2" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>

--- a/data/facteurs de caractérisation.xlsx
+++ b/data/facteurs de caractérisation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\CIRED\PlaneFR\Code\Module_PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D30BDE-4BB8-4E35-8F8C-B8E4EC4DD7EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC80E7E-889C-45A1-B902-5CC01D3EB4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="8002" windowWidth="14595" windowHeight="8745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="synthèse" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4432" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4428" uniqueCount="531">
   <si>
     <t>Processus du système Terre</t>
   </si>
@@ -2275,7 +2275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G631"/>
+  <dimension ref="A1:G630"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24.69140625" style="6" customWidth="1"/>
@@ -2356,20 +2356,20 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A5" s="38" t="s">
-        <v>461</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="41">
-        <v>3.0399999999999998E-10</v>
+      <c r="A5" s="43" t="s">
+        <v>499</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="46">
+        <v>3E-10</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
@@ -2380,7 +2380,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="45" t="s">
         <v>8</v>
@@ -2390,20 +2390,20 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A7" s="43" t="s">
-        <v>499</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="46">
-        <v>3E-10</v>
+      <c r="A7" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="37">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
@@ -2414,7 +2414,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D8" s="36" t="s">
         <v>18</v>
@@ -2431,7 +2431,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="36" t="s">
         <v>18</v>
@@ -2448,7 +2448,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="36" t="s">
         <v>18</v>
@@ -2465,7 +2465,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="36" t="s">
         <v>18</v>
@@ -2482,7 +2482,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" s="36" t="s">
         <v>18</v>
@@ -2499,7 +2499,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" s="36" t="s">
         <v>18</v>
@@ -2516,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" s="36" t="s">
         <v>18</v>
@@ -2533,7 +2533,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15" s="36" t="s">
         <v>18</v>
@@ -2550,7 +2550,7 @@
         <v>16</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16" s="36" t="s">
         <v>18</v>
@@ -2567,7 +2567,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17" s="36" t="s">
         <v>18</v>
@@ -2584,7 +2584,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18" s="36" t="s">
         <v>18</v>
@@ -2601,7 +2601,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19" s="36" t="s">
         <v>18</v>
@@ -2618,7 +2618,7 @@
         <v>16</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20" s="36" t="s">
         <v>18</v>
@@ -2635,7 +2635,7 @@
         <v>16</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21" s="36" t="s">
         <v>18</v>
@@ -2652,7 +2652,7 @@
         <v>16</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" s="36" t="s">
         <v>18</v>
@@ -2669,7 +2669,7 @@
         <v>16</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" s="36" t="s">
         <v>18</v>
@@ -2686,7 +2686,7 @@
         <v>16</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24" s="36" t="s">
         <v>18</v>
@@ -2703,7 +2703,7 @@
         <v>16</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D25" s="36" t="s">
         <v>18</v>
@@ -2720,7 +2720,7 @@
         <v>16</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D26" s="36" t="s">
         <v>18</v>
@@ -2737,7 +2737,7 @@
         <v>16</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D27" s="36" t="s">
         <v>18</v>
@@ -2754,7 +2754,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D28" s="36" t="s">
         <v>18</v>
@@ -2771,7 +2771,7 @@
         <v>16</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D29" s="36" t="s">
         <v>18</v>
@@ -2788,7 +2788,7 @@
         <v>16</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D30" s="36" t="s">
         <v>18</v>
@@ -2805,7 +2805,7 @@
         <v>16</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D31" s="36" t="s">
         <v>18</v>
@@ -2822,7 +2822,7 @@
         <v>16</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D32" s="36" t="s">
         <v>18</v>
@@ -2839,7 +2839,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D33" s="36" t="s">
         <v>18</v>
@@ -2856,7 +2856,7 @@
         <v>16</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D34" s="36" t="s">
         <v>18</v>
@@ -2873,7 +2873,7 @@
         <v>16</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D35" s="36" t="s">
         <v>18</v>
@@ -2890,7 +2890,7 @@
         <v>16</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D36" s="36" t="s">
         <v>18</v>
@@ -2907,7 +2907,7 @@
         <v>16</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D37" s="36" t="s">
         <v>18</v>
@@ -2924,7 +2924,7 @@
         <v>16</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D38" s="36" t="s">
         <v>18</v>
@@ -2941,7 +2941,7 @@
         <v>16</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D39" s="36" t="s">
         <v>18</v>
@@ -2958,7 +2958,7 @@
         <v>16</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D40" s="36" t="s">
         <v>18</v>
@@ -2975,7 +2975,7 @@
         <v>16</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D41" s="36" t="s">
         <v>18</v>
@@ -2992,7 +2992,7 @@
         <v>16</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D42" s="36" t="s">
         <v>18</v>
@@ -3009,7 +3009,7 @@
         <v>16</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D43" s="36" t="s">
         <v>18</v>
@@ -3026,7 +3026,7 @@
         <v>16</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D44" s="36" t="s">
         <v>18</v>
@@ -3043,7 +3043,7 @@
         <v>16</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D45" s="36" t="s">
         <v>18</v>
@@ -3060,7 +3060,7 @@
         <v>16</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D46" s="36" t="s">
         <v>18</v>
@@ -3077,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D47" s="36" t="s">
         <v>18</v>
@@ -3094,7 +3094,7 @@
         <v>16</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D48" s="36" t="s">
         <v>18</v>
@@ -3111,7 +3111,7 @@
         <v>16</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D49" s="36" t="s">
         <v>18</v>
@@ -3128,7 +3128,7 @@
         <v>16</v>
       </c>
       <c r="C50" s="35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D50" s="36" t="s">
         <v>18</v>
@@ -3145,7 +3145,7 @@
         <v>16</v>
       </c>
       <c r="C51" s="35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D51" s="36" t="s">
         <v>18</v>
@@ -3162,7 +3162,7 @@
         <v>16</v>
       </c>
       <c r="C52" s="35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D52" s="36" t="s">
         <v>18</v>
@@ -3179,7 +3179,7 @@
         <v>16</v>
       </c>
       <c r="C53" s="35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D53" s="36" t="s">
         <v>18</v>
@@ -3196,7 +3196,7 @@
         <v>16</v>
       </c>
       <c r="C54" s="35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D54" s="36" t="s">
         <v>18</v>
@@ -3213,7 +3213,7 @@
         <v>16</v>
       </c>
       <c r="C55" s="35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D55" s="36" t="s">
         <v>18</v>
@@ -3230,7 +3230,7 @@
         <v>16</v>
       </c>
       <c r="C56" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D56" s="36" t="s">
         <v>18</v>
@@ -3247,7 +3247,7 @@
         <v>16</v>
       </c>
       <c r="C57" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D57" s="36" t="s">
         <v>18</v>
@@ -3264,7 +3264,7 @@
         <v>16</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D58" s="36" t="s">
         <v>18</v>
@@ -3281,7 +3281,7 @@
         <v>16</v>
       </c>
       <c r="C59" s="35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D59" s="36" t="s">
         <v>18</v>
@@ -3298,7 +3298,7 @@
         <v>16</v>
       </c>
       <c r="C60" s="35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D60" s="36" t="s">
         <v>18</v>
@@ -3315,7 +3315,7 @@
         <v>16</v>
       </c>
       <c r="C61" s="35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D61" s="36" t="s">
         <v>18</v>
@@ -3332,7 +3332,7 @@
         <v>16</v>
       </c>
       <c r="C62" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D62" s="36" t="s">
         <v>18</v>
@@ -3349,7 +3349,7 @@
         <v>16</v>
       </c>
       <c r="C63" s="35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D63" s="36" t="s">
         <v>18</v>
@@ -3366,7 +3366,7 @@
         <v>16</v>
       </c>
       <c r="C64" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D64" s="36" t="s">
         <v>18</v>
@@ -3383,7 +3383,7 @@
         <v>16</v>
       </c>
       <c r="C65" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D65" s="36" t="s">
         <v>18</v>
@@ -3400,7 +3400,7 @@
         <v>16</v>
       </c>
       <c r="C66" s="35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D66" s="36" t="s">
         <v>18</v>
@@ -3417,7 +3417,7 @@
         <v>16</v>
       </c>
       <c r="C67" s="35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D67" s="36" t="s">
         <v>18</v>
@@ -3434,7 +3434,7 @@
         <v>16</v>
       </c>
       <c r="C68" s="35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D68" s="36" t="s">
         <v>18</v>
@@ -3451,7 +3451,7 @@
         <v>16</v>
       </c>
       <c r="C69" s="35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D69" s="36" t="s">
         <v>18</v>
@@ -3468,7 +3468,7 @@
         <v>16</v>
       </c>
       <c r="C70" s="35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D70" s="36" t="s">
         <v>18</v>
@@ -3485,7 +3485,7 @@
         <v>16</v>
       </c>
       <c r="C71" s="35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D71" s="36" t="s">
         <v>18</v>
@@ -3502,7 +3502,7 @@
         <v>16</v>
       </c>
       <c r="C72" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D72" s="36" t="s">
         <v>18</v>
@@ -3519,7 +3519,7 @@
         <v>16</v>
       </c>
       <c r="C73" s="35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D73" s="36" t="s">
         <v>18</v>
@@ -3536,7 +3536,7 @@
         <v>16</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D74" s="36" t="s">
         <v>18</v>
@@ -3553,7 +3553,7 @@
         <v>16</v>
       </c>
       <c r="C75" s="35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D75" s="36" t="s">
         <v>18</v>
@@ -3570,7 +3570,7 @@
         <v>16</v>
       </c>
       <c r="C76" s="35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D76" s="36" t="s">
         <v>18</v>
@@ -3587,7 +3587,7 @@
         <v>16</v>
       </c>
       <c r="C77" s="35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D77" s="36" t="s">
         <v>18</v>
@@ -3604,7 +3604,7 @@
         <v>16</v>
       </c>
       <c r="C78" s="35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D78" s="36" t="s">
         <v>18</v>
@@ -3621,7 +3621,7 @@
         <v>16</v>
       </c>
       <c r="C79" s="35" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D79" s="36" t="s">
         <v>18</v>
@@ -3638,7 +3638,7 @@
         <v>16</v>
       </c>
       <c r="C80" s="35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D80" s="36" t="s">
         <v>18</v>
@@ -3655,7 +3655,7 @@
         <v>16</v>
       </c>
       <c r="C81" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D81" s="36" t="s">
         <v>18</v>
@@ -3672,7 +3672,7 @@
         <v>16</v>
       </c>
       <c r="C82" s="35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D82" s="36" t="s">
         <v>18</v>
@@ -3689,7 +3689,7 @@
         <v>16</v>
       </c>
       <c r="C83" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D83" s="36" t="s">
         <v>18</v>
@@ -3706,7 +3706,7 @@
         <v>16</v>
       </c>
       <c r="C84" s="35" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D84" s="36" t="s">
         <v>18</v>
@@ -3723,7 +3723,7 @@
         <v>16</v>
       </c>
       <c r="C85" s="35" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D85" s="36" t="s">
         <v>18</v>
@@ -3740,7 +3740,7 @@
         <v>16</v>
       </c>
       <c r="C86" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D86" s="36" t="s">
         <v>18</v>
@@ -3757,7 +3757,7 @@
         <v>16</v>
       </c>
       <c r="C87" s="35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D87" s="36" t="s">
         <v>18</v>
@@ -3774,7 +3774,7 @@
         <v>16</v>
       </c>
       <c r="C88" s="35" t="s">
-        <v>98</v>
+        <v>500</v>
       </c>
       <c r="D88" s="36" t="s">
         <v>18</v>
@@ -3791,7 +3791,7 @@
         <v>16</v>
       </c>
       <c r="C89" s="35" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="D89" s="36" t="s">
         <v>18</v>
@@ -3808,7 +3808,7 @@
         <v>16</v>
       </c>
       <c r="C90" s="35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D90" s="36" t="s">
         <v>18</v>
@@ -3825,7 +3825,7 @@
         <v>16</v>
       </c>
       <c r="C91" s="35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D91" s="36" t="s">
         <v>18</v>
@@ -3842,7 +3842,7 @@
         <v>16</v>
       </c>
       <c r="C92" s="35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D92" s="36" t="s">
         <v>18</v>
@@ -3859,7 +3859,7 @@
         <v>16</v>
       </c>
       <c r="C93" s="35" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D93" s="36" t="s">
         <v>18</v>
@@ -3876,7 +3876,7 @@
         <v>16</v>
       </c>
       <c r="C94" s="35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D94" s="36" t="s">
         <v>18</v>
@@ -3893,7 +3893,7 @@
         <v>16</v>
       </c>
       <c r="C95" s="35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D95" s="36" t="s">
         <v>18</v>
@@ -3910,7 +3910,7 @@
         <v>16</v>
       </c>
       <c r="C96" s="35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D96" s="36" t="s">
         <v>18</v>
@@ -3927,7 +3927,7 @@
         <v>16</v>
       </c>
       <c r="C97" s="35" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D97" s="36" t="s">
         <v>18</v>
@@ -3944,7 +3944,7 @@
         <v>16</v>
       </c>
       <c r="C98" s="35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D98" s="36" t="s">
         <v>18</v>
@@ -3961,7 +3961,7 @@
         <v>16</v>
       </c>
       <c r="C99" s="35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D99" s="36" t="s">
         <v>18</v>
@@ -3978,7 +3978,7 @@
         <v>16</v>
       </c>
       <c r="C100" s="35" t="s">
-        <v>110</v>
+        <v>501</v>
       </c>
       <c r="D100" s="36" t="s">
         <v>18</v>
@@ -3995,7 +3995,7 @@
         <v>16</v>
       </c>
       <c r="C101" s="35" t="s">
-        <v>501</v>
+        <v>112</v>
       </c>
       <c r="D101" s="36" t="s">
         <v>18</v>
@@ -4012,7 +4012,7 @@
         <v>16</v>
       </c>
       <c r="C102" s="35" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D102" s="36" t="s">
         <v>18</v>
@@ -4029,7 +4029,7 @@
         <v>16</v>
       </c>
       <c r="C103" s="35" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D103" s="36" t="s">
         <v>18</v>
@@ -4046,7 +4046,7 @@
         <v>16</v>
       </c>
       <c r="C104" s="35" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D104" s="36" t="s">
         <v>18</v>
@@ -4063,7 +4063,7 @@
         <v>16</v>
       </c>
       <c r="C105" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D105" s="36" t="s">
         <v>18</v>
@@ -4080,7 +4080,7 @@
         <v>16</v>
       </c>
       <c r="C106" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D106" s="36" t="s">
         <v>18</v>
@@ -4097,7 +4097,7 @@
         <v>16</v>
       </c>
       <c r="C107" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D107" s="36" t="s">
         <v>18</v>
@@ -4114,7 +4114,7 @@
         <v>16</v>
       </c>
       <c r="C108" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D108" s="36" t="s">
         <v>18</v>
@@ -4131,7 +4131,7 @@
         <v>16</v>
       </c>
       <c r="C109" s="35" t="s">
-        <v>119</v>
+        <v>502</v>
       </c>
       <c r="D109" s="36" t="s">
         <v>18</v>
@@ -4148,7 +4148,7 @@
         <v>16</v>
       </c>
       <c r="C110" s="35" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D110" s="36" t="s">
         <v>18</v>
@@ -4165,7 +4165,7 @@
         <v>16</v>
       </c>
       <c r="C111" s="35" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D111" s="36" t="s">
         <v>18</v>
@@ -4182,7 +4182,7 @@
         <v>16</v>
       </c>
       <c r="C112" s="35" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D112" s="36" t="s">
         <v>18</v>
@@ -4199,7 +4199,7 @@
         <v>16</v>
       </c>
       <c r="C113" s="35" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D113" s="36" t="s">
         <v>18</v>
@@ -4216,7 +4216,7 @@
         <v>16</v>
       </c>
       <c r="C114" s="35" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D114" s="36" t="s">
         <v>18</v>
@@ -4233,7 +4233,7 @@
         <v>16</v>
       </c>
       <c r="C115" s="35" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D115" s="36" t="s">
         <v>18</v>
@@ -4250,7 +4250,7 @@
         <v>16</v>
       </c>
       <c r="C116" s="35" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D116" s="36" t="s">
         <v>18</v>
@@ -4267,7 +4267,7 @@
         <v>16</v>
       </c>
       <c r="C117" s="35" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D117" s="36" t="s">
         <v>18</v>
@@ -4284,7 +4284,7 @@
         <v>16</v>
       </c>
       <c r="C118" s="35" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D118" s="36" t="s">
         <v>18</v>
@@ -4301,7 +4301,7 @@
         <v>16</v>
       </c>
       <c r="C119" s="35" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D119" s="36" t="s">
         <v>18</v>
@@ -4318,7 +4318,7 @@
         <v>16</v>
       </c>
       <c r="C120" s="35" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D120" s="36" t="s">
         <v>18</v>
@@ -4335,7 +4335,7 @@
         <v>16</v>
       </c>
       <c r="C121" s="35" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D121" s="36" t="s">
         <v>18</v>
@@ -4352,7 +4352,7 @@
         <v>16</v>
       </c>
       <c r="C122" s="35" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D122" s="36" t="s">
         <v>18</v>
@@ -4369,7 +4369,7 @@
         <v>16</v>
       </c>
       <c r="C123" s="35" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D123" s="36" t="s">
         <v>18</v>
@@ -4386,7 +4386,7 @@
         <v>16</v>
       </c>
       <c r="C124" s="35" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D124" s="36" t="s">
         <v>18</v>
@@ -4403,7 +4403,7 @@
         <v>16</v>
       </c>
       <c r="C125" s="35" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D125" s="36" t="s">
         <v>18</v>
@@ -4420,7 +4420,7 @@
         <v>16</v>
       </c>
       <c r="C126" s="35" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D126" s="36" t="s">
         <v>18</v>
@@ -4437,7 +4437,7 @@
         <v>16</v>
       </c>
       <c r="C127" s="35" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D127" s="36" t="s">
         <v>18</v>
@@ -4454,7 +4454,7 @@
         <v>16</v>
       </c>
       <c r="C128" s="35" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D128" s="36" t="s">
         <v>18</v>
@@ -4471,7 +4471,7 @@
         <v>16</v>
       </c>
       <c r="C129" s="35" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D129" s="36" t="s">
         <v>18</v>
@@ -4488,7 +4488,7 @@
         <v>16</v>
       </c>
       <c r="C130" s="35" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D130" s="36" t="s">
         <v>18</v>
@@ -4505,7 +4505,7 @@
         <v>16</v>
       </c>
       <c r="C131" s="35" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D131" s="36" t="s">
         <v>18</v>
@@ -4522,7 +4522,7 @@
         <v>16</v>
       </c>
       <c r="C132" s="35" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D132" s="36" t="s">
         <v>18</v>
@@ -4539,7 +4539,7 @@
         <v>16</v>
       </c>
       <c r="C133" s="35" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D133" s="36" t="s">
         <v>18</v>
@@ -4556,7 +4556,7 @@
         <v>16</v>
       </c>
       <c r="C134" s="35" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D134" s="36" t="s">
         <v>18</v>
@@ -4573,7 +4573,7 @@
         <v>16</v>
       </c>
       <c r="C135" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D135" s="36" t="s">
         <v>18</v>
@@ -4583,19 +4583,19 @@
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A136" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" s="35" t="s">
-        <v>528</v>
-      </c>
-      <c r="D136" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E136" s="37">
+      <c r="A136" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B136" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="C136" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="D136" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E136" s="34">
         <v>1</v>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
         <v>122</v>
       </c>
       <c r="C137" s="32" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D137" s="33" t="s">
         <v>124</v>
@@ -4624,7 +4624,7 @@
         <v>122</v>
       </c>
       <c r="C138" s="32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D138" s="33" t="s">
         <v>124</v>
@@ -4641,7 +4641,7 @@
         <v>122</v>
       </c>
       <c r="C139" s="32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D139" s="33" t="s">
         <v>124</v>
@@ -4658,7 +4658,7 @@
         <v>122</v>
       </c>
       <c r="C140" s="32" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D140" s="33" t="s">
         <v>124</v>
@@ -4675,7 +4675,7 @@
         <v>122</v>
       </c>
       <c r="C141" s="32" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D141" s="33" t="s">
         <v>124</v>
@@ -4692,7 +4692,7 @@
         <v>122</v>
       </c>
       <c r="C142" s="32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D142" s="33" t="s">
         <v>124</v>
@@ -4709,7 +4709,7 @@
         <v>122</v>
       </c>
       <c r="C143" s="32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D143" s="33" t="s">
         <v>124</v>
@@ -4726,7 +4726,7 @@
         <v>122</v>
       </c>
       <c r="C144" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D144" s="33" t="s">
         <v>124</v>
@@ -4743,7 +4743,7 @@
         <v>122</v>
       </c>
       <c r="C145" s="32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D145" s="33" t="s">
         <v>124</v>
@@ -4760,7 +4760,7 @@
         <v>122</v>
       </c>
       <c r="C146" s="32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D146" s="33" t="s">
         <v>124</v>
@@ -4777,7 +4777,7 @@
         <v>122</v>
       </c>
       <c r="C147" s="32" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D147" s="33" t="s">
         <v>124</v>
@@ -4794,7 +4794,7 @@
         <v>122</v>
       </c>
       <c r="C148" s="32" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D148" s="33" t="s">
         <v>124</v>
@@ -4811,7 +4811,7 @@
         <v>122</v>
       </c>
       <c r="C149" s="32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D149" s="33" t="s">
         <v>124</v>
@@ -4828,7 +4828,7 @@
         <v>122</v>
       </c>
       <c r="C150" s="32" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D150" s="33" t="s">
         <v>124</v>
@@ -4845,7 +4845,7 @@
         <v>122</v>
       </c>
       <c r="C151" s="32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D151" s="33" t="s">
         <v>124</v>
@@ -4862,7 +4862,7 @@
         <v>122</v>
       </c>
       <c r="C152" s="32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D152" s="33" t="s">
         <v>124</v>
@@ -4879,7 +4879,7 @@
         <v>122</v>
       </c>
       <c r="C153" s="32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D153" s="33" t="s">
         <v>124</v>
@@ -4896,7 +4896,7 @@
         <v>122</v>
       </c>
       <c r="C154" s="32" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D154" s="33" t="s">
         <v>124</v>
@@ -4913,7 +4913,7 @@
         <v>122</v>
       </c>
       <c r="C155" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D155" s="33" t="s">
         <v>124</v>
@@ -4930,7 +4930,7 @@
         <v>122</v>
       </c>
       <c r="C156" s="32" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D156" s="33" t="s">
         <v>124</v>
@@ -4940,25 +4940,25 @@
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A157" s="31" t="s">
-        <v>498</v>
-      </c>
-      <c r="B157" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C157" s="32" t="s">
-        <v>144</v>
-      </c>
-      <c r="D157" s="33" t="s">
-        <v>124</v>
-      </c>
-      <c r="E157" s="34">
+      <c r="A157" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B157" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C157" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="D157" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E157" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A158" s="26" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B158" s="26" t="s">
         <v>146</v>
@@ -4981,7 +4981,7 @@
         <v>146</v>
       </c>
       <c r="C159" s="27" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D159" s="28" t="s">
         <v>148</v>
@@ -4997,8 +4997,8 @@
       <c r="B160" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C160" s="27" t="s">
-        <v>150</v>
+      <c r="C160" s="30" t="s">
+        <v>151</v>
       </c>
       <c r="D160" s="28" t="s">
         <v>148</v>
@@ -5015,7 +5015,7 @@
         <v>146</v>
       </c>
       <c r="C161" s="30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D161" s="28" t="s">
         <v>148</v>
@@ -5032,7 +5032,7 @@
         <v>146</v>
       </c>
       <c r="C162" s="30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D162" s="28" t="s">
         <v>148</v>
@@ -5049,7 +5049,7 @@
         <v>146</v>
       </c>
       <c r="C163" s="30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D163" s="28" t="s">
         <v>148</v>
@@ -5059,25 +5059,26 @@
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A164" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="B164" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="C164" s="30" t="s">
-        <v>154</v>
-      </c>
-      <c r="D164" s="28" t="s">
+      <c r="A164" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="B164" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C164" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D164" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="E164" s="29">
-        <v>1</v>
+      <c r="E164" s="21">
+        <f t="shared" ref="E164:E170" si="0">(0.110407441507011+0.0165)*1000000000</f>
+        <v>126907441.507011</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A165" s="18" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B165" s="19" t="s">
         <v>478</v>
@@ -5089,7 +5090,7 @@
         <v>148</v>
       </c>
       <c r="E165" s="21">
-        <f t="shared" ref="E165:E171" si="0">(0.110407441507011+0.0165)*1000000000</f>
+        <f t="shared" si="0"/>
         <v>126907441.507011</v>
       </c>
     </row>
@@ -5101,7 +5102,7 @@
         <v>478</v>
       </c>
       <c r="C166" s="19" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D166" s="20" t="s">
         <v>148</v>
@@ -5118,8 +5119,8 @@
       <c r="B167" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C167" s="19" t="s">
-        <v>150</v>
+      <c r="C167" s="22" t="s">
+        <v>151</v>
       </c>
       <c r="D167" s="20" t="s">
         <v>148</v>
@@ -5137,7 +5138,7 @@
         <v>478</v>
       </c>
       <c r="C168" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D168" s="20" t="s">
         <v>148</v>
@@ -5155,7 +5156,7 @@
         <v>478</v>
       </c>
       <c r="C169" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D169" s="20" t="s">
         <v>148</v>
@@ -5173,7 +5174,7 @@
         <v>478</v>
       </c>
       <c r="C170" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D170" s="20" t="s">
         <v>148</v>
@@ -5185,20 +5186,19 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A171" s="18" t="s">
-        <v>149</v>
+        <v>498</v>
       </c>
       <c r="B171" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C171" s="22" t="s">
-        <v>154</v>
+      <c r="C171" s="23" t="s">
+        <v>157</v>
       </c>
       <c r="D171" s="20" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="E171" s="21">
-        <f t="shared" si="0"/>
-        <v>126907441.507011</v>
+        <v>485679.81716597301</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.4">
@@ -5209,13 +5209,13 @@
         <v>478</v>
       </c>
       <c r="C172" s="23" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="D172" s="20" t="s">
         <v>124</v>
       </c>
       <c r="E172" s="21">
-        <v>485679.81716597301</v>
+        <v>608053.19508885196</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.4">
@@ -5226,7 +5226,7 @@
         <v>478</v>
       </c>
       <c r="C173" s="23" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D173" s="20" t="s">
         <v>124</v>
@@ -5243,7 +5243,7 @@
         <v>478</v>
       </c>
       <c r="C174" s="23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D174" s="20" t="s">
         <v>124</v>
@@ -5260,7 +5260,7 @@
         <v>478</v>
       </c>
       <c r="C175" s="23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D175" s="20" t="s">
         <v>124</v>
@@ -5277,7 +5277,7 @@
         <v>478</v>
       </c>
       <c r="C176" s="23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D176" s="20" t="s">
         <v>124</v>
@@ -5294,7 +5294,7 @@
         <v>478</v>
       </c>
       <c r="C177" s="23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D177" s="20" t="s">
         <v>124</v>
@@ -5311,7 +5311,7 @@
         <v>478</v>
       </c>
       <c r="C178" s="23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D178" s="20" t="s">
         <v>124</v>
@@ -5328,7 +5328,7 @@
         <v>478</v>
       </c>
       <c r="C179" s="23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D179" s="20" t="s">
         <v>124</v>
@@ -5345,13 +5345,13 @@
         <v>478</v>
       </c>
       <c r="C180" s="23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D180" s="20" t="s">
         <v>124</v>
       </c>
       <c r="E180" s="21">
-        <v>608053.19508885196</v>
+        <v>229042.93475783701</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.4">
@@ -5362,7 +5362,7 @@
         <v>478</v>
       </c>
       <c r="C181" s="23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D181" s="20" t="s">
         <v>124</v>
@@ -5379,7 +5379,7 @@
         <v>478</v>
       </c>
       <c r="C182" s="23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D182" s="20" t="s">
         <v>124</v>
@@ -5396,7 +5396,7 @@
         <v>478</v>
       </c>
       <c r="C183" s="23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D183" s="20" t="s">
         <v>124</v>
@@ -5413,7 +5413,7 @@
         <v>478</v>
       </c>
       <c r="C184" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D184" s="20" t="s">
         <v>124</v>
@@ -5430,7 +5430,7 @@
         <v>478</v>
       </c>
       <c r="C185" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D185" s="20" t="s">
         <v>124</v>
@@ -5447,7 +5447,7 @@
         <v>478</v>
       </c>
       <c r="C186" s="23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D186" s="20" t="s">
         <v>124</v>
@@ -5464,7 +5464,7 @@
         <v>478</v>
       </c>
       <c r="C187" s="23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D187" s="20" t="s">
         <v>124</v>
@@ -5481,7 +5481,7 @@
         <v>478</v>
       </c>
       <c r="C188" s="23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D188" s="20" t="s">
         <v>124</v>
@@ -5498,7 +5498,7 @@
         <v>478</v>
       </c>
       <c r="C189" s="23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D189" s="20" t="s">
         <v>124</v>
@@ -5515,7 +5515,7 @@
         <v>478</v>
       </c>
       <c r="C190" s="23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D190" s="20" t="s">
         <v>124</v>
@@ -5532,7 +5532,7 @@
         <v>478</v>
       </c>
       <c r="C191" s="23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D191" s="20" t="s">
         <v>124</v>
@@ -5549,7 +5549,7 @@
         <v>478</v>
       </c>
       <c r="C192" s="23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D192" s="20" t="s">
         <v>124</v>
@@ -5566,7 +5566,7 @@
         <v>478</v>
       </c>
       <c r="C193" s="23" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="D193" s="20" t="s">
         <v>124</v>
@@ -5583,7 +5583,7 @@
         <v>478</v>
       </c>
       <c r="C194" s="23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D194" s="20" t="s">
         <v>124</v>
@@ -5600,7 +5600,7 @@
         <v>478</v>
       </c>
       <c r="C195" s="23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D195" s="20" t="s">
         <v>124</v>
@@ -5609,7 +5609,7 @@
         <v>229042.93475783701</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:5" s="62" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A196" s="18" t="s">
         <v>498</v>
       </c>
@@ -5617,13 +5617,13 @@
         <v>478</v>
       </c>
       <c r="C196" s="23" t="s">
-        <v>161</v>
+        <v>529</v>
       </c>
       <c r="D196" s="20" t="s">
         <v>124</v>
       </c>
       <c r="E196" s="21">
-        <v>229042.93475783701</v>
+        <v>109564.693955489</v>
       </c>
     </row>
     <row r="197" spans="1:5" s="62" customFormat="1" x14ac:dyDescent="0.4">
@@ -5634,7 +5634,7 @@
         <v>478</v>
       </c>
       <c r="C197" s="23" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D197" s="20" t="s">
         <v>124</v>
@@ -5643,21 +5643,21 @@
         <v>109564.693955489</v>
       </c>
     </row>
-    <row r="198" spans="1:5" s="62" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A198" s="18" t="s">
-        <v>498</v>
+        <v>15</v>
       </c>
       <c r="B198" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C198" s="23" t="s">
-        <v>530</v>
+      <c r="C198" s="19" t="s">
+        <v>17</v>
       </c>
       <c r="D198" s="20" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="E198" s="21">
-        <v>109564.693955489</v>
+        <v>306.2</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.4">
@@ -5668,7 +5668,7 @@
         <v>478</v>
       </c>
       <c r="C199" s="19" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D199" s="20" t="s">
         <v>18</v>
@@ -5685,7 +5685,7 @@
         <v>478</v>
       </c>
       <c r="C200" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D200" s="20" t="s">
         <v>18</v>
@@ -5702,7 +5702,7 @@
         <v>478</v>
       </c>
       <c r="C201" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D201" s="20" t="s">
         <v>18</v>
@@ -5719,7 +5719,7 @@
         <v>478</v>
       </c>
       <c r="C202" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D202" s="20" t="s">
         <v>18</v>
@@ -5736,7 +5736,7 @@
         <v>478</v>
       </c>
       <c r="C203" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D203" s="20" t="s">
         <v>18</v>
@@ -5753,7 +5753,7 @@
         <v>478</v>
       </c>
       <c r="C204" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D204" s="20" t="s">
         <v>18</v>
@@ -5770,7 +5770,7 @@
         <v>478</v>
       </c>
       <c r="C205" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D205" s="20" t="s">
         <v>18</v>
@@ -5787,7 +5787,7 @@
         <v>478</v>
       </c>
       <c r="C206" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D206" s="20" t="s">
         <v>18</v>
@@ -5804,7 +5804,7 @@
         <v>478</v>
       </c>
       <c r="C207" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D207" s="20" t="s">
         <v>18</v>
@@ -5821,7 +5821,7 @@
         <v>478</v>
       </c>
       <c r="C208" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D208" s="20" t="s">
         <v>18</v>
@@ -5838,7 +5838,7 @@
         <v>478</v>
       </c>
       <c r="C209" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D209" s="20" t="s">
         <v>18</v>
@@ -5855,7 +5855,7 @@
         <v>478</v>
       </c>
       <c r="C210" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D210" s="20" t="s">
         <v>18</v>
@@ -5872,7 +5872,7 @@
         <v>478</v>
       </c>
       <c r="C211" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D211" s="20" t="s">
         <v>18</v>
@@ -5889,7 +5889,7 @@
         <v>478</v>
       </c>
       <c r="C212" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D212" s="20" t="s">
         <v>18</v>
@@ -5906,7 +5906,7 @@
         <v>478</v>
       </c>
       <c r="C213" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D213" s="20" t="s">
         <v>18</v>
@@ -5923,7 +5923,7 @@
         <v>478</v>
       </c>
       <c r="C214" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D214" s="20" t="s">
         <v>18</v>
@@ -5940,7 +5940,7 @@
         <v>478</v>
       </c>
       <c r="C215" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D215" s="20" t="s">
         <v>18</v>
@@ -5957,7 +5957,7 @@
         <v>478</v>
       </c>
       <c r="C216" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D216" s="20" t="s">
         <v>18</v>
@@ -5974,7 +5974,7 @@
         <v>478</v>
       </c>
       <c r="C217" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D217" s="20" t="s">
         <v>18</v>
@@ -5991,7 +5991,7 @@
         <v>478</v>
       </c>
       <c r="C218" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D218" s="20" t="s">
         <v>18</v>
@@ -6008,7 +6008,7 @@
         <v>478</v>
       </c>
       <c r="C219" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D219" s="20" t="s">
         <v>18</v>
@@ -6025,7 +6025,7 @@
         <v>478</v>
       </c>
       <c r="C220" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D220" s="20" t="s">
         <v>18</v>
@@ -6042,7 +6042,7 @@
         <v>478</v>
       </c>
       <c r="C221" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D221" s="20" t="s">
         <v>18</v>
@@ -6059,7 +6059,7 @@
         <v>478</v>
       </c>
       <c r="C222" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D222" s="20" t="s">
         <v>18</v>
@@ -6076,7 +6076,7 @@
         <v>478</v>
       </c>
       <c r="C223" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D223" s="20" t="s">
         <v>18</v>
@@ -6093,7 +6093,7 @@
         <v>478</v>
       </c>
       <c r="C224" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D224" s="20" t="s">
         <v>18</v>
@@ -6110,7 +6110,7 @@
         <v>478</v>
       </c>
       <c r="C225" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D225" s="20" t="s">
         <v>18</v>
@@ -6127,7 +6127,7 @@
         <v>478</v>
       </c>
       <c r="C226" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D226" s="20" t="s">
         <v>18</v>
@@ -6144,7 +6144,7 @@
         <v>478</v>
       </c>
       <c r="C227" s="19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D227" s="20" t="s">
         <v>18</v>
@@ -6161,7 +6161,7 @@
         <v>478</v>
       </c>
       <c r="C228" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D228" s="20" t="s">
         <v>18</v>
@@ -6178,7 +6178,7 @@
         <v>478</v>
       </c>
       <c r="C229" s="19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D229" s="20" t="s">
         <v>18</v>
@@ -6195,7 +6195,7 @@
         <v>478</v>
       </c>
       <c r="C230" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D230" s="20" t="s">
         <v>18</v>
@@ -6212,7 +6212,7 @@
         <v>478</v>
       </c>
       <c r="C231" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D231" s="20" t="s">
         <v>18</v>
@@ -6229,7 +6229,7 @@
         <v>478</v>
       </c>
       <c r="C232" s="19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D232" s="20" t="s">
         <v>18</v>
@@ -6246,7 +6246,7 @@
         <v>478</v>
       </c>
       <c r="C233" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D233" s="20" t="s">
         <v>18</v>
@@ -6263,7 +6263,7 @@
         <v>478</v>
       </c>
       <c r="C234" s="19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D234" s="20" t="s">
         <v>18</v>
@@ -6280,7 +6280,7 @@
         <v>478</v>
       </c>
       <c r="C235" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D235" s="20" t="s">
         <v>18</v>
@@ -6297,7 +6297,7 @@
         <v>478</v>
       </c>
       <c r="C236" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D236" s="20" t="s">
         <v>18</v>
@@ -6314,7 +6314,7 @@
         <v>478</v>
       </c>
       <c r="C237" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D237" s="20" t="s">
         <v>18</v>
@@ -6331,7 +6331,7 @@
         <v>478</v>
       </c>
       <c r="C238" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D238" s="20" t="s">
         <v>18</v>
@@ -6348,7 +6348,7 @@
         <v>478</v>
       </c>
       <c r="C239" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D239" s="20" t="s">
         <v>18</v>
@@ -6365,7 +6365,7 @@
         <v>478</v>
       </c>
       <c r="C240" s="19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D240" s="20" t="s">
         <v>18</v>
@@ -6382,7 +6382,7 @@
         <v>478</v>
       </c>
       <c r="C241" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D241" s="20" t="s">
         <v>18</v>
@@ -6399,7 +6399,7 @@
         <v>478</v>
       </c>
       <c r="C242" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D242" s="20" t="s">
         <v>18</v>
@@ -6416,7 +6416,7 @@
         <v>478</v>
       </c>
       <c r="C243" s="19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D243" s="20" t="s">
         <v>18</v>
@@ -6433,7 +6433,7 @@
         <v>478</v>
       </c>
       <c r="C244" s="19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D244" s="20" t="s">
         <v>18</v>
@@ -6450,7 +6450,7 @@
         <v>478</v>
       </c>
       <c r="C245" s="19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D245" s="20" t="s">
         <v>18</v>
@@ -6467,7 +6467,7 @@
         <v>478</v>
       </c>
       <c r="C246" s="19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D246" s="20" t="s">
         <v>18</v>
@@ -6484,7 +6484,7 @@
         <v>478</v>
       </c>
       <c r="C247" s="19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D247" s="20" t="s">
         <v>18</v>
@@ -6501,7 +6501,7 @@
         <v>478</v>
       </c>
       <c r="C248" s="19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D248" s="20" t="s">
         <v>18</v>
@@ -6518,7 +6518,7 @@
         <v>478</v>
       </c>
       <c r="C249" s="19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D249" s="20" t="s">
         <v>18</v>
@@ -6535,7 +6535,7 @@
         <v>478</v>
       </c>
       <c r="C250" s="19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D250" s="20" t="s">
         <v>18</v>
@@ -6552,7 +6552,7 @@
         <v>478</v>
       </c>
       <c r="C251" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D251" s="20" t="s">
         <v>18</v>
@@ -6569,7 +6569,7 @@
         <v>478</v>
       </c>
       <c r="C252" s="19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D252" s="20" t="s">
         <v>18</v>
@@ -6586,7 +6586,7 @@
         <v>478</v>
       </c>
       <c r="C253" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D253" s="20" t="s">
         <v>18</v>
@@ -6603,7 +6603,7 @@
         <v>478</v>
       </c>
       <c r="C254" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D254" s="20" t="s">
         <v>18</v>
@@ -6620,7 +6620,7 @@
         <v>478</v>
       </c>
       <c r="C255" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D255" s="20" t="s">
         <v>18</v>
@@ -6637,7 +6637,7 @@
         <v>478</v>
       </c>
       <c r="C256" s="19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D256" s="20" t="s">
         <v>18</v>
@@ -6654,7 +6654,7 @@
         <v>478</v>
       </c>
       <c r="C257" s="19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D257" s="20" t="s">
         <v>18</v>
@@ -6671,7 +6671,7 @@
         <v>478</v>
       </c>
       <c r="C258" s="19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D258" s="20" t="s">
         <v>18</v>
@@ -6688,7 +6688,7 @@
         <v>478</v>
       </c>
       <c r="C259" s="19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D259" s="20" t="s">
         <v>18</v>
@@ -6705,7 +6705,7 @@
         <v>478</v>
       </c>
       <c r="C260" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D260" s="20" t="s">
         <v>18</v>
@@ -6722,7 +6722,7 @@
         <v>478</v>
       </c>
       <c r="C261" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D261" s="20" t="s">
         <v>18</v>
@@ -6739,7 +6739,7 @@
         <v>478</v>
       </c>
       <c r="C262" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D262" s="20" t="s">
         <v>18</v>
@@ -6756,7 +6756,7 @@
         <v>478</v>
       </c>
       <c r="C263" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D263" s="20" t="s">
         <v>18</v>
@@ -6773,7 +6773,7 @@
         <v>478</v>
       </c>
       <c r="C264" s="19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D264" s="20" t="s">
         <v>18</v>
@@ -6790,7 +6790,7 @@
         <v>478</v>
       </c>
       <c r="C265" s="19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D265" s="20" t="s">
         <v>18</v>
@@ -6807,7 +6807,7 @@
         <v>478</v>
       </c>
       <c r="C266" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D266" s="20" t="s">
         <v>18</v>
@@ -6824,7 +6824,7 @@
         <v>478</v>
       </c>
       <c r="C267" s="19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D267" s="20" t="s">
         <v>18</v>
@@ -6841,7 +6841,7 @@
         <v>478</v>
       </c>
       <c r="C268" s="19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D268" s="20" t="s">
         <v>18</v>
@@ -6858,7 +6858,7 @@
         <v>478</v>
       </c>
       <c r="C269" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D269" s="20" t="s">
         <v>18</v>
@@ -6875,7 +6875,7 @@
         <v>478</v>
       </c>
       <c r="C270" s="19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D270" s="20" t="s">
         <v>18</v>
@@ -6892,7 +6892,7 @@
         <v>478</v>
       </c>
       <c r="C271" s="19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D271" s="20" t="s">
         <v>18</v>
@@ -6909,7 +6909,7 @@
         <v>478</v>
       </c>
       <c r="C272" s="19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D272" s="20" t="s">
         <v>18</v>
@@ -6926,7 +6926,7 @@
         <v>478</v>
       </c>
       <c r="C273" s="19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D273" s="20" t="s">
         <v>18</v>
@@ -6943,7 +6943,7 @@
         <v>478</v>
       </c>
       <c r="C274" s="19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D274" s="20" t="s">
         <v>18</v>
@@ -6952,7 +6952,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A275" s="18" t="s">
         <v>15</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>478</v>
       </c>
       <c r="C275" s="19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D275" s="20" t="s">
         <v>18</v>
@@ -6969,7 +6969,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A276" s="18" t="s">
         <v>15</v>
       </c>
@@ -6977,7 +6977,7 @@
         <v>478</v>
       </c>
       <c r="C276" s="19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D276" s="20" t="s">
         <v>18</v>
@@ -6986,7 +6986,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A277" s="18" t="s">
         <v>15</v>
       </c>
@@ -6994,7 +6994,7 @@
         <v>478</v>
       </c>
       <c r="C277" s="19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D277" s="20" t="s">
         <v>18</v>
@@ -7003,7 +7003,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:5" ht="14.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A278" s="18" t="s">
         <v>15</v>
       </c>
@@ -7011,7 +7011,7 @@
         <v>478</v>
       </c>
       <c r="C278" s="19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D278" s="20" t="s">
         <v>18</v>
@@ -7028,7 +7028,7 @@
         <v>478</v>
       </c>
       <c r="C279" s="19" t="s">
-        <v>98</v>
+        <v>500</v>
       </c>
       <c r="D279" s="20" t="s">
         <v>18</v>
@@ -7037,7 +7037,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="14.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A280" s="18" t="s">
         <v>15</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>478</v>
       </c>
       <c r="C280" s="19" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="D280" s="20" t="s">
         <v>18</v>
@@ -7062,7 +7062,7 @@
         <v>478</v>
       </c>
       <c r="C281" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D281" s="20" t="s">
         <v>18</v>
@@ -7079,7 +7079,7 @@
         <v>478</v>
       </c>
       <c r="C282" s="19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D282" s="20" t="s">
         <v>18</v>
@@ -7096,7 +7096,7 @@
         <v>478</v>
       </c>
       <c r="C283" s="19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D283" s="20" t="s">
         <v>18</v>
@@ -7105,7 +7105,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A284" s="18" t="s">
         <v>15</v>
       </c>
@@ -7113,7 +7113,7 @@
         <v>478</v>
       </c>
       <c r="C284" s="19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D284" s="20" t="s">
         <v>18</v>
@@ -7122,7 +7122,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A285" s="18" t="s">
         <v>15</v>
       </c>
@@ -7130,7 +7130,7 @@
         <v>478</v>
       </c>
       <c r="C285" s="19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D285" s="20" t="s">
         <v>18</v>
@@ -7147,7 +7147,7 @@
         <v>478</v>
       </c>
       <c r="C286" s="19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D286" s="20" t="s">
         <v>18</v>
@@ -7164,7 +7164,7 @@
         <v>478</v>
       </c>
       <c r="C287" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D287" s="20" t="s">
         <v>18</v>
@@ -7181,7 +7181,7 @@
         <v>478</v>
       </c>
       <c r="C288" s="19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D288" s="20" t="s">
         <v>18</v>
@@ -7198,7 +7198,7 @@
         <v>478</v>
       </c>
       <c r="C289" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D289" s="20" t="s">
         <v>18</v>
@@ -7215,7 +7215,7 @@
         <v>478</v>
       </c>
       <c r="C290" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D290" s="20" t="s">
         <v>18</v>
@@ -7232,7 +7232,7 @@
         <v>478</v>
       </c>
       <c r="C291" s="19" t="s">
-        <v>110</v>
+        <v>501</v>
       </c>
       <c r="D291" s="20" t="s">
         <v>18</v>
@@ -7249,7 +7249,7 @@
         <v>478</v>
       </c>
       <c r="C292" s="19" t="s">
-        <v>501</v>
+        <v>112</v>
       </c>
       <c r="D292" s="20" t="s">
         <v>18</v>
@@ -7266,7 +7266,7 @@
         <v>478</v>
       </c>
       <c r="C293" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D293" s="20" t="s">
         <v>18</v>
@@ -7283,7 +7283,7 @@
         <v>478</v>
       </c>
       <c r="C294" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D294" s="20" t="s">
         <v>18</v>
@@ -7300,7 +7300,7 @@
         <v>478</v>
       </c>
       <c r="C295" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D295" s="20" t="s">
         <v>18</v>
@@ -7317,7 +7317,7 @@
         <v>478</v>
       </c>
       <c r="C296" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D296" s="20" t="s">
         <v>18</v>
@@ -7334,7 +7334,7 @@
         <v>478</v>
       </c>
       <c r="C297" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D297" s="20" t="s">
         <v>18</v>
@@ -7351,7 +7351,7 @@
         <v>478</v>
       </c>
       <c r="C298" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D298" s="20" t="s">
         <v>18</v>
@@ -7368,7 +7368,7 @@
         <v>478</v>
       </c>
       <c r="C299" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D299" s="20" t="s">
         <v>18</v>
@@ -7385,7 +7385,7 @@
         <v>478</v>
       </c>
       <c r="C300" s="19" t="s">
-        <v>119</v>
+        <v>502</v>
       </c>
       <c r="D300" s="20" t="s">
         <v>18</v>
@@ -7394,7 +7394,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A301" s="18" t="s">
         <v>15</v>
       </c>
@@ -7402,7 +7402,7 @@
         <v>478</v>
       </c>
       <c r="C301" s="19" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D301" s="20" t="s">
         <v>18</v>
@@ -7411,7 +7411,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A302" s="18" t="s">
         <v>15</v>
       </c>
@@ -7419,7 +7419,7 @@
         <v>478</v>
       </c>
       <c r="C302" s="19" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D302" s="20" t="s">
         <v>18</v>
@@ -7436,7 +7436,7 @@
         <v>478</v>
       </c>
       <c r="C303" s="19" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D303" s="20" t="s">
         <v>18</v>
@@ -7453,7 +7453,7 @@
         <v>478</v>
       </c>
       <c r="C304" s="19" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D304" s="20" t="s">
         <v>18</v>
@@ -7470,7 +7470,7 @@
         <v>478</v>
       </c>
       <c r="C305" s="19" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D305" s="20" t="s">
         <v>18</v>
@@ -7487,7 +7487,7 @@
         <v>478</v>
       </c>
       <c r="C306" s="19" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D306" s="20" t="s">
         <v>18</v>
@@ -7504,7 +7504,7 @@
         <v>478</v>
       </c>
       <c r="C307" s="19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D307" s="20" t="s">
         <v>18</v>
@@ -7521,7 +7521,7 @@
         <v>478</v>
       </c>
       <c r="C308" s="19" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D308" s="20" t="s">
         <v>18</v>
@@ -7538,7 +7538,7 @@
         <v>478</v>
       </c>
       <c r="C309" s="19" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D309" s="20" t="s">
         <v>18</v>
@@ -7555,7 +7555,7 @@
         <v>478</v>
       </c>
       <c r="C310" s="19" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D310" s="20" t="s">
         <v>18</v>
@@ -7572,7 +7572,7 @@
         <v>478</v>
       </c>
       <c r="C311" s="19" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D311" s="20" t="s">
         <v>18</v>
@@ -7589,7 +7589,7 @@
         <v>478</v>
       </c>
       <c r="C312" s="19" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D312" s="20" t="s">
         <v>18</v>
@@ -7606,7 +7606,7 @@
         <v>478</v>
       </c>
       <c r="C313" s="19" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D313" s="20" t="s">
         <v>18</v>
@@ -7623,7 +7623,7 @@
         <v>478</v>
       </c>
       <c r="C314" s="19" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D314" s="20" t="s">
         <v>18</v>
@@ -7640,7 +7640,7 @@
         <v>478</v>
       </c>
       <c r="C315" s="19" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D315" s="20" t="s">
         <v>18</v>
@@ -7657,7 +7657,7 @@
         <v>478</v>
       </c>
       <c r="C316" s="19" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D316" s="20" t="s">
         <v>18</v>
@@ -7674,7 +7674,7 @@
         <v>478</v>
       </c>
       <c r="C317" s="19" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D317" s="20" t="s">
         <v>18</v>
@@ -7691,7 +7691,7 @@
         <v>478</v>
       </c>
       <c r="C318" s="19" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D318" s="20" t="s">
         <v>18</v>
@@ -7708,7 +7708,7 @@
         <v>478</v>
       </c>
       <c r="C319" s="19" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D319" s="20" t="s">
         <v>18</v>
@@ -7725,7 +7725,7 @@
         <v>478</v>
       </c>
       <c r="C320" s="19" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D320" s="20" t="s">
         <v>18</v>
@@ -7742,7 +7742,7 @@
         <v>478</v>
       </c>
       <c r="C321" s="19" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D321" s="20" t="s">
         <v>18</v>
@@ -7759,7 +7759,7 @@
         <v>478</v>
       </c>
       <c r="C322" s="19" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D322" s="20" t="s">
         <v>18</v>
@@ -7776,7 +7776,7 @@
         <v>478</v>
       </c>
       <c r="C323" s="19" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D323" s="20" t="s">
         <v>18</v>
@@ -7793,7 +7793,7 @@
         <v>478</v>
       </c>
       <c r="C324" s="19" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D324" s="20" t="s">
         <v>18</v>
@@ -7810,7 +7810,7 @@
         <v>478</v>
       </c>
       <c r="C325" s="19" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D325" s="20" t="s">
         <v>18</v>
@@ -7827,7 +7827,7 @@
         <v>478</v>
       </c>
       <c r="C326" s="19" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D326" s="20" t="s">
         <v>18</v>
@@ -7837,37 +7837,38 @@
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A327" s="18" t="s">
-        <v>15</v>
+      <c r="A327" s="24" t="s">
+        <v>499</v>
       </c>
       <c r="B327" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C327" s="19" t="s">
-        <v>528</v>
-      </c>
-      <c r="D327" s="20" t="s">
-        <v>18</v>
+      <c r="C327" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D327" s="25" t="s">
+        <v>8</v>
       </c>
       <c r="E327" s="21">
-        <v>306.2</v>
+        <v>8.7617627530354198</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A328" s="24" t="s">
-        <v>499</v>
+        <v>461</v>
       </c>
       <c r="B328" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C328" s="22" t="s">
-        <v>7</v>
+      <c r="C328" s="23" t="s">
+        <v>9</v>
       </c>
       <c r="D328" s="25" t="s">
         <v>8</v>
       </c>
       <c r="E328" s="21">
-        <v>8.7617627530354198</v>
+        <f>1.83271287591511+0.699355765772355+23.6965393660799</f>
+        <v>26.228608007767363</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.4">
@@ -7878,87 +7879,87 @@
         <v>478</v>
       </c>
       <c r="C329" s="23" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D329" s="25" t="s">
         <v>8</v>
       </c>
       <c r="E329" s="21">
+        <f>0.794035881175228+0.259790348838566+6.53631669485161+8.71621621621622</f>
+        <v>16.306359141081622</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A330" s="51" t="s">
+        <v>499</v>
+      </c>
+      <c r="B330" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C330" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D330" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="E330" s="54">
+        <f>9.31371545207318</f>
+        <v>9.3137154520731809</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A331" s="64" t="s">
+        <v>499</v>
+      </c>
+      <c r="B331" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C331" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="D331" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E331" s="21">
+        <v>8.7617627530354198</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A332" s="65" t="s">
+        <v>499</v>
+      </c>
+      <c r="B332" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C332" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="D332" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E332" s="21">
+        <f>9.31371545207318</f>
+        <v>9.3137154520731809</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A333" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="B333" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C333" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="D333" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E333" s="21">
         <f>1.83271287591511+0.699355765772355+23.6965393660799</f>
         <v>26.228608007767363</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A330" s="24" t="s">
-        <v>461</v>
-      </c>
-      <c r="B330" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C330" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D330" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E330" s="21">
-        <f>0.794035881175228+0.259790348838566+6.53631669485161+8.71621621621622</f>
-        <v>16.306359141081622</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A331" s="51" t="s">
-        <v>499</v>
-      </c>
-      <c r="B331" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C331" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="D331" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="E331" s="54">
-        <f>9.31371545207318</f>
-        <v>9.3137154520731809</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A332" s="64" t="s">
-        <v>499</v>
-      </c>
-      <c r="B332" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C332" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="D332" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E332" s="21">
-        <v>8.7617627530354198</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A333" s="65" t="s">
-        <v>499</v>
-      </c>
-      <c r="B333" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C333" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D333" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E333" s="21">
-        <f>9.31371545207318</f>
-        <v>9.3137154520731809</v>
-      </c>
-    </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A334" s="24" t="s">
         <v>461</v>
@@ -7967,7 +7968,7 @@
         <v>478</v>
       </c>
       <c r="C334" s="23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D334" s="25" t="s">
         <v>8</v>
@@ -7981,11 +7982,11 @@
       <c r="A335" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B335" s="19" t="s">
+      <c r="B335" s="66" t="s">
         <v>478</v>
       </c>
       <c r="C335" s="23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D335" s="25" t="s">
         <v>8</v>
@@ -7999,18 +8000,18 @@
       <c r="A336" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="B336" s="66" t="s">
+      <c r="B336" s="19" t="s">
         <v>478</v>
       </c>
       <c r="C336" s="23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D336" s="25" t="s">
         <v>8</v>
       </c>
       <c r="E336" s="21">
-        <f>1.83271287591511+0.699355765772355+23.6965393660799</f>
-        <v>26.228608007767363</v>
+        <f t="shared" ref="E336" si="1">0.794035881175228+0.259790348838566+6.53631669485161+8.71621621621622</f>
+        <v>16.306359141081622</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.4">
@@ -8020,15 +8021,14 @@
       <c r="B337" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C337" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="D337" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E337" s="21">
-        <f t="shared" ref="E337" si="1">0.794035881175228+0.259790348838566+6.53631669485161+8.71621621621622</f>
-        <v>16.306359141081622</v>
+      <c r="C337" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="D337" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E337" s="24">
+        <v>0.47448299012375972</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.4">
@@ -8039,7 +8039,7 @@
         <v>478</v>
       </c>
       <c r="C338" s="24" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D338" s="24" t="s">
         <v>8</v>
@@ -8056,7 +8056,7 @@
         <v>478</v>
       </c>
       <c r="C339" s="24" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D339" s="24" t="s">
         <v>8</v>
@@ -8073,7 +8073,7 @@
         <v>478</v>
       </c>
       <c r="C340" s="24" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D340" s="24" t="s">
         <v>8</v>
@@ -8090,7 +8090,7 @@
         <v>478</v>
       </c>
       <c r="C341" s="24" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D341" s="24" t="s">
         <v>8</v>
@@ -8107,7 +8107,7 @@
         <v>478</v>
       </c>
       <c r="C342" s="24" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D342" s="24" t="s">
         <v>8</v>
@@ -8124,7 +8124,7 @@
         <v>478</v>
       </c>
       <c r="C343" s="24" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D343" s="24" t="s">
         <v>8</v>
@@ -8141,7 +8141,7 @@
         <v>478</v>
       </c>
       <c r="C344" s="24" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D344" s="24" t="s">
         <v>8</v>
@@ -8158,7 +8158,7 @@
         <v>478</v>
       </c>
       <c r="C345" s="24" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D345" s="24" t="s">
         <v>8</v>
@@ -8175,13 +8175,13 @@
         <v>478</v>
       </c>
       <c r="C346" s="24" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D346" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E346" s="24">
-        <v>0.47448299012375972</v>
+        <v>7.0137417235817956E-2</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.4">
@@ -8192,7 +8192,7 @@
         <v>478</v>
       </c>
       <c r="C347" s="24" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D347" s="24" t="s">
         <v>8</v>
@@ -8209,7 +8209,7 @@
         <v>478</v>
       </c>
       <c r="C348" s="24" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D348" s="24" t="s">
         <v>8</v>
@@ -8226,7 +8226,7 @@
         <v>478</v>
       </c>
       <c r="C349" s="24" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D349" s="24" t="s">
         <v>8</v>
@@ -8243,13 +8243,13 @@
         <v>478</v>
       </c>
       <c r="C350" s="24" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="D350" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E350" s="24">
-        <v>7.0137417235817956E-2</v>
+        <v>3.3662903906841443E-2</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.4">
@@ -8260,7 +8260,7 @@
         <v>478</v>
       </c>
       <c r="C351" s="24" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D351" s="24" t="s">
         <v>8</v>
@@ -8277,7 +8277,7 @@
         <v>478</v>
       </c>
       <c r="C352" s="24" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D352" s="24" t="s">
         <v>8</v>
@@ -8294,7 +8294,7 @@
         <v>478</v>
       </c>
       <c r="C353" s="24" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D353" s="24" t="s">
         <v>8</v>
@@ -8311,7 +8311,7 @@
         <v>478</v>
       </c>
       <c r="C354" s="24" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D354" s="24" t="s">
         <v>8</v>
@@ -8328,7 +8328,7 @@
         <v>478</v>
       </c>
       <c r="C355" s="24" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D355" s="24" t="s">
         <v>8</v>
@@ -8337,7 +8337,7 @@
         <v>3.3662903906841443E-2</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A356" s="24" t="s">
         <v>461</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>478</v>
       </c>
       <c r="C356" s="24" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D356" s="24" t="s">
         <v>8</v>
@@ -8354,7 +8354,7 @@
         <v>3.3662903906841443E-2</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A357" s="24" t="s">
         <v>461</v>
       </c>
@@ -8362,7 +8362,7 @@
         <v>478</v>
       </c>
       <c r="C357" s="24" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D357" s="24" t="s">
         <v>8</v>
@@ -8379,7 +8379,7 @@
         <v>478</v>
       </c>
       <c r="C358" s="24" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D358" s="24" t="s">
         <v>8</v>
@@ -8396,7 +8396,7 @@
         <v>478</v>
       </c>
       <c r="C359" s="24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D359" s="24" t="s">
         <v>8</v>
@@ -8413,7 +8413,7 @@
         <v>478</v>
       </c>
       <c r="C360" s="24" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D360" s="24" t="s">
         <v>8</v>
@@ -8430,7 +8430,7 @@
         <v>478</v>
       </c>
       <c r="C361" s="24" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D361" s="24" t="s">
         <v>8</v>
@@ -8447,7 +8447,7 @@
         <v>478</v>
       </c>
       <c r="C362" s="24" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D362" s="24" t="s">
         <v>8</v>
@@ -8464,7 +8464,7 @@
         <v>478</v>
       </c>
       <c r="C363" s="24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D363" s="24" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>478</v>
       </c>
       <c r="C364" s="24" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D364" s="24" t="s">
         <v>8</v>
@@ -8498,7 +8498,7 @@
         <v>478</v>
       </c>
       <c r="C365" s="24" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D365" s="24" t="s">
         <v>8</v>
@@ -8515,7 +8515,7 @@
         <v>478</v>
       </c>
       <c r="C366" s="24" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D366" s="24" t="s">
         <v>8</v>
@@ -8532,7 +8532,7 @@
         <v>478</v>
       </c>
       <c r="C367" s="24" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D367" s="24" t="s">
         <v>8</v>
@@ -8549,7 +8549,7 @@
         <v>478</v>
       </c>
       <c r="C368" s="24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D368" s="24" t="s">
         <v>8</v>
@@ -8566,13 +8566,13 @@
         <v>478</v>
       </c>
       <c r="C369" s="24" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D369" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E369" s="24">
-        <v>3.3662903906841443E-2</v>
+        <v>185.69758349435509</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.4">
@@ -8583,7 +8583,7 @@
         <v>478</v>
       </c>
       <c r="C370" s="24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D370" s="24" t="s">
         <v>8</v>
@@ -8600,7 +8600,7 @@
         <v>478</v>
       </c>
       <c r="C371" s="24" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D371" s="24" t="s">
         <v>8</v>
@@ -8617,7 +8617,7 @@
         <v>478</v>
       </c>
       <c r="C372" s="24" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D372" s="24" t="s">
         <v>8</v>
@@ -8634,7 +8634,7 @@
         <v>478</v>
       </c>
       <c r="C373" s="24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D373" s="24" t="s">
         <v>8</v>
@@ -8651,7 +8651,7 @@
         <v>478</v>
       </c>
       <c r="C374" s="24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D374" s="24" t="s">
         <v>8</v>
@@ -8668,7 +8668,7 @@
         <v>478</v>
       </c>
       <c r="C375" s="24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D375" s="24" t="s">
         <v>8</v>
@@ -8685,7 +8685,7 @@
         <v>478</v>
       </c>
       <c r="C376" s="24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D376" s="24" t="s">
         <v>8</v>
@@ -8702,7 +8702,7 @@
         <v>478</v>
       </c>
       <c r="C377" s="24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D377" s="24" t="s">
         <v>8</v>
@@ -8719,7 +8719,7 @@
         <v>478</v>
       </c>
       <c r="C378" s="24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D378" s="24" t="s">
         <v>8</v>
@@ -8736,7 +8736,7 @@
         <v>478</v>
       </c>
       <c r="C379" s="24" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D379" s="24" t="s">
         <v>8</v>
@@ -8753,7 +8753,7 @@
         <v>478</v>
       </c>
       <c r="C380" s="24" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D380" s="24" t="s">
         <v>8</v>
@@ -8770,7 +8770,7 @@
         <v>478</v>
       </c>
       <c r="C381" s="24" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D381" s="24" t="s">
         <v>8</v>
@@ -8787,7 +8787,7 @@
         <v>478</v>
       </c>
       <c r="C382" s="24" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D382" s="24" t="s">
         <v>8</v>
@@ -8804,13 +8804,13 @@
         <v>478</v>
       </c>
       <c r="C383" s="24" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D383" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E383" s="24">
-        <v>185.69758349435509</v>
+        <v>3047.4121773829488</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.4">
@@ -8821,7 +8821,7 @@
         <v>478</v>
       </c>
       <c r="C384" s="24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D384" s="24" t="s">
         <v>8</v>
@@ -8838,7 +8838,7 @@
         <v>478</v>
       </c>
       <c r="C385" s="24" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D385" s="24" t="s">
         <v>8</v>
@@ -8855,7 +8855,7 @@
         <v>478</v>
       </c>
       <c r="C386" s="24" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D386" s="24" t="s">
         <v>8</v>
@@ -8872,7 +8872,7 @@
         <v>478</v>
       </c>
       <c r="C387" s="24" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D387" s="24" t="s">
         <v>8</v>
@@ -8889,7 +8889,7 @@
         <v>478</v>
       </c>
       <c r="C388" s="24" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D388" s="24" t="s">
         <v>8</v>
@@ -8906,7 +8906,7 @@
         <v>478</v>
       </c>
       <c r="C389" s="24" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D389" s="24" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>478</v>
       </c>
       <c r="C390" s="24" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D390" s="24" t="s">
         <v>8</v>
@@ -8940,13 +8940,13 @@
         <v>478</v>
       </c>
       <c r="C391" s="24" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D391" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E391" s="24">
-        <v>3047.4121773829488</v>
+        <v>3528.885850254635</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.4">
@@ -8957,7 +8957,7 @@
         <v>478</v>
       </c>
       <c r="C392" s="24" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D392" s="24" t="s">
         <v>8</v>
@@ -8974,7 +8974,7 @@
         <v>478</v>
       </c>
       <c r="C393" s="24" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D393" s="24" t="s">
         <v>8</v>
@@ -8991,7 +8991,7 @@
         <v>478</v>
       </c>
       <c r="C394" s="24" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D394" s="24" t="s">
         <v>8</v>
@@ -9008,7 +9008,7 @@
         <v>478</v>
       </c>
       <c r="C395" s="24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D395" s="24" t="s">
         <v>8</v>
@@ -9025,7 +9025,7 @@
         <v>478</v>
       </c>
       <c r="C396" s="24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D396" s="24" t="s">
         <v>8</v>
@@ -9042,7 +9042,7 @@
         <v>478</v>
       </c>
       <c r="C397" s="24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D397" s="24" t="s">
         <v>8</v>
@@ -9059,7 +9059,7 @@
         <v>478</v>
       </c>
       <c r="C398" s="24" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D398" s="24" t="s">
         <v>8</v>
@@ -9076,13 +9076,13 @@
         <v>478</v>
       </c>
       <c r="C399" s="24" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D399" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E399" s="24">
-        <v>3528.885850254635</v>
+        <v>0.29887053900547389</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.4">
@@ -9093,7 +9093,7 @@
         <v>478</v>
       </c>
       <c r="C400" s="24" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D400" s="24" t="s">
         <v>8</v>
@@ -9110,7 +9110,7 @@
         <v>478</v>
       </c>
       <c r="C401" s="24" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D401" s="24" t="s">
         <v>8</v>
@@ -9127,7 +9127,7 @@
         <v>478</v>
       </c>
       <c r="C402" s="24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D402" s="24" t="s">
         <v>8</v>
@@ -9144,13 +9144,13 @@
         <v>478</v>
       </c>
       <c r="C403" s="24" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D403" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E403" s="24">
-        <v>0.29887053900547389</v>
+        <v>5.1888755947493877E-3</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.4">
@@ -9161,7 +9161,7 @@
         <v>478</v>
       </c>
       <c r="C404" s="24" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D404" s="24" t="s">
         <v>8</v>
@@ -9178,7 +9178,7 @@
         <v>478</v>
       </c>
       <c r="C405" s="24" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D405" s="24" t="s">
         <v>8</v>
@@ -9195,7 +9195,7 @@
         <v>478</v>
       </c>
       <c r="C406" s="24" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D406" s="24" t="s">
         <v>8</v>
@@ -9212,7 +9212,7 @@
         <v>478</v>
       </c>
       <c r="C407" s="24" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D407" s="24" t="s">
         <v>8</v>
@@ -9229,7 +9229,7 @@
         <v>478</v>
       </c>
       <c r="C408" s="24" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D408" s="24" t="s">
         <v>8</v>
@@ -9246,7 +9246,7 @@
         <v>478</v>
       </c>
       <c r="C409" s="24" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D409" s="24" t="s">
         <v>8</v>
@@ -9263,7 +9263,7 @@
         <v>478</v>
       </c>
       <c r="C410" s="24" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D410" s="24" t="s">
         <v>8</v>
@@ -9280,7 +9280,7 @@
         <v>478</v>
       </c>
       <c r="C411" s="24" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D411" s="24" t="s">
         <v>8</v>
@@ -9297,7 +9297,7 @@
         <v>478</v>
       </c>
       <c r="C412" s="24" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D412" s="24" t="s">
         <v>8</v>
@@ -9314,7 +9314,7 @@
         <v>478</v>
       </c>
       <c r="C413" s="24" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D413" s="24" t="s">
         <v>8</v>
@@ -9331,7 +9331,7 @@
         <v>478</v>
       </c>
       <c r="C414" s="24" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D414" s="24" t="s">
         <v>8</v>
@@ -9348,7 +9348,7 @@
         <v>478</v>
       </c>
       <c r="C415" s="24" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D415" s="24" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>478</v>
       </c>
       <c r="C416" s="24" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D416" s="24" t="s">
         <v>8</v>
@@ -9382,13 +9382,13 @@
         <v>478</v>
       </c>
       <c r="C417" s="24" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D417" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E417" s="24">
-        <v>5.1888755947493877E-3</v>
+        <v>2.5277027027027019</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.4">
@@ -9399,7 +9399,7 @@
         <v>478</v>
       </c>
       <c r="C418" s="24" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D418" s="24" t="s">
         <v>8</v>
@@ -9416,7 +9416,7 @@
         <v>478</v>
       </c>
       <c r="C419" s="24" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D419" s="24" t="s">
         <v>8</v>
@@ -9433,7 +9433,7 @@
         <v>478</v>
       </c>
       <c r="C420" s="24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D420" s="24" t="s">
         <v>8</v>
@@ -9450,7 +9450,7 @@
         <v>478</v>
       </c>
       <c r="C421" s="24" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D421" s="24" t="s">
         <v>8</v>
@@ -9459,7 +9459,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A422" s="24" t="s">
         <v>461</v>
       </c>
@@ -9467,7 +9467,7 @@
         <v>478</v>
       </c>
       <c r="C422" s="24" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D422" s="24" t="s">
         <v>8</v>
@@ -9484,7 +9484,7 @@
         <v>478</v>
       </c>
       <c r="C423" s="24" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D423" s="24" t="s">
         <v>8</v>
@@ -9493,7 +9493,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A424" s="24" t="s">
         <v>461</v>
       </c>
@@ -9501,7 +9501,7 @@
         <v>478</v>
       </c>
       <c r="C424" s="24" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D424" s="24" t="s">
         <v>8</v>
@@ -9518,7 +9518,7 @@
         <v>478</v>
       </c>
       <c r="C425" s="24" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D425" s="24" t="s">
         <v>8</v>
@@ -9535,7 +9535,7 @@
         <v>478</v>
       </c>
       <c r="C426" s="24" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D426" s="24" t="s">
         <v>8</v>
@@ -9552,7 +9552,7 @@
         <v>478</v>
       </c>
       <c r="C427" s="24" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D427" s="24" t="s">
         <v>8</v>
@@ -9569,7 +9569,7 @@
         <v>478</v>
       </c>
       <c r="C428" s="24" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D428" s="24" t="s">
         <v>8</v>
@@ -9586,7 +9586,7 @@
         <v>478</v>
       </c>
       <c r="C429" s="24" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D429" s="24" t="s">
         <v>8</v>
@@ -9595,7 +9595,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A430" s="24" t="s">
         <v>461</v>
       </c>
@@ -9603,7 +9603,7 @@
         <v>478</v>
       </c>
       <c r="C430" s="24" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D430" s="24" t="s">
         <v>8</v>
@@ -9620,7 +9620,7 @@
         <v>478</v>
       </c>
       <c r="C431" s="24" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D431" s="24" t="s">
         <v>8</v>
@@ -9629,7 +9629,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A432" s="24" t="s">
         <v>461</v>
       </c>
@@ -9637,7 +9637,7 @@
         <v>478</v>
       </c>
       <c r="C432" s="24" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D432" s="24" t="s">
         <v>8</v>
@@ -9654,7 +9654,7 @@
         <v>478</v>
       </c>
       <c r="C433" s="24" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D433" s="24" t="s">
         <v>8</v>
@@ -9671,7 +9671,7 @@
         <v>478</v>
       </c>
       <c r="C434" s="24" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D434" s="24" t="s">
         <v>8</v>
@@ -9680,7 +9680,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A435" s="24" t="s">
         <v>461</v>
       </c>
@@ -9688,7 +9688,7 @@
         <v>478</v>
       </c>
       <c r="C435" s="24" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D435" s="24" t="s">
         <v>8</v>
@@ -9705,7 +9705,7 @@
         <v>478</v>
       </c>
       <c r="C436" s="24" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D436" s="24" t="s">
         <v>8</v>
@@ -9722,7 +9722,7 @@
         <v>478</v>
       </c>
       <c r="C437" s="24" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D437" s="24" t="s">
         <v>8</v>
@@ -9739,7 +9739,7 @@
         <v>478</v>
       </c>
       <c r="C438" s="24" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D438" s="24" t="s">
         <v>8</v>
@@ -9756,7 +9756,7 @@
         <v>478</v>
       </c>
       <c r="C439" s="24" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D439" s="24" t="s">
         <v>8</v>
@@ -9773,7 +9773,7 @@
         <v>478</v>
       </c>
       <c r="C440" s="24" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D440" s="24" t="s">
         <v>8</v>
@@ -9782,7 +9782,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A441" s="24" t="s">
         <v>461</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>478</v>
       </c>
       <c r="C441" s="24" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D441" s="24" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>478</v>
       </c>
       <c r="C442" s="24" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D442" s="24" t="s">
         <v>8</v>
@@ -9824,7 +9824,7 @@
         <v>478</v>
       </c>
       <c r="C443" s="24" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D443" s="24" t="s">
         <v>8</v>
@@ -9841,7 +9841,7 @@
         <v>478</v>
       </c>
       <c r="C444" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D444" s="24" t="s">
         <v>8</v>
@@ -9858,7 +9858,7 @@
         <v>478</v>
       </c>
       <c r="C445" s="24" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D445" s="24" t="s">
         <v>8</v>
@@ -9875,7 +9875,7 @@
         <v>478</v>
       </c>
       <c r="C446" s="24" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D446" s="24" t="s">
         <v>8</v>
@@ -9892,7 +9892,7 @@
         <v>478</v>
       </c>
       <c r="C447" s="24" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D447" s="24" t="s">
         <v>8</v>
@@ -9909,7 +9909,7 @@
         <v>478</v>
       </c>
       <c r="C448" s="24" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D448" s="24" t="s">
         <v>8</v>
@@ -9926,7 +9926,7 @@
         <v>478</v>
       </c>
       <c r="C449" s="24" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D449" s="24" t="s">
         <v>8</v>
@@ -9943,7 +9943,7 @@
         <v>478</v>
       </c>
       <c r="C450" s="24" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D450" s="24" t="s">
         <v>8</v>
@@ -9960,7 +9960,7 @@
         <v>478</v>
       </c>
       <c r="C451" s="24" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D451" s="24" t="s">
         <v>8</v>
@@ -9969,7 +9969,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A452" s="24" t="s">
         <v>461</v>
       </c>
@@ -9977,7 +9977,7 @@
         <v>478</v>
       </c>
       <c r="C452" s="24" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D452" s="24" t="s">
         <v>8</v>
@@ -9986,7 +9986,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A453" s="24" t="s">
         <v>461</v>
       </c>
@@ -9994,7 +9994,7 @@
         <v>478</v>
       </c>
       <c r="C453" s="24" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D453" s="24" t="s">
         <v>8</v>
@@ -10011,7 +10011,7 @@
         <v>478</v>
       </c>
       <c r="C454" s="24" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D454" s="24" t="s">
         <v>8</v>
@@ -10028,7 +10028,7 @@
         <v>478</v>
       </c>
       <c r="C455" s="24" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D455" s="24" t="s">
         <v>8</v>
@@ -10045,7 +10045,7 @@
         <v>478</v>
       </c>
       <c r="C456" s="24" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D456" s="24" t="s">
         <v>8</v>
@@ -10062,7 +10062,7 @@
         <v>478</v>
       </c>
       <c r="C457" s="24" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D457" s="24" t="s">
         <v>8</v>
@@ -10079,7 +10079,7 @@
         <v>478</v>
       </c>
       <c r="C458" s="24" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D458" s="24" t="s">
         <v>8</v>
@@ -10096,7 +10096,7 @@
         <v>478</v>
       </c>
       <c r="C459" s="24" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D459" s="24" t="s">
         <v>8</v>
@@ -10113,7 +10113,7 @@
         <v>478</v>
       </c>
       <c r="C460" s="24" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D460" s="24" t="s">
         <v>8</v>
@@ -10130,7 +10130,7 @@
         <v>478</v>
       </c>
       <c r="C461" s="24" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D461" s="24" t="s">
         <v>8</v>
@@ -10147,7 +10147,7 @@
         <v>478</v>
       </c>
       <c r="C462" s="24" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D462" s="24" t="s">
         <v>8</v>
@@ -10164,7 +10164,7 @@
         <v>478</v>
       </c>
       <c r="C463" s="24" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D463" s="24" t="s">
         <v>8</v>
@@ -10181,7 +10181,7 @@
         <v>478</v>
       </c>
       <c r="C464" s="24" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D464" s="24" t="s">
         <v>8</v>
@@ -10198,13 +10198,13 @@
         <v>478</v>
       </c>
       <c r="C465" s="24" t="s">
-        <v>357</v>
+        <v>168</v>
       </c>
       <c r="D465" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E465" s="24">
-        <v>2.5277027027027019</v>
+        <v>16.306359141081622</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.4">
@@ -10215,7 +10215,7 @@
         <v>478</v>
       </c>
       <c r="C466" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D466" s="24" t="s">
         <v>8</v>
@@ -10232,7 +10232,7 @@
         <v>478</v>
       </c>
       <c r="C467" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D467" s="24" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>478</v>
       </c>
       <c r="C468" s="24" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D468" s="24" t="s">
         <v>8</v>
@@ -10266,7 +10266,7 @@
         <v>478</v>
       </c>
       <c r="C469" s="24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D469" s="24" t="s">
         <v>8</v>
@@ -10283,7 +10283,7 @@
         <v>478</v>
       </c>
       <c r="C470" s="24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D470" s="24" t="s">
         <v>8</v>
@@ -10292,7 +10292,7 @@
         <v>16.306359141081622</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A471" s="24" t="s">
         <v>461</v>
       </c>
@@ -10300,7 +10300,7 @@
         <v>478</v>
       </c>
       <c r="C471" s="24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D471" s="24" t="s">
         <v>8</v>
@@ -10317,7 +10317,7 @@
         <v>478</v>
       </c>
       <c r="C472" s="24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D472" s="24" t="s">
         <v>8</v>
@@ -10326,7 +10326,7 @@
         <v>16.306359141081622</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A473" s="24" t="s">
         <v>461</v>
       </c>
@@ -10334,7 +10334,7 @@
         <v>478</v>
       </c>
       <c r="C473" s="24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D473" s="24" t="s">
         <v>8</v>
@@ -10351,7 +10351,7 @@
         <v>478</v>
       </c>
       <c r="C474" s="24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D474" s="24" t="s">
         <v>8</v>
@@ -10368,7 +10368,7 @@
         <v>478</v>
       </c>
       <c r="C475" s="24" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D475" s="24" t="s">
         <v>8</v>
@@ -10385,7 +10385,7 @@
         <v>478</v>
       </c>
       <c r="C476" s="24" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D476" s="24" t="s">
         <v>8</v>
@@ -10402,7 +10402,7 @@
         <v>478</v>
       </c>
       <c r="C477" s="24" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D477" s="24" t="s">
         <v>8</v>
@@ -10419,7 +10419,7 @@
         <v>478</v>
       </c>
       <c r="C478" s="24" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D478" s="24" t="s">
         <v>8</v>
@@ -10436,7 +10436,7 @@
         <v>478</v>
       </c>
       <c r="C479" s="24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D479" s="24" t="s">
         <v>8</v>
@@ -10453,7 +10453,7 @@
         <v>478</v>
       </c>
       <c r="C480" s="24" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D480" s="24" t="s">
         <v>8</v>
@@ -10470,7 +10470,7 @@
         <v>478</v>
       </c>
       <c r="C481" s="24" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D481" s="24" t="s">
         <v>8</v>
@@ -10487,7 +10487,7 @@
         <v>478</v>
       </c>
       <c r="C482" s="24" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D482" s="24" t="s">
         <v>8</v>
@@ -10504,7 +10504,7 @@
         <v>478</v>
       </c>
       <c r="C483" s="24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D483" s="24" t="s">
         <v>8</v>
@@ -10521,7 +10521,7 @@
         <v>478</v>
       </c>
       <c r="C484" s="24" t="s">
-        <v>186</v>
+        <v>358</v>
       </c>
       <c r="D484" s="24" t="s">
         <v>8</v>
@@ -10538,7 +10538,7 @@
         <v>478</v>
       </c>
       <c r="C485" s="24" t="s">
-        <v>358</v>
+        <v>187</v>
       </c>
       <c r="D485" s="24" t="s">
         <v>8</v>
@@ -10555,7 +10555,7 @@
         <v>478</v>
       </c>
       <c r="C486" s="24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D486" s="24" t="s">
         <v>8</v>
@@ -10572,7 +10572,7 @@
         <v>478</v>
       </c>
       <c r="C487" s="24" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D487" s="24" t="s">
         <v>8</v>
@@ -10589,13 +10589,13 @@
         <v>478</v>
       </c>
       <c r="C488" s="24" t="s">
-        <v>189</v>
+        <v>359</v>
       </c>
       <c r="D488" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E488" s="24">
-        <v>16.306359141081622</v>
+        <v>16.639550829227119</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.4">
@@ -10606,7 +10606,7 @@
         <v>478</v>
       </c>
       <c r="C489" s="24" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D489" s="24" t="s">
         <v>8</v>
@@ -10623,7 +10623,7 @@
         <v>478</v>
       </c>
       <c r="C490" s="24" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D490" s="24" t="s">
         <v>8</v>
@@ -10640,7 +10640,7 @@
         <v>478</v>
       </c>
       <c r="C491" s="24" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D491" s="24" t="s">
         <v>8</v>
@@ -10657,7 +10657,7 @@
         <v>478</v>
       </c>
       <c r="C492" s="24" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D492" s="24" t="s">
         <v>8</v>
@@ -10674,7 +10674,7 @@
         <v>478</v>
       </c>
       <c r="C493" s="24" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D493" s="24" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>478</v>
       </c>
       <c r="C494" s="24" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D494" s="24" t="s">
         <v>8</v>
@@ -10708,7 +10708,7 @@
         <v>478</v>
       </c>
       <c r="C495" s="24" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D495" s="24" t="s">
         <v>8</v>
@@ -10725,7 +10725,7 @@
         <v>478</v>
       </c>
       <c r="C496" s="24" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D496" s="24" t="s">
         <v>8</v>
@@ -10742,13 +10742,13 @@
         <v>478</v>
       </c>
       <c r="C497" s="24" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D497" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E497" s="24">
-        <v>16.639550829227119</v>
+        <v>2.2923648648648651</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.4">
@@ -10759,7 +10759,7 @@
         <v>478</v>
       </c>
       <c r="C498" s="24" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D498" s="24" t="s">
         <v>8</v>
@@ -10776,7 +10776,7 @@
         <v>478</v>
       </c>
       <c r="C499" s="24" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D499" s="24" t="s">
         <v>8</v>
@@ -10793,7 +10793,7 @@
         <v>478</v>
       </c>
       <c r="C500" s="24" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D500" s="24" t="s">
         <v>8</v>
@@ -10810,7 +10810,7 @@
         <v>478</v>
       </c>
       <c r="C501" s="24" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D501" s="24" t="s">
         <v>8</v>
@@ -10827,7 +10827,7 @@
         <v>478</v>
       </c>
       <c r="C502" s="24" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D502" s="24" t="s">
         <v>8</v>
@@ -10844,7 +10844,7 @@
         <v>478</v>
       </c>
       <c r="C503" s="24" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D503" s="24" t="s">
         <v>8</v>
@@ -10861,13 +10861,13 @@
         <v>478</v>
       </c>
       <c r="C504" s="24" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D504" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E504" s="24">
-        <v>2.2923648648648651</v>
+        <v>8.6578351118679522E-2</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.4">
@@ -10878,7 +10878,7 @@
         <v>478</v>
       </c>
       <c r="C505" s="24" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D505" s="24" t="s">
         <v>8</v>
@@ -10895,7 +10895,7 @@
         <v>478</v>
       </c>
       <c r="C506" s="24" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D506" s="24" t="s">
         <v>8</v>
@@ -10912,7 +10912,7 @@
         <v>478</v>
       </c>
       <c r="C507" s="24" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D507" s="24" t="s">
         <v>8</v>
@@ -10929,7 +10929,7 @@
         <v>478</v>
       </c>
       <c r="C508" s="24" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D508" s="24" t="s">
         <v>8</v>
@@ -10946,7 +10946,7 @@
         <v>478</v>
       </c>
       <c r="C509" s="24" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D509" s="24" t="s">
         <v>8</v>
@@ -10963,13 +10963,13 @@
         <v>478</v>
       </c>
       <c r="C510" s="24" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D510" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E510" s="24">
-        <v>8.6578351118679522E-2</v>
+        <v>50.022439716030298</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.4">
@@ -10980,7 +10980,7 @@
         <v>478</v>
       </c>
       <c r="C511" s="24" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D511" s="24" t="s">
         <v>8</v>
@@ -10997,7 +10997,7 @@
         <v>478</v>
       </c>
       <c r="C512" s="24" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D512" s="24" t="s">
         <v>8</v>
@@ -11014,7 +11014,7 @@
         <v>478</v>
       </c>
       <c r="C513" s="24" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D513" s="24" t="s">
         <v>8</v>
@@ -11031,7 +11031,7 @@
         <v>478</v>
       </c>
       <c r="C514" s="24" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D514" s="24" t="s">
         <v>8</v>
@@ -11048,7 +11048,7 @@
         <v>478</v>
       </c>
       <c r="C515" s="24" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D515" s="24" t="s">
         <v>8</v>
@@ -11065,7 +11065,7 @@
         <v>478</v>
       </c>
       <c r="C516" s="24" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D516" s="24" t="s">
         <v>8</v>
@@ -11082,13 +11082,13 @@
         <v>478</v>
       </c>
       <c r="C517" s="24" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D517" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E517" s="24">
-        <v>50.022439716030298</v>
+        <v>5.7228812061140499E-2</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.4">
@@ -11099,7 +11099,7 @@
         <v>478</v>
       </c>
       <c r="C518" s="24" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D518" s="24" t="s">
         <v>8</v>
@@ -11116,7 +11116,7 @@
         <v>478</v>
       </c>
       <c r="C519" s="24" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D519" s="24" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>478</v>
       </c>
       <c r="C520" s="24" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D520" s="24" t="s">
         <v>8</v>
@@ -11150,7 +11150,7 @@
         <v>478</v>
       </c>
       <c r="C521" s="24" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D521" s="24" t="s">
         <v>8</v>
@@ -11167,7 +11167,7 @@
         <v>478</v>
       </c>
       <c r="C522" s="24" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D522" s="24" t="s">
         <v>8</v>
@@ -11184,7 +11184,7 @@
         <v>478</v>
       </c>
       <c r="C523" s="24" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D523" s="24" t="s">
         <v>8</v>
@@ -11201,7 +11201,7 @@
         <v>478</v>
       </c>
       <c r="C524" s="24" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D524" s="24" t="s">
         <v>8</v>
@@ -11218,7 +11218,7 @@
         <v>478</v>
       </c>
       <c r="C525" s="24" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D525" s="24" t="s">
         <v>8</v>
@@ -11235,7 +11235,7 @@
         <v>478</v>
       </c>
       <c r="C526" s="24" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D526" s="24" t="s">
         <v>8</v>
@@ -11252,7 +11252,7 @@
         <v>478</v>
       </c>
       <c r="C527" s="24" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D527" s="24" t="s">
         <v>8</v>
@@ -11269,7 +11269,7 @@
         <v>478</v>
       </c>
       <c r="C528" s="24" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D528" s="24" t="s">
         <v>8</v>
@@ -11286,7 +11286,7 @@
         <v>478</v>
       </c>
       <c r="C529" s="24" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D529" s="24" t="s">
         <v>8</v>
@@ -11303,7 +11303,7 @@
         <v>478</v>
       </c>
       <c r="C530" s="24" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D530" s="24" t="s">
         <v>8</v>
@@ -11320,7 +11320,7 @@
         <v>478</v>
       </c>
       <c r="C531" s="24" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D531" s="24" t="s">
         <v>8</v>
@@ -11337,13 +11337,13 @@
         <v>478</v>
       </c>
       <c r="C532" s="24" t="s">
-        <v>403</v>
+        <v>190</v>
       </c>
       <c r="D532" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E532" s="24">
-        <v>5.7228812061140499E-2</v>
+        <v>16.620052075727429</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.4">
@@ -11354,7 +11354,7 @@
         <v>478</v>
       </c>
       <c r="C533" s="24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D533" s="24" t="s">
         <v>8</v>
@@ -11371,7 +11371,7 @@
         <v>478</v>
       </c>
       <c r="C534" s="24" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D534" s="24" t="s">
         <v>8</v>
@@ -11388,7 +11388,7 @@
         <v>478</v>
       </c>
       <c r="C535" s="24" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D535" s="24" t="s">
         <v>8</v>
@@ -11405,7 +11405,7 @@
         <v>478</v>
       </c>
       <c r="C536" s="24" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D536" s="24" t="s">
         <v>8</v>
@@ -11422,7 +11422,7 @@
         <v>478</v>
       </c>
       <c r="C537" s="24" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D537" s="24" t="s">
         <v>8</v>
@@ -11431,7 +11431,7 @@
         <v>16.620052075727429</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A538" s="24" t="s">
         <v>461</v>
       </c>
@@ -11439,7 +11439,7 @@
         <v>478</v>
       </c>
       <c r="C538" s="24" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D538" s="24" t="s">
         <v>8</v>
@@ -11456,7 +11456,7 @@
         <v>478</v>
       </c>
       <c r="C539" s="24" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D539" s="24" t="s">
         <v>8</v>
@@ -11465,7 +11465,7 @@
         <v>16.620052075727429</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A540" s="24" t="s">
         <v>461</v>
       </c>
@@ -11473,7 +11473,7 @@
         <v>478</v>
       </c>
       <c r="C540" s="24" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D540" s="24" t="s">
         <v>8</v>
@@ -11490,7 +11490,7 @@
         <v>478</v>
       </c>
       <c r="C541" s="24" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D541" s="24" t="s">
         <v>8</v>
@@ -11507,7 +11507,7 @@
         <v>478</v>
       </c>
       <c r="C542" s="24" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D542" s="24" t="s">
         <v>8</v>
@@ -11524,7 +11524,7 @@
         <v>478</v>
       </c>
       <c r="C543" s="24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D543" s="24" t="s">
         <v>8</v>
@@ -11541,7 +11541,7 @@
         <v>478</v>
       </c>
       <c r="C544" s="24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D544" s="24" t="s">
         <v>8</v>
@@ -11558,7 +11558,7 @@
         <v>478</v>
       </c>
       <c r="C545" s="24" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D545" s="24" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>478</v>
       </c>
       <c r="C546" s="24" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D546" s="24" t="s">
         <v>8</v>
@@ -11592,7 +11592,7 @@
         <v>478</v>
       </c>
       <c r="C547" s="24" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D547" s="24" t="s">
         <v>8</v>
@@ -11609,7 +11609,7 @@
         <v>478</v>
       </c>
       <c r="C548" s="24" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D548" s="24" t="s">
         <v>8</v>
@@ -11626,7 +11626,7 @@
         <v>478</v>
       </c>
       <c r="C549" s="24" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D549" s="24" t="s">
         <v>8</v>
@@ -11634,6 +11634,7 @@
       <c r="E549" s="24">
         <v>16.620052075727429</v>
       </c>
+      <c r="F549" s="62"/>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A550" s="24" t="s">
@@ -11643,7 +11644,7 @@
         <v>478</v>
       </c>
       <c r="C550" s="24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D550" s="24" t="s">
         <v>8</v>
@@ -11661,7 +11662,7 @@
         <v>478</v>
       </c>
       <c r="C551" s="24" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D551" s="24" t="s">
         <v>8</v>
@@ -11679,7 +11680,7 @@
         <v>478</v>
       </c>
       <c r="C552" s="24" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D552" s="24" t="s">
         <v>8</v>
@@ -11689,7 +11690,7 @@
       </c>
       <c r="F552" s="62"/>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A553" s="24" t="s">
         <v>461</v>
       </c>
@@ -11697,7 +11698,7 @@
         <v>478</v>
       </c>
       <c r="C553" s="24" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D553" s="24" t="s">
         <v>8</v>
@@ -11705,7 +11706,6 @@
       <c r="E553" s="24">
         <v>16.620052075727429</v>
       </c>
-      <c r="F553" s="62"/>
     </row>
     <row r="554" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A554" s="24" t="s">
@@ -11715,13 +11715,13 @@
         <v>478</v>
       </c>
       <c r="C554" s="24" t="s">
-        <v>211</v>
+        <v>405</v>
       </c>
       <c r="D554" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E554" s="24">
-        <v>16.620052075727429</v>
+        <v>1.200133763891887</v>
       </c>
     </row>
     <row r="555" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.4">
@@ -11732,7 +11732,7 @@
         <v>478</v>
       </c>
       <c r="C555" s="24" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D555" s="24" t="s">
         <v>8</v>
@@ -11740,6 +11740,7 @@
       <c r="E555" s="24">
         <v>1.200133763891887</v>
       </c>
+      <c r="F555" s="6"/>
     </row>
     <row r="556" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A556" s="24" t="s">
@@ -11749,7 +11750,7 @@
         <v>478</v>
       </c>
       <c r="C556" s="24" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D556" s="24" t="s">
         <v>8</v>
@@ -11767,7 +11768,7 @@
         <v>478</v>
       </c>
       <c r="C557" s="24" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D557" s="24" t="s">
         <v>8</v>
@@ -11777,7 +11778,7 @@
       </c>
       <c r="F557" s="6"/>
     </row>
-    <row r="558" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A558" s="24" t="s">
         <v>461</v>
       </c>
@@ -11785,7 +11786,7 @@
         <v>478</v>
       </c>
       <c r="C558" s="24" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D558" s="24" t="s">
         <v>8</v>
@@ -11793,7 +11794,6 @@
       <c r="E558" s="24">
         <v>1.200133763891887</v>
       </c>
-      <c r="F558" s="6"/>
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A559" s="24" t="s">
@@ -11803,13 +11803,13 @@
         <v>478</v>
       </c>
       <c r="C559" s="24" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D559" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E559" s="24">
-        <v>1.200133763891887</v>
+        <v>2.2950826268293949</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.4">
@@ -11820,7 +11820,7 @@
         <v>478</v>
       </c>
       <c r="C560" s="24" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D560" s="24" t="s">
         <v>8</v>
@@ -11837,7 +11837,7 @@
         <v>478</v>
       </c>
       <c r="C561" s="24" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D561" s="24" t="s">
         <v>8</v>
@@ -11845,6 +11845,7 @@
       <c r="E561" s="24">
         <v>2.2950826268293949</v>
       </c>
+      <c r="G561" s="9"/>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A562" s="24" t="s">
@@ -11854,7 +11855,7 @@
         <v>478</v>
       </c>
       <c r="C562" s="24" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D562" s="24" t="s">
         <v>8</v>
@@ -11872,7 +11873,7 @@
         <v>478</v>
       </c>
       <c r="C563" s="24" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D563" s="24" t="s">
         <v>8</v>
@@ -11890,7 +11891,7 @@
         <v>478</v>
       </c>
       <c r="C564" s="24" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D564" s="24" t="s">
         <v>8</v>
@@ -11908,7 +11909,7 @@
         <v>478</v>
       </c>
       <c r="C565" s="24" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D565" s="24" t="s">
         <v>8</v>
@@ -11926,7 +11927,7 @@
         <v>478</v>
       </c>
       <c r="C566" s="24" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D566" s="24" t="s">
         <v>8</v>
@@ -11944,7 +11945,7 @@
         <v>478</v>
       </c>
       <c r="C567" s="24" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D567" s="24" t="s">
         <v>8</v>
@@ -11962,7 +11963,7 @@
         <v>478</v>
       </c>
       <c r="C568" s="24" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D568" s="24" t="s">
         <v>8</v>
@@ -11980,7 +11981,7 @@
         <v>478</v>
       </c>
       <c r="C569" s="24" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D569" s="24" t="s">
         <v>8</v>
@@ -11998,7 +11999,7 @@
         <v>478</v>
       </c>
       <c r="C570" s="24" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D570" s="24" t="s">
         <v>8</v>
@@ -12016,7 +12017,7 @@
         <v>478</v>
       </c>
       <c r="C571" s="24" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D571" s="24" t="s">
         <v>8</v>
@@ -12027,20 +12028,20 @@
       <c r="G571" s="9"/>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A572" s="24" t="s">
-        <v>461</v>
-      </c>
-      <c r="B572" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C572" s="24" t="s">
-        <v>422</v>
-      </c>
-      <c r="D572" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="E572" s="24">
-        <v>2.2950826268293949</v>
+      <c r="A572" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B572" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C572" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="D572" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E572" s="59">
+        <v>3.65E-7</v>
       </c>
       <c r="G572" s="9"/>
     </row>
@@ -12052,13 +12053,13 @@
         <v>477</v>
       </c>
       <c r="C573" s="57" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D573" s="58" t="s">
         <v>124</v>
       </c>
       <c r="E573" s="59">
-        <v>3.65E-7</v>
+        <v>2.28E-7</v>
       </c>
       <c r="G573" s="9"/>
     </row>
@@ -12070,7 +12071,7 @@
         <v>477</v>
       </c>
       <c r="C574" s="57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D574" s="58" t="s">
         <v>124</v>
@@ -12088,7 +12089,7 @@
         <v>477</v>
       </c>
       <c r="C575" s="57" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D575" s="58" t="s">
         <v>124</v>
@@ -12106,7 +12107,7 @@
         <v>477</v>
       </c>
       <c r="C576" s="57" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D576" s="58" t="s">
         <v>124</v>
@@ -12124,7 +12125,7 @@
         <v>477</v>
       </c>
       <c r="C577" s="57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D577" s="58" t="s">
         <v>124</v>
@@ -12142,7 +12143,7 @@
         <v>477</v>
       </c>
       <c r="C578" s="57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D578" s="58" t="s">
         <v>124</v>
@@ -12160,7 +12161,7 @@
         <v>477</v>
       </c>
       <c r="C579" s="57" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D579" s="58" t="s">
         <v>124</v>
@@ -12168,7 +12169,6 @@
       <c r="E579" s="59">
         <v>2.28E-7</v>
       </c>
-      <c r="G579" s="9"/>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A580" s="55" t="s">
@@ -12178,13 +12178,13 @@
         <v>477</v>
       </c>
       <c r="C580" s="57" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D580" s="58" t="s">
         <v>124</v>
       </c>
       <c r="E580" s="59">
-        <v>2.28E-7</v>
+        <v>1.2200000000000001E-7</v>
       </c>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.4">
@@ -12195,7 +12195,7 @@
         <v>477</v>
       </c>
       <c r="C581" s="57" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D581" s="58" t="s">
         <v>124</v>
@@ -12212,7 +12212,7 @@
         <v>477</v>
       </c>
       <c r="C582" s="57" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D582" s="58" t="s">
         <v>124</v>
@@ -12229,7 +12229,7 @@
         <v>477</v>
       </c>
       <c r="C583" s="57" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D583" s="58" t="s">
         <v>124</v>
@@ -12246,7 +12246,7 @@
         <v>477</v>
       </c>
       <c r="C584" s="57" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D584" s="58" t="s">
         <v>124</v>
@@ -12263,7 +12263,7 @@
         <v>477</v>
       </c>
       <c r="C585" s="57" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D585" s="58" t="s">
         <v>124</v>
@@ -12280,7 +12280,7 @@
         <v>477</v>
       </c>
       <c r="C586" s="57" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D586" s="58" t="s">
         <v>124</v>
@@ -12297,7 +12297,7 @@
         <v>477</v>
       </c>
       <c r="C587" s="57" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D587" s="58" t="s">
         <v>124</v>
@@ -12314,7 +12314,7 @@
         <v>477</v>
       </c>
       <c r="C588" s="57" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D588" s="58" t="s">
         <v>124</v>
@@ -12331,7 +12331,7 @@
         <v>477</v>
       </c>
       <c r="C589" s="57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D589" s="58" t="s">
         <v>124</v>
@@ -12348,7 +12348,7 @@
         <v>477</v>
       </c>
       <c r="C590" s="57" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D590" s="58" t="s">
         <v>124</v>
@@ -12365,7 +12365,7 @@
         <v>477</v>
       </c>
       <c r="C591" s="57" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D591" s="58" t="s">
         <v>124</v>
@@ -12382,7 +12382,7 @@
         <v>477</v>
       </c>
       <c r="C592" s="57" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D592" s="58" t="s">
         <v>124</v>
@@ -12399,13 +12399,13 @@
         <v>477</v>
       </c>
       <c r="C593" s="57" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="D593" s="58" t="s">
         <v>124</v>
       </c>
       <c r="E593" s="59">
-        <v>1.2200000000000001E-7</v>
+        <v>5.2999999999999998E-8</v>
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.4">
@@ -12416,7 +12416,7 @@
         <v>477</v>
       </c>
       <c r="C594" s="57" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D594" s="58" t="s">
         <v>124</v>
@@ -12433,7 +12433,7 @@
         <v>477</v>
       </c>
       <c r="C595" s="57" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D595" s="58" t="s">
         <v>124</v>
@@ -12443,20 +12443,20 @@
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A596" s="55" t="s">
-        <v>498</v>
+      <c r="A596" s="60" t="s">
+        <v>427</v>
       </c>
       <c r="B596" s="56" t="s">
         <v>477</v>
       </c>
-      <c r="C596" s="57" t="s">
-        <v>161</v>
+      <c r="C596" s="60" t="s">
+        <v>462</v>
       </c>
       <c r="D596" s="58" t="s">
-        <v>124</v>
+        <v>430</v>
       </c>
       <c r="E596" s="59">
-        <v>5.2999999999999998E-8</v>
+        <v>5.4624999999999996E-7</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.4">
@@ -12467,13 +12467,13 @@
         <v>477</v>
       </c>
       <c r="C597" s="60" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D597" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E597" s="59">
-        <v>5.4624999999999996E-7</v>
+        <v>4.3700000000000001E-7</v>
       </c>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.4">
@@ -12484,13 +12484,13 @@
         <v>477</v>
       </c>
       <c r="C598" s="60" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D598" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E598" s="59">
-        <v>4.3700000000000001E-7</v>
+        <v>4.752375E-7</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.4">
@@ -12501,13 +12501,13 @@
         <v>477</v>
       </c>
       <c r="C599" s="60" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D599" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E599" s="59">
-        <v>4.752375E-7</v>
+        <v>1.0105625E-7</v>
       </c>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.4">
@@ -12518,7 +12518,7 @@
         <v>477</v>
       </c>
       <c r="C600" s="60" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D600" s="58" t="s">
         <v>430</v>
@@ -12535,13 +12535,13 @@
         <v>477</v>
       </c>
       <c r="C601" s="60" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D601" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E601" s="59">
-        <v>1.0105625E-7</v>
+        <v>1.3656249999999999E-7</v>
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.4">
@@ -12552,13 +12552,13 @@
         <v>477</v>
       </c>
       <c r="C602" s="60" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D602" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E602" s="59">
-        <v>1.3656249999999999E-7</v>
+        <v>5.0254999999999996E-7</v>
       </c>
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.4">
@@ -12569,13 +12569,13 @@
         <v>477</v>
       </c>
       <c r="C603" s="60" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D603" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E603" s="59">
-        <v>5.0254999999999996E-7</v>
+        <v>4.9162500000000004E-7</v>
       </c>
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.4">
@@ -12586,13 +12586,13 @@
         <v>477</v>
       </c>
       <c r="C604" s="60" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D604" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E604" s="59">
-        <v>4.9162500000000004E-7</v>
+        <v>4.0375E-7</v>
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.4">
@@ -12603,7 +12603,7 @@
         <v>477</v>
       </c>
       <c r="C605" s="60" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D605" s="58" t="s">
         <v>430</v>
@@ -12620,7 +12620,7 @@
         <v>477</v>
       </c>
       <c r="C606" s="60" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D606" s="58" t="s">
         <v>430</v>
@@ -12637,7 +12637,7 @@
         <v>477</v>
       </c>
       <c r="C607" s="60" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D607" s="58" t="s">
         <v>430</v>
@@ -12654,7 +12654,7 @@
         <v>477</v>
       </c>
       <c r="C608" s="60" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D608" s="58" t="s">
         <v>430</v>
@@ -12671,7 +12671,7 @@
         <v>477</v>
       </c>
       <c r="C609" s="60" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D609" s="58" t="s">
         <v>430</v>
@@ -12681,37 +12681,37 @@
       </c>
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A610" s="60" t="s">
+      <c r="A610" s="61" t="s">
         <v>427</v>
       </c>
       <c r="B610" s="56" t="s">
         <v>477</v>
       </c>
-      <c r="C610" s="60" t="s">
-        <v>475</v>
+      <c r="C610" s="61" t="s">
+        <v>476</v>
       </c>
       <c r="D610" s="58" t="s">
         <v>430</v>
       </c>
-      <c r="E610" s="59">
-        <v>4.0375E-7</v>
+      <c r="E610" s="63">
+        <v>3.8000000000000001E-7</v>
       </c>
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A611" s="61" t="s">
+      <c r="A611" s="60" t="s">
         <v>427</v>
       </c>
       <c r="B611" s="56" t="s">
         <v>477</v>
       </c>
-      <c r="C611" s="61" t="s">
-        <v>476</v>
+      <c r="C611" s="60" t="s">
+        <v>479</v>
       </c>
       <c r="D611" s="58" t="s">
         <v>430</v>
       </c>
-      <c r="E611" s="63">
-        <v>3.8000000000000001E-7</v>
+      <c r="E611" s="59">
+        <v>5.4624999999999996E-7</v>
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.4">
@@ -12722,13 +12722,13 @@
         <v>477</v>
       </c>
       <c r="C612" s="60" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D612" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E612" s="59">
-        <v>5.4624999999999996E-7</v>
+        <v>4.369999999999999E-7</v>
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.4">
@@ -12739,13 +12739,13 @@
         <v>477</v>
       </c>
       <c r="C613" s="60" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D613" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E613" s="59">
-        <v>4.369999999999999E-7</v>
+        <v>4.7523749999999994E-7</v>
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.4">
@@ -12756,13 +12756,13 @@
         <v>477</v>
       </c>
       <c r="C614" s="60" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D614" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E614" s="59">
-        <v>4.7523749999999994E-7</v>
+        <v>1.0105625000000002E-7</v>
       </c>
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.4">
@@ -12773,13 +12773,13 @@
         <v>477</v>
       </c>
       <c r="C615" s="60" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D615" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E615" s="59">
-        <v>1.0105625000000002E-7</v>
+        <v>5.4624999999999996E-7</v>
       </c>
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.4">
@@ -12790,13 +12790,13 @@
         <v>477</v>
       </c>
       <c r="C616" s="60" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D616" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E616" s="59">
-        <v>5.4624999999999996E-7</v>
+        <v>5.2002999999999987E-7</v>
       </c>
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.4">
@@ -12807,13 +12807,13 @@
         <v>477</v>
       </c>
       <c r="C617" s="60" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D617" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E617" s="59">
-        <v>5.2002999999999987E-7</v>
+        <v>6.6642499999999983E-8</v>
       </c>
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.4">
@@ -12823,14 +12823,14 @@
       <c r="B618" s="56" t="s">
         <v>477</v>
       </c>
-      <c r="C618" s="60" t="s">
-        <v>485</v>
+      <c r="C618" s="61" t="s">
+        <v>486</v>
       </c>
       <c r="D618" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E618" s="59">
-        <v>6.6642499999999983E-8</v>
+        <v>1.0105625000000002E-7</v>
       </c>
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.4">
@@ -12840,8 +12840,8 @@
       <c r="B619" s="56" t="s">
         <v>477</v>
       </c>
-      <c r="C619" s="61" t="s">
-        <v>486</v>
+      <c r="C619" s="60" t="s">
+        <v>487</v>
       </c>
       <c r="D619" s="58" t="s">
         <v>430</v>
@@ -12858,13 +12858,13 @@
         <v>477</v>
       </c>
       <c r="C620" s="60" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D620" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E620" s="59">
-        <v>1.0105625000000002E-7</v>
+        <v>1.3656249999999996E-7</v>
       </c>
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.4">
@@ -12875,13 +12875,13 @@
         <v>477</v>
       </c>
       <c r="C621" s="60" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D621" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E621" s="59">
-        <v>1.3656249999999996E-7</v>
+        <v>5.0254999999999996E-7</v>
       </c>
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.4">
@@ -12892,13 +12892,13 @@
         <v>477</v>
       </c>
       <c r="C622" s="60" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D622" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E622" s="59">
-        <v>5.0254999999999996E-7</v>
+        <v>2.7312499999999993E-7</v>
       </c>
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.4">
@@ -12909,13 +12909,13 @@
         <v>477</v>
       </c>
       <c r="C623" s="60" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D623" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E623" s="59">
-        <v>2.7312499999999993E-7</v>
+        <v>4.9162499999999993E-7</v>
       </c>
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.4">
@@ -12926,13 +12926,13 @@
         <v>477</v>
       </c>
       <c r="C624" s="60" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D624" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E624" s="59">
-        <v>4.9162499999999993E-7</v>
+        <v>4.6431249999999992E-7</v>
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.4">
@@ -12943,7 +12943,7 @@
         <v>477</v>
       </c>
       <c r="C625" s="60" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D625" s="58" t="s">
         <v>430</v>
@@ -12960,13 +12960,13 @@
         <v>477</v>
       </c>
       <c r="C626" s="60" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D626" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E626" s="59">
-        <v>4.6431249999999992E-7</v>
+        <v>4.0374999999999995E-7</v>
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.4">
@@ -12977,13 +12977,13 @@
         <v>477</v>
       </c>
       <c r="C627" s="60" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D627" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E627" s="59">
-        <v>4.0374999999999995E-7</v>
+        <v>3.7999999999999996E-7</v>
       </c>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.4">
@@ -12994,7 +12994,7 @@
         <v>477</v>
       </c>
       <c r="C628" s="60" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D628" s="58" t="s">
         <v>430</v>
@@ -13011,7 +13011,7 @@
         <v>477</v>
       </c>
       <c r="C629" s="60" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D629" s="58" t="s">
         <v>430</v>
@@ -13021,36 +13021,19 @@
       </c>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A630" s="60" t="s">
+      <c r="A630" s="47" t="s">
         <v>427</v>
       </c>
-      <c r="B630" s="56" t="s">
-        <v>477</v>
-      </c>
-      <c r="C630" s="60" t="s">
-        <v>497</v>
-      </c>
-      <c r="D630" s="58" t="s">
+      <c r="B630" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C630" s="48" t="s">
+        <v>429</v>
+      </c>
+      <c r="D630" s="49" t="s">
         <v>430</v>
       </c>
-      <c r="E630" s="59">
-        <v>3.7999999999999996E-7</v>
-      </c>
-    </row>
-    <row r="631" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A631" s="47" t="s">
-        <v>427</v>
-      </c>
-      <c r="B631" s="47" t="s">
-        <v>428</v>
-      </c>
-      <c r="C631" s="48" t="s">
-        <v>429</v>
-      </c>
-      <c r="D631" s="49" t="s">
-        <v>430</v>
-      </c>
-      <c r="E631" s="50">
+      <c r="E630" s="50">
         <v>1</v>
       </c>
     </row>

--- a/data/facteurs de caractérisation.xlsx
+++ b/data/facteurs de caractérisation.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\CIRED\PlaneFR\Code\Module_PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC80E7E-889C-45A1-B902-5CC01D3EB4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEDE94C-F4ED-4BF9-820F-28BCBB3326F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="8002" windowWidth="14595" windowHeight="8745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="synthèse" sheetId="1" r:id="rId1"/>
-    <sheet name="synthèse MSA" sheetId="2" r:id="rId2"/>
-    <sheet name="synthèse v3" sheetId="3" r:id="rId3"/>
-    <sheet name="synthèse v2" sheetId="4" r:id="rId4"/>
-    <sheet name="Feuil1" sheetId="5" r:id="rId5"/>
-    <sheet name="Feuil2" sheetId="6" r:id="rId6"/>
+    <sheet name="synthèse agri" sheetId="7" r:id="rId2"/>
+    <sheet name="synthèse MSA" sheetId="2" r:id="rId3"/>
+    <sheet name="synthèse v3" sheetId="3" r:id="rId4"/>
+    <sheet name="synthèse v2" sheetId="4" r:id="rId5"/>
+    <sheet name="Feuil1" sheetId="5" r:id="rId6"/>
+    <sheet name="Feuil2" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4428" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4933" uniqueCount="532">
   <si>
     <t>Processus du système Terre</t>
   </si>
@@ -1632,6 +1633,9 @@
   </si>
   <si>
     <t>Planted forest</t>
+  </si>
+  <si>
+    <t>Agricultural land</t>
   </si>
 </sst>
 </file>
@@ -2275,7 +2279,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G630"/>
+  <dimension ref="A1:G633"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24.69140625" style="6" customWidth="1"/>
@@ -4587,7 +4591,7 @@
         <v>498</v>
       </c>
       <c r="B136" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C136" s="32" t="s">
         <v>123</v>
@@ -4604,7 +4608,7 @@
         <v>498</v>
       </c>
       <c r="B137" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C137" s="32" t="s">
         <v>125</v>
@@ -4621,7 +4625,7 @@
         <v>498</v>
       </c>
       <c r="B138" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C138" s="32" t="s">
         <v>126</v>
@@ -4638,7 +4642,7 @@
         <v>498</v>
       </c>
       <c r="B139" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C139" s="32" t="s">
         <v>127</v>
@@ -4655,7 +4659,7 @@
         <v>498</v>
       </c>
       <c r="B140" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C140" s="32" t="s">
         <v>128</v>
@@ -4672,7 +4676,7 @@
         <v>498</v>
       </c>
       <c r="B141" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C141" s="32" t="s">
         <v>129</v>
@@ -4689,7 +4693,7 @@
         <v>498</v>
       </c>
       <c r="B142" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C142" s="32" t="s">
         <v>130</v>
@@ -4706,7 +4710,7 @@
         <v>498</v>
       </c>
       <c r="B143" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C143" s="32" t="s">
         <v>131</v>
@@ -4723,7 +4727,7 @@
         <v>498</v>
       </c>
       <c r="B144" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C144" s="32" t="s">
         <v>132</v>
@@ -4740,7 +4744,7 @@
         <v>498</v>
       </c>
       <c r="B145" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C145" s="32" t="s">
         <v>133</v>
@@ -4757,7 +4761,7 @@
         <v>498</v>
       </c>
       <c r="B146" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C146" s="32" t="s">
         <v>134</v>
@@ -4774,7 +4778,7 @@
         <v>498</v>
       </c>
       <c r="B147" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C147" s="32" t="s">
         <v>135</v>
@@ -4791,7 +4795,7 @@
         <v>498</v>
       </c>
       <c r="B148" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C148" s="32" t="s">
         <v>136</v>
@@ -4808,7 +4812,7 @@
         <v>498</v>
       </c>
       <c r="B149" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C149" s="32" t="s">
         <v>137</v>
@@ -4825,7 +4829,7 @@
         <v>498</v>
       </c>
       <c r="B150" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C150" s="32" t="s">
         <v>138</v>
@@ -4842,7 +4846,7 @@
         <v>498</v>
       </c>
       <c r="B151" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C151" s="32" t="s">
         <v>139</v>
@@ -4859,7 +4863,7 @@
         <v>498</v>
       </c>
       <c r="B152" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C152" s="32" t="s">
         <v>140</v>
@@ -4876,7 +4880,7 @@
         <v>498</v>
       </c>
       <c r="B153" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C153" s="32" t="s">
         <v>141</v>
@@ -4893,7 +4897,7 @@
         <v>498</v>
       </c>
       <c r="B154" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C154" s="32" t="s">
         <v>142</v>
@@ -4910,7 +4914,7 @@
         <v>498</v>
       </c>
       <c r="B155" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C155" s="32" t="s">
         <v>143</v>
@@ -4927,7 +4931,7 @@
         <v>498</v>
       </c>
       <c r="B156" s="31" t="s">
-        <v>122</v>
+        <v>531</v>
       </c>
       <c r="C156" s="32" t="s">
         <v>144</v>
@@ -4939,66 +4943,66 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A157" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="B157" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="C157" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="D157" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="E157" s="29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A158" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="B158" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="C158" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="D158" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="E158" s="29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A159" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="B159" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="C159" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="D159" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="E159" s="29">
+    <row r="157" spans="1:5" s="62" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A157" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B157" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C157" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="D157" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E157" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" s="62" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A158" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B158" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C158" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="D158" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E158" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" s="62" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A159" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B159" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C159" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="D159" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E159" s="34">
         <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A160" s="26" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B160" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C160" s="30" t="s">
-        <v>151</v>
+      <c r="C160" s="27" t="s">
+        <v>147</v>
       </c>
       <c r="D160" s="28" t="s">
         <v>148</v>
@@ -5014,8 +5018,8 @@
       <c r="B161" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C161" s="30" t="s">
-        <v>152</v>
+      <c r="C161" s="27" t="s">
+        <v>147</v>
       </c>
       <c r="D161" s="28" t="s">
         <v>148</v>
@@ -5031,8 +5035,8 @@
       <c r="B162" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C162" s="30" t="s">
-        <v>153</v>
+      <c r="C162" s="27" t="s">
+        <v>150</v>
       </c>
       <c r="D162" s="28" t="s">
         <v>148</v>
@@ -5049,7 +5053,7 @@
         <v>146</v>
       </c>
       <c r="C163" s="30" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D163" s="28" t="s">
         <v>148</v>
@@ -5059,74 +5063,71 @@
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A164" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="B164" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C164" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="D164" s="20" t="s">
+      <c r="A164" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B164" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C164" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="D164" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="E164" s="21">
-        <f t="shared" ref="E164:E170" si="0">(0.110407441507011+0.0165)*1000000000</f>
-        <v>126907441.507011</v>
+      <c r="E164" s="29">
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A165" s="18" t="s">
+      <c r="A165" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="B165" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C165" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="D165" s="20" t="s">
+      <c r="B165" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C165" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="D165" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="E165" s="21">
-        <f t="shared" si="0"/>
-        <v>126907441.507011</v>
+      <c r="E165" s="29">
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A166" s="18" t="s">
+      <c r="A166" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="B166" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C166" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="D166" s="20" t="s">
+      <c r="B166" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C166" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="D166" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="E166" s="21">
-        <f t="shared" si="0"/>
-        <v>126907441.507011</v>
+      <c r="E166" s="29">
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A167" s="18" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B167" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C167" s="22" t="s">
-        <v>151</v>
+      <c r="C167" s="19" t="s">
+        <v>147</v>
       </c>
       <c r="D167" s="20" t="s">
         <v>148</v>
       </c>
       <c r="E167" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E167:E173" si="0">(0.110407441507011+0.0165)*1000000000</f>
         <v>126907441.507011</v>
       </c>
     </row>
@@ -5137,8 +5138,8 @@
       <c r="B168" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C168" s="22" t="s">
-        <v>152</v>
+      <c r="C168" s="19" t="s">
+        <v>147</v>
       </c>
       <c r="D168" s="20" t="s">
         <v>148</v>
@@ -5155,8 +5156,8 @@
       <c r="B169" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C169" s="22" t="s">
-        <v>153</v>
+      <c r="C169" s="19" t="s">
+        <v>150</v>
       </c>
       <c r="D169" s="20" t="s">
         <v>148</v>
@@ -5174,7 +5175,7 @@
         <v>478</v>
       </c>
       <c r="C170" s="22" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D170" s="20" t="s">
         <v>148</v>
@@ -5186,53 +5187,56 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A171" s="18" t="s">
-        <v>498</v>
+        <v>149</v>
       </c>
       <c r="B171" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C171" s="23" t="s">
-        <v>157</v>
+      <c r="C171" s="22" t="s">
+        <v>152</v>
       </c>
       <c r="D171" s="20" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="E171" s="21">
-        <v>485679.81716597301</v>
+        <f t="shared" si="0"/>
+        <v>126907441.507011</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A172" s="18" t="s">
-        <v>498</v>
+        <v>149</v>
       </c>
       <c r="B172" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C172" s="23" t="s">
-        <v>123</v>
+      <c r="C172" s="22" t="s">
+        <v>153</v>
       </c>
       <c r="D172" s="20" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="E172" s="21">
-        <v>608053.19508885196</v>
+        <f t="shared" si="0"/>
+        <v>126907441.507011</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A173" s="18" t="s">
-        <v>498</v>
+        <v>149</v>
       </c>
       <c r="B173" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C173" s="23" t="s">
-        <v>125</v>
+      <c r="C173" s="22" t="s">
+        <v>154</v>
       </c>
       <c r="D173" s="20" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="E173" s="21">
-        <v>608053.19508885196</v>
+        <f t="shared" si="0"/>
+        <v>126907441.507011</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.4">
@@ -5243,13 +5247,13 @@
         <v>478</v>
       </c>
       <c r="C174" s="23" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="D174" s="20" t="s">
         <v>124</v>
       </c>
       <c r="E174" s="21">
-        <v>608053.19508885196</v>
+        <v>485679.81716597301</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.4">
@@ -5260,7 +5264,7 @@
         <v>478</v>
       </c>
       <c r="C175" s="23" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D175" s="20" t="s">
         <v>124</v>
@@ -5277,7 +5281,7 @@
         <v>478</v>
       </c>
       <c r="C176" s="23" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D176" s="20" t="s">
         <v>124</v>
@@ -5294,7 +5298,7 @@
         <v>478</v>
       </c>
       <c r="C177" s="23" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D177" s="20" t="s">
         <v>124</v>
@@ -5311,7 +5315,7 @@
         <v>478</v>
       </c>
       <c r="C178" s="23" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D178" s="20" t="s">
         <v>124</v>
@@ -5328,7 +5332,7 @@
         <v>478</v>
       </c>
       <c r="C179" s="23" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D179" s="20" t="s">
         <v>124</v>
@@ -5345,13 +5349,13 @@
         <v>478</v>
       </c>
       <c r="C180" s="23" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D180" s="20" t="s">
         <v>124</v>
       </c>
       <c r="E180" s="21">
-        <v>229042.93475783701</v>
+        <v>608053.19508885196</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.4">
@@ -5362,13 +5366,13 @@
         <v>478</v>
       </c>
       <c r="C181" s="23" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D181" s="20" t="s">
         <v>124</v>
       </c>
       <c r="E181" s="21">
-        <v>229042.93475783701</v>
+        <v>608053.19508885196</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.4">
@@ -5379,13 +5383,13 @@
         <v>478</v>
       </c>
       <c r="C182" s="23" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D182" s="20" t="s">
         <v>124</v>
       </c>
       <c r="E182" s="21">
-        <v>229042.93475783701</v>
+        <v>608053.19508885196</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.4">
@@ -5396,7 +5400,7 @@
         <v>478</v>
       </c>
       <c r="C183" s="23" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D183" s="20" t="s">
         <v>124</v>
@@ -5413,7 +5417,7 @@
         <v>478</v>
       </c>
       <c r="C184" s="23" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D184" s="20" t="s">
         <v>124</v>
@@ -5430,7 +5434,7 @@
         <v>478</v>
       </c>
       <c r="C185" s="23" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D185" s="20" t="s">
         <v>124</v>
@@ -5447,7 +5451,7 @@
         <v>478</v>
       </c>
       <c r="C186" s="23" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D186" s="20" t="s">
         <v>124</v>
@@ -5464,7 +5468,7 @@
         <v>478</v>
       </c>
       <c r="C187" s="23" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D187" s="20" t="s">
         <v>124</v>
@@ -5481,7 +5485,7 @@
         <v>478</v>
       </c>
       <c r="C188" s="23" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D188" s="20" t="s">
         <v>124</v>
@@ -5498,7 +5502,7 @@
         <v>478</v>
       </c>
       <c r="C189" s="23" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D189" s="20" t="s">
         <v>124</v>
@@ -5515,7 +5519,7 @@
         <v>478</v>
       </c>
       <c r="C190" s="23" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D190" s="20" t="s">
         <v>124</v>
@@ -5532,7 +5536,7 @@
         <v>478</v>
       </c>
       <c r="C191" s="23" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D191" s="20" t="s">
         <v>124</v>
@@ -5549,7 +5553,7 @@
         <v>478</v>
       </c>
       <c r="C192" s="23" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D192" s="20" t="s">
         <v>124</v>
@@ -5566,7 +5570,7 @@
         <v>478</v>
       </c>
       <c r="C193" s="23" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="D193" s="20" t="s">
         <v>124</v>
@@ -5583,7 +5587,7 @@
         <v>478</v>
       </c>
       <c r="C194" s="23" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="D194" s="20" t="s">
         <v>124</v>
@@ -5600,7 +5604,7 @@
         <v>478</v>
       </c>
       <c r="C195" s="23" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="D195" s="20" t="s">
         <v>124</v>
@@ -5609,7 +5613,7 @@
         <v>229042.93475783701</v>
       </c>
     </row>
-    <row r="196" spans="1:5" s="62" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A196" s="18" t="s">
         <v>498</v>
       </c>
@@ -5617,16 +5621,16 @@
         <v>478</v>
       </c>
       <c r="C196" s="23" t="s">
-        <v>529</v>
+        <v>159</v>
       </c>
       <c r="D196" s="20" t="s">
         <v>124</v>
       </c>
       <c r="E196" s="21">
-        <v>109564.693955489</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" s="62" customFormat="1" x14ac:dyDescent="0.4">
+        <v>229042.93475783701</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A197" s="18" t="s">
         <v>498</v>
       </c>
@@ -5634,64 +5638,64 @@
         <v>478</v>
       </c>
       <c r="C197" s="23" t="s">
-        <v>530</v>
+        <v>160</v>
       </c>
       <c r="D197" s="20" t="s">
         <v>124</v>
       </c>
       <c r="E197" s="21">
-        <v>109564.693955489</v>
+        <v>229042.93475783701</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A198" s="18" t="s">
-        <v>15</v>
+        <v>498</v>
       </c>
       <c r="B198" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C198" s="19" t="s">
-        <v>17</v>
+      <c r="C198" s="23" t="s">
+        <v>161</v>
       </c>
       <c r="D198" s="20" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="E198" s="21">
-        <v>306.2</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.4">
+        <v>229042.93475783701</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" s="62" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A199" s="18" t="s">
-        <v>15</v>
+        <v>498</v>
       </c>
       <c r="B199" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C199" s="19" t="s">
-        <v>19</v>
+      <c r="C199" s="23" t="s">
+        <v>529</v>
       </c>
       <c r="D199" s="20" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="E199" s="21">
-        <v>306.2</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.4">
+        <v>109564.693955489</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" s="62" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A200" s="18" t="s">
-        <v>15</v>
+        <v>498</v>
       </c>
       <c r="B200" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C200" s="19" t="s">
-        <v>20</v>
+      <c r="C200" s="23" t="s">
+        <v>530</v>
       </c>
       <c r="D200" s="20" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="E200" s="21">
-        <v>306.2</v>
+        <v>109564.693955489</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.4">
@@ -5702,7 +5706,7 @@
         <v>478</v>
       </c>
       <c r="C201" s="19" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D201" s="20" t="s">
         <v>18</v>
@@ -5719,7 +5723,7 @@
         <v>478</v>
       </c>
       <c r="C202" s="19" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D202" s="20" t="s">
         <v>18</v>
@@ -5736,7 +5740,7 @@
         <v>478</v>
       </c>
       <c r="C203" s="19" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D203" s="20" t="s">
         <v>18</v>
@@ -5753,7 +5757,7 @@
         <v>478</v>
       </c>
       <c r="C204" s="19" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D204" s="20" t="s">
         <v>18</v>
@@ -5770,7 +5774,7 @@
         <v>478</v>
       </c>
       <c r="C205" s="19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D205" s="20" t="s">
         <v>18</v>
@@ -5787,7 +5791,7 @@
         <v>478</v>
       </c>
       <c r="C206" s="19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D206" s="20" t="s">
         <v>18</v>
@@ -5804,7 +5808,7 @@
         <v>478</v>
       </c>
       <c r="C207" s="19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D207" s="20" t="s">
         <v>18</v>
@@ -5821,7 +5825,7 @@
         <v>478</v>
       </c>
       <c r="C208" s="19" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D208" s="20" t="s">
         <v>18</v>
@@ -5838,7 +5842,7 @@
         <v>478</v>
       </c>
       <c r="C209" s="19" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D209" s="20" t="s">
         <v>18</v>
@@ -5855,7 +5859,7 @@
         <v>478</v>
       </c>
       <c r="C210" s="19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D210" s="20" t="s">
         <v>18</v>
@@ -5872,7 +5876,7 @@
         <v>478</v>
       </c>
       <c r="C211" s="19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D211" s="20" t="s">
         <v>18</v>
@@ -5889,7 +5893,7 @@
         <v>478</v>
       </c>
       <c r="C212" s="19" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D212" s="20" t="s">
         <v>18</v>
@@ -5906,7 +5910,7 @@
         <v>478</v>
       </c>
       <c r="C213" s="19" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D213" s="20" t="s">
         <v>18</v>
@@ -5923,7 +5927,7 @@
         <v>478</v>
       </c>
       <c r="C214" s="19" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D214" s="20" t="s">
         <v>18</v>
@@ -5940,7 +5944,7 @@
         <v>478</v>
       </c>
       <c r="C215" s="19" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D215" s="20" t="s">
         <v>18</v>
@@ -5957,7 +5961,7 @@
         <v>478</v>
       </c>
       <c r="C216" s="19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D216" s="20" t="s">
         <v>18</v>
@@ -5974,7 +5978,7 @@
         <v>478</v>
       </c>
       <c r="C217" s="19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D217" s="20" t="s">
         <v>18</v>
@@ -5991,7 +5995,7 @@
         <v>478</v>
       </c>
       <c r="C218" s="19" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D218" s="20" t="s">
         <v>18</v>
@@ -6008,7 +6012,7 @@
         <v>478</v>
       </c>
       <c r="C219" s="19" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D219" s="20" t="s">
         <v>18</v>
@@ -6025,7 +6029,7 @@
         <v>478</v>
       </c>
       <c r="C220" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D220" s="20" t="s">
         <v>18</v>
@@ -6042,7 +6046,7 @@
         <v>478</v>
       </c>
       <c r="C221" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D221" s="20" t="s">
         <v>18</v>
@@ -6059,7 +6063,7 @@
         <v>478</v>
       </c>
       <c r="C222" s="19" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D222" s="20" t="s">
         <v>18</v>
@@ -6076,7 +6080,7 @@
         <v>478</v>
       </c>
       <c r="C223" s="19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D223" s="20" t="s">
         <v>18</v>
@@ -6093,7 +6097,7 @@
         <v>478</v>
       </c>
       <c r="C224" s="19" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D224" s="20" t="s">
         <v>18</v>
@@ -6110,7 +6114,7 @@
         <v>478</v>
       </c>
       <c r="C225" s="19" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D225" s="20" t="s">
         <v>18</v>
@@ -6127,7 +6131,7 @@
         <v>478</v>
       </c>
       <c r="C226" s="19" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D226" s="20" t="s">
         <v>18</v>
@@ -6144,7 +6148,7 @@
         <v>478</v>
       </c>
       <c r="C227" s="19" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D227" s="20" t="s">
         <v>18</v>
@@ -6161,7 +6165,7 @@
         <v>478</v>
       </c>
       <c r="C228" s="19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D228" s="20" t="s">
         <v>18</v>
@@ -6178,7 +6182,7 @@
         <v>478</v>
       </c>
       <c r="C229" s="19" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D229" s="20" t="s">
         <v>18</v>
@@ -6195,7 +6199,7 @@
         <v>478</v>
       </c>
       <c r="C230" s="19" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D230" s="20" t="s">
         <v>18</v>
@@ -6212,7 +6216,7 @@
         <v>478</v>
       </c>
       <c r="C231" s="19" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D231" s="20" t="s">
         <v>18</v>
@@ -6229,7 +6233,7 @@
         <v>478</v>
       </c>
       <c r="C232" s="19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D232" s="20" t="s">
         <v>18</v>
@@ -6246,7 +6250,7 @@
         <v>478</v>
       </c>
       <c r="C233" s="19" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D233" s="20" t="s">
         <v>18</v>
@@ -6263,7 +6267,7 @@
         <v>478</v>
       </c>
       <c r="C234" s="19" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D234" s="20" t="s">
         <v>18</v>
@@ -6280,7 +6284,7 @@
         <v>478</v>
       </c>
       <c r="C235" s="19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D235" s="20" t="s">
         <v>18</v>
@@ -6297,7 +6301,7 @@
         <v>478</v>
       </c>
       <c r="C236" s="19" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D236" s="20" t="s">
         <v>18</v>
@@ -6314,7 +6318,7 @@
         <v>478</v>
       </c>
       <c r="C237" s="19" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D237" s="20" t="s">
         <v>18</v>
@@ -6331,7 +6335,7 @@
         <v>478</v>
       </c>
       <c r="C238" s="19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D238" s="20" t="s">
         <v>18</v>
@@ -6348,7 +6352,7 @@
         <v>478</v>
       </c>
       <c r="C239" s="19" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D239" s="20" t="s">
         <v>18</v>
@@ -6365,7 +6369,7 @@
         <v>478</v>
       </c>
       <c r="C240" s="19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D240" s="20" t="s">
         <v>18</v>
@@ -6382,7 +6386,7 @@
         <v>478</v>
       </c>
       <c r="C241" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D241" s="20" t="s">
         <v>18</v>
@@ -6399,7 +6403,7 @@
         <v>478</v>
       </c>
       <c r="C242" s="19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D242" s="20" t="s">
         <v>18</v>
@@ -6416,7 +6420,7 @@
         <v>478</v>
       </c>
       <c r="C243" s="19" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D243" s="20" t="s">
         <v>18</v>
@@ -6433,7 +6437,7 @@
         <v>478</v>
       </c>
       <c r="C244" s="19" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D244" s="20" t="s">
         <v>18</v>
@@ -6450,7 +6454,7 @@
         <v>478</v>
       </c>
       <c r="C245" s="19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D245" s="20" t="s">
         <v>18</v>
@@ -6467,7 +6471,7 @@
         <v>478</v>
       </c>
       <c r="C246" s="19" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D246" s="20" t="s">
         <v>18</v>
@@ -6484,7 +6488,7 @@
         <v>478</v>
       </c>
       <c r="C247" s="19" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D247" s="20" t="s">
         <v>18</v>
@@ -6501,7 +6505,7 @@
         <v>478</v>
       </c>
       <c r="C248" s="19" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D248" s="20" t="s">
         <v>18</v>
@@ -6518,7 +6522,7 @@
         <v>478</v>
       </c>
       <c r="C249" s="19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D249" s="20" t="s">
         <v>18</v>
@@ -6535,7 +6539,7 @@
         <v>478</v>
       </c>
       <c r="C250" s="19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D250" s="20" t="s">
         <v>18</v>
@@ -6552,7 +6556,7 @@
         <v>478</v>
       </c>
       <c r="C251" s="19" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D251" s="20" t="s">
         <v>18</v>
@@ -6569,7 +6573,7 @@
         <v>478</v>
       </c>
       <c r="C252" s="19" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D252" s="20" t="s">
         <v>18</v>
@@ -6586,7 +6590,7 @@
         <v>478</v>
       </c>
       <c r="C253" s="19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D253" s="20" t="s">
         <v>18</v>
@@ -6603,7 +6607,7 @@
         <v>478</v>
       </c>
       <c r="C254" s="19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D254" s="20" t="s">
         <v>18</v>
@@ -6620,7 +6624,7 @@
         <v>478</v>
       </c>
       <c r="C255" s="19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D255" s="20" t="s">
         <v>18</v>
@@ -6637,7 +6641,7 @@
         <v>478</v>
       </c>
       <c r="C256" s="19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D256" s="20" t="s">
         <v>18</v>
@@ -6654,7 +6658,7 @@
         <v>478</v>
       </c>
       <c r="C257" s="19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D257" s="20" t="s">
         <v>18</v>
@@ -6671,7 +6675,7 @@
         <v>478</v>
       </c>
       <c r="C258" s="19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D258" s="20" t="s">
         <v>18</v>
@@ -6688,7 +6692,7 @@
         <v>478</v>
       </c>
       <c r="C259" s="19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D259" s="20" t="s">
         <v>18</v>
@@ -6705,7 +6709,7 @@
         <v>478</v>
       </c>
       <c r="C260" s="19" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D260" s="20" t="s">
         <v>18</v>
@@ -6722,7 +6726,7 @@
         <v>478</v>
       </c>
       <c r="C261" s="19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D261" s="20" t="s">
         <v>18</v>
@@ -6739,7 +6743,7 @@
         <v>478</v>
       </c>
       <c r="C262" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D262" s="20" t="s">
         <v>18</v>
@@ -6756,7 +6760,7 @@
         <v>478</v>
       </c>
       <c r="C263" s="19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D263" s="20" t="s">
         <v>18</v>
@@ -6773,7 +6777,7 @@
         <v>478</v>
       </c>
       <c r="C264" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D264" s="20" t="s">
         <v>18</v>
@@ -6790,7 +6794,7 @@
         <v>478</v>
       </c>
       <c r="C265" s="19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D265" s="20" t="s">
         <v>18</v>
@@ -6807,7 +6811,7 @@
         <v>478</v>
       </c>
       <c r="C266" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D266" s="20" t="s">
         <v>18</v>
@@ -6824,7 +6828,7 @@
         <v>478</v>
       </c>
       <c r="C267" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D267" s="20" t="s">
         <v>18</v>
@@ -6841,7 +6845,7 @@
         <v>478</v>
       </c>
       <c r="C268" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D268" s="20" t="s">
         <v>18</v>
@@ -6858,7 +6862,7 @@
         <v>478</v>
       </c>
       <c r="C269" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D269" s="20" t="s">
         <v>18</v>
@@ -6875,7 +6879,7 @@
         <v>478</v>
       </c>
       <c r="C270" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D270" s="20" t="s">
         <v>18</v>
@@ -6892,7 +6896,7 @@
         <v>478</v>
       </c>
       <c r="C271" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D271" s="20" t="s">
         <v>18</v>
@@ -6909,7 +6913,7 @@
         <v>478</v>
       </c>
       <c r="C272" s="19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D272" s="20" t="s">
         <v>18</v>
@@ -6926,7 +6930,7 @@
         <v>478</v>
       </c>
       <c r="C273" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D273" s="20" t="s">
         <v>18</v>
@@ -6943,7 +6947,7 @@
         <v>478</v>
       </c>
       <c r="C274" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D274" s="20" t="s">
         <v>18</v>
@@ -6952,7 +6956,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A275" s="18" t="s">
         <v>15</v>
       </c>
@@ -6960,7 +6964,7 @@
         <v>478</v>
       </c>
       <c r="C275" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D275" s="20" t="s">
         <v>18</v>
@@ -6977,7 +6981,7 @@
         <v>478</v>
       </c>
       <c r="C276" s="19" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D276" s="20" t="s">
         <v>18</v>
@@ -6986,7 +6990,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A277" s="18" t="s">
         <v>15</v>
       </c>
@@ -6994,7 +6998,7 @@
         <v>478</v>
       </c>
       <c r="C277" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D277" s="20" t="s">
         <v>18</v>
@@ -7003,7 +7007,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="14.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A278" s="18" t="s">
         <v>15</v>
       </c>
@@ -7011,7 +7015,7 @@
         <v>478</v>
       </c>
       <c r="C278" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D278" s="20" t="s">
         <v>18</v>
@@ -7020,7 +7024,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="14.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A279" s="18" t="s">
         <v>15</v>
       </c>
@@ -7028,7 +7032,7 @@
         <v>478</v>
       </c>
       <c r="C279" s="19" t="s">
-        <v>500</v>
+        <v>96</v>
       </c>
       <c r="D279" s="20" t="s">
         <v>18</v>
@@ -7037,7 +7041,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A280" s="18" t="s">
         <v>15</v>
       </c>
@@ -7045,7 +7049,7 @@
         <v>478</v>
       </c>
       <c r="C280" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D280" s="20" t="s">
         <v>18</v>
@@ -7054,7 +7058,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:5" ht="14.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A281" s="18" t="s">
         <v>15</v>
       </c>
@@ -7062,7 +7066,7 @@
         <v>478</v>
       </c>
       <c r="C281" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D281" s="20" t="s">
         <v>18</v>
@@ -7071,7 +7075,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:5" ht="14.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A282" s="18" t="s">
         <v>15</v>
       </c>
@@ -7079,7 +7083,7 @@
         <v>478</v>
       </c>
       <c r="C282" s="19" t="s">
-        <v>102</v>
+        <v>500</v>
       </c>
       <c r="D282" s="20" t="s">
         <v>18</v>
@@ -7096,7 +7100,7 @@
         <v>478</v>
       </c>
       <c r="C283" s="19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D283" s="20" t="s">
         <v>18</v>
@@ -7105,7 +7109,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A284" s="18" t="s">
         <v>15</v>
       </c>
@@ -7113,7 +7117,7 @@
         <v>478</v>
       </c>
       <c r="C284" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D284" s="20" t="s">
         <v>18</v>
@@ -7130,7 +7134,7 @@
         <v>478</v>
       </c>
       <c r="C285" s="19" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D285" s="20" t="s">
         <v>18</v>
@@ -7147,7 +7151,7 @@
         <v>478</v>
       </c>
       <c r="C286" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D286" s="20" t="s">
         <v>18</v>
@@ -7156,7 +7160,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A287" s="18" t="s">
         <v>15</v>
       </c>
@@ -7164,7 +7168,7 @@
         <v>478</v>
       </c>
       <c r="C287" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D287" s="20" t="s">
         <v>18</v>
@@ -7181,7 +7185,7 @@
         <v>478</v>
       </c>
       <c r="C288" s="19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D288" s="20" t="s">
         <v>18</v>
@@ -7198,7 +7202,7 @@
         <v>478</v>
       </c>
       <c r="C289" s="19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D289" s="20" t="s">
         <v>18</v>
@@ -7215,7 +7219,7 @@
         <v>478</v>
       </c>
       <c r="C290" s="19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D290" s="20" t="s">
         <v>18</v>
@@ -7232,7 +7236,7 @@
         <v>478</v>
       </c>
       <c r="C291" s="19" t="s">
-        <v>501</v>
+        <v>108</v>
       </c>
       <c r="D291" s="20" t="s">
         <v>18</v>
@@ -7249,7 +7253,7 @@
         <v>478</v>
       </c>
       <c r="C292" s="19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D292" s="20" t="s">
         <v>18</v>
@@ -7266,7 +7270,7 @@
         <v>478</v>
       </c>
       <c r="C293" s="19" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D293" s="20" t="s">
         <v>18</v>
@@ -7283,7 +7287,7 @@
         <v>478</v>
       </c>
       <c r="C294" s="19" t="s">
-        <v>114</v>
+        <v>501</v>
       </c>
       <c r="D294" s="20" t="s">
         <v>18</v>
@@ -7300,7 +7304,7 @@
         <v>478</v>
       </c>
       <c r="C295" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D295" s="20" t="s">
         <v>18</v>
@@ -7317,7 +7321,7 @@
         <v>478</v>
       </c>
       <c r="C296" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D296" s="20" t="s">
         <v>18</v>
@@ -7334,7 +7338,7 @@
         <v>478</v>
       </c>
       <c r="C297" s="19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D297" s="20" t="s">
         <v>18</v>
@@ -7351,7 +7355,7 @@
         <v>478</v>
       </c>
       <c r="C298" s="19" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D298" s="20" t="s">
         <v>18</v>
@@ -7368,7 +7372,7 @@
         <v>478</v>
       </c>
       <c r="C299" s="19" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D299" s="20" t="s">
         <v>18</v>
@@ -7385,7 +7389,7 @@
         <v>478</v>
       </c>
       <c r="C300" s="19" t="s">
-        <v>502</v>
+        <v>117</v>
       </c>
       <c r="D300" s="20" t="s">
         <v>18</v>
@@ -7394,7 +7398,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A301" s="18" t="s">
         <v>15</v>
       </c>
@@ -7402,7 +7406,7 @@
         <v>478</v>
       </c>
       <c r="C301" s="19" t="s">
-        <v>503</v>
+        <v>118</v>
       </c>
       <c r="D301" s="20" t="s">
         <v>18</v>
@@ -7419,7 +7423,7 @@
         <v>478</v>
       </c>
       <c r="C302" s="19" t="s">
-        <v>504</v>
+        <v>119</v>
       </c>
       <c r="D302" s="20" t="s">
         <v>18</v>
@@ -7436,7 +7440,7 @@
         <v>478</v>
       </c>
       <c r="C303" s="19" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D303" s="20" t="s">
         <v>18</v>
@@ -7445,7 +7449,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A304" s="18" t="s">
         <v>15</v>
       </c>
@@ -7453,7 +7457,7 @@
         <v>478</v>
       </c>
       <c r="C304" s="19" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D304" s="20" t="s">
         <v>18</v>
@@ -7470,7 +7474,7 @@
         <v>478</v>
       </c>
       <c r="C305" s="19" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D305" s="20" t="s">
         <v>18</v>
@@ -7487,7 +7491,7 @@
         <v>478</v>
       </c>
       <c r="C306" s="19" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D306" s="20" t="s">
         <v>18</v>
@@ -7504,7 +7508,7 @@
         <v>478</v>
       </c>
       <c r="C307" s="19" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D307" s="20" t="s">
         <v>18</v>
@@ -7521,7 +7525,7 @@
         <v>478</v>
       </c>
       <c r="C308" s="19" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D308" s="20" t="s">
         <v>18</v>
@@ -7538,7 +7542,7 @@
         <v>478</v>
       </c>
       <c r="C309" s="19" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D309" s="20" t="s">
         <v>18</v>
@@ -7555,7 +7559,7 @@
         <v>478</v>
       </c>
       <c r="C310" s="19" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D310" s="20" t="s">
         <v>18</v>
@@ -7572,7 +7576,7 @@
         <v>478</v>
       </c>
       <c r="C311" s="19" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D311" s="20" t="s">
         <v>18</v>
@@ -7589,7 +7593,7 @@
         <v>478</v>
       </c>
       <c r="C312" s="19" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D312" s="20" t="s">
         <v>18</v>
@@ -7606,7 +7610,7 @@
         <v>478</v>
       </c>
       <c r="C313" s="19" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D313" s="20" t="s">
         <v>18</v>
@@ -7623,7 +7627,7 @@
         <v>478</v>
       </c>
       <c r="C314" s="19" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D314" s="20" t="s">
         <v>18</v>
@@ -7640,7 +7644,7 @@
         <v>478</v>
       </c>
       <c r="C315" s="19" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D315" s="20" t="s">
         <v>18</v>
@@ -7657,7 +7661,7 @@
         <v>478</v>
       </c>
       <c r="C316" s="19" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D316" s="20" t="s">
         <v>18</v>
@@ -7674,7 +7678,7 @@
         <v>478</v>
       </c>
       <c r="C317" s="19" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D317" s="20" t="s">
         <v>18</v>
@@ -7691,7 +7695,7 @@
         <v>478</v>
       </c>
       <c r="C318" s="19" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D318" s="20" t="s">
         <v>18</v>
@@ -7708,7 +7712,7 @@
         <v>478</v>
       </c>
       <c r="C319" s="19" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D319" s="20" t="s">
         <v>18</v>
@@ -7725,7 +7729,7 @@
         <v>478</v>
       </c>
       <c r="C320" s="19" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D320" s="20" t="s">
         <v>18</v>
@@ -7742,7 +7746,7 @@
         <v>478</v>
       </c>
       <c r="C321" s="19" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D321" s="20" t="s">
         <v>18</v>
@@ -7759,7 +7763,7 @@
         <v>478</v>
       </c>
       <c r="C322" s="19" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D322" s="20" t="s">
         <v>18</v>
@@ -7776,7 +7780,7 @@
         <v>478</v>
       </c>
       <c r="C323" s="19" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D323" s="20" t="s">
         <v>18</v>
@@ -7793,7 +7797,7 @@
         <v>478</v>
       </c>
       <c r="C324" s="19" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D324" s="20" t="s">
         <v>18</v>
@@ -7810,7 +7814,7 @@
         <v>478</v>
       </c>
       <c r="C325" s="19" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D325" s="20" t="s">
         <v>18</v>
@@ -7827,7 +7831,7 @@
         <v>478</v>
       </c>
       <c r="C326" s="19" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D326" s="20" t="s">
         <v>18</v>
@@ -7837,217 +7841,216 @@
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A327" s="24" t="s">
+      <c r="A327" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B327" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C327" s="19" t="s">
+        <v>526</v>
+      </c>
+      <c r="D327" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E327" s="21">
+        <v>306.2</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A328" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B328" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C328" s="19" t="s">
+        <v>527</v>
+      </c>
+      <c r="D328" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E328" s="21">
+        <v>306.2</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A329" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B329" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C329" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="D329" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E329" s="21">
+        <v>306.2</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A330" s="24" t="s">
         <v>499</v>
       </c>
-      <c r="B327" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C327" s="22" t="s">
+      <c r="B330" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C330" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="D327" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E327" s="21">
+      <c r="D330" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E330" s="21">
         <v>8.7617627530354198</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A328" s="24" t="s">
-        <v>461</v>
-      </c>
-      <c r="B328" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C328" s="23" t="s">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A331" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="B331" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C331" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D328" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E328" s="21">
+      <c r="D331" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E331" s="21">
         <f>1.83271287591511+0.699355765772355+23.6965393660799</f>
         <v>26.228608007767363</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A329" s="24" t="s">
-        <v>461</v>
-      </c>
-      <c r="B329" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C329" s="23" t="s">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A332" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="B332" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C332" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D329" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E329" s="21">
+      <c r="D332" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E332" s="21">
         <f>0.794035881175228+0.259790348838566+6.53631669485161+8.71621621621622</f>
         <v>16.306359141081622</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A330" s="51" t="s">
+    <row r="333" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A333" s="51" t="s">
         <v>499</v>
       </c>
-      <c r="B330" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C330" s="52" t="s">
+      <c r="B333" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C333" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="D330" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="E330" s="54">
+      <c r="D333" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="E333" s="54">
         <f>9.31371545207318</f>
         <v>9.3137154520731809</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A331" s="64" t="s">
+    <row r="334" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A334" s="64" t="s">
         <v>499</v>
       </c>
-      <c r="B331" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C331" s="22" t="s">
+      <c r="B334" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C334" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="D331" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E331" s="21">
+      <c r="D334" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E334" s="21">
         <v>8.7617627530354198</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A332" s="65" t="s">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A335" s="65" t="s">
         <v>499</v>
       </c>
-      <c r="B332" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C332" s="23" t="s">
+      <c r="B335" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C335" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="D332" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E332" s="21">
+      <c r="D335" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E335" s="21">
         <f>9.31371545207318</f>
         <v>9.3137154520731809</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A333" s="24" t="s">
-        <v>461</v>
-      </c>
-      <c r="B333" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C333" s="23" t="s">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A336" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="B336" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C336" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="D333" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E333" s="21">
+      <c r="D336" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E336" s="21">
         <f>1.83271287591511+0.699355765772355+23.6965393660799</f>
         <v>26.228608007767363</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A334" s="24" t="s">
-        <v>461</v>
-      </c>
-      <c r="B334" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C334" s="23" t="s">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A337" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="B337" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C337" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="D334" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E334" s="21">
+      <c r="D337" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E337" s="21">
         <f>1.83271287591511+0.699355765772355+23.6965393660799</f>
         <v>26.228608007767363</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A335" s="24" t="s">
-        <v>461</v>
-      </c>
-      <c r="B335" s="66" t="s">
-        <v>478</v>
-      </c>
-      <c r="C335" s="23" t="s">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A338" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="B338" s="66" t="s">
+        <v>478</v>
+      </c>
+      <c r="C338" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="D335" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E335" s="21">
+      <c r="D338" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E338" s="21">
         <f>1.83271287591511+0.699355765772355+23.6965393660799</f>
         <v>26.228608007767363</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A336" s="24" t="s">
-        <v>461</v>
-      </c>
-      <c r="B336" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C336" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="D336" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E336" s="21">
-        <f t="shared" ref="E336" si="1">0.794035881175228+0.259790348838566+6.53631669485161+8.71621621621622</f>
-        <v>16.306359141081622</v>
-      </c>
-    </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A337" s="24" t="s">
-        <v>461</v>
-      </c>
-      <c r="B337" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C337" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="D337" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="E337" s="24">
-        <v>0.47448299012375972</v>
-      </c>
-    </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A338" s="24" t="s">
-        <v>461</v>
-      </c>
-      <c r="B338" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="C338" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="D338" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="E338" s="24">
-        <v>0.47448299012375972</v>
-      </c>
-    </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A339" s="24" t="s">
         <v>461</v>
@@ -8055,14 +8058,15 @@
       <c r="B339" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="C339" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="D339" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="E339" s="24">
-        <v>0.47448299012375972</v>
+      <c r="C339" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="D339" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E339" s="21">
+        <f t="shared" ref="E339" si="1">0.794035881175228+0.259790348838566+6.53631669485161+8.71621621621622</f>
+        <v>16.306359141081622</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.4">
@@ -8073,7 +8077,7 @@
         <v>478</v>
       </c>
       <c r="C340" s="24" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D340" s="24" t="s">
         <v>8</v>
@@ -8090,7 +8094,7 @@
         <v>478</v>
       </c>
       <c r="C341" s="24" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D341" s="24" t="s">
         <v>8</v>
@@ -8107,7 +8111,7 @@
         <v>478</v>
       </c>
       <c r="C342" s="24" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D342" s="24" t="s">
         <v>8</v>
@@ -8124,7 +8128,7 @@
         <v>478</v>
       </c>
       <c r="C343" s="24" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D343" s="24" t="s">
         <v>8</v>
@@ -8141,7 +8145,7 @@
         <v>478</v>
       </c>
       <c r="C344" s="24" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D344" s="24" t="s">
         <v>8</v>
@@ -8158,7 +8162,7 @@
         <v>478</v>
       </c>
       <c r="C345" s="24" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D345" s="24" t="s">
         <v>8</v>
@@ -8175,13 +8179,13 @@
         <v>478</v>
       </c>
       <c r="C346" s="24" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D346" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E346" s="24">
-        <v>7.0137417235817956E-2</v>
+        <v>0.47448299012375972</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.4">
@@ -8192,13 +8196,13 @@
         <v>478</v>
       </c>
       <c r="C347" s="24" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D347" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E347" s="24">
-        <v>7.0137417235817956E-2</v>
+        <v>0.47448299012375972</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.4">
@@ -8209,13 +8213,13 @@
         <v>478</v>
       </c>
       <c r="C348" s="24" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D348" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E348" s="24">
-        <v>7.0137417235817956E-2</v>
+        <v>0.47448299012375972</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.4">
@@ -8226,7 +8230,7 @@
         <v>478</v>
       </c>
       <c r="C349" s="24" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D349" s="24" t="s">
         <v>8</v>
@@ -8243,13 +8247,13 @@
         <v>478</v>
       </c>
       <c r="C350" s="24" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="D350" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E350" s="24">
-        <v>3.3662903906841443E-2</v>
+        <v>7.0137417235817956E-2</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.4">
@@ -8260,13 +8264,13 @@
         <v>478</v>
       </c>
       <c r="C351" s="24" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="D351" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E351" s="24">
-        <v>3.3662903906841443E-2</v>
+        <v>7.0137417235817956E-2</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.4">
@@ -8277,13 +8281,13 @@
         <v>478</v>
       </c>
       <c r="C352" s="24" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="D352" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E352" s="24">
-        <v>3.3662903906841443E-2</v>
+        <v>7.0137417235817956E-2</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.4">
@@ -8294,7 +8298,7 @@
         <v>478</v>
       </c>
       <c r="C353" s="24" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D353" s="24" t="s">
         <v>8</v>
@@ -8311,7 +8315,7 @@
         <v>478</v>
       </c>
       <c r="C354" s="24" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D354" s="24" t="s">
         <v>8</v>
@@ -8328,7 +8332,7 @@
         <v>478</v>
       </c>
       <c r="C355" s="24" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D355" s="24" t="s">
         <v>8</v>
@@ -8337,7 +8341,7 @@
         <v>3.3662903906841443E-2</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A356" s="24" t="s">
         <v>461</v>
       </c>
@@ -8345,7 +8349,7 @@
         <v>478</v>
       </c>
       <c r="C356" s="24" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D356" s="24" t="s">
         <v>8</v>
@@ -8362,7 +8366,7 @@
         <v>478</v>
       </c>
       <c r="C357" s="24" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D357" s="24" t="s">
         <v>8</v>
@@ -8379,7 +8383,7 @@
         <v>478</v>
       </c>
       <c r="C358" s="24" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D358" s="24" t="s">
         <v>8</v>
@@ -8388,7 +8392,7 @@
         <v>3.3662903906841443E-2</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A359" s="24" t="s">
         <v>461</v>
       </c>
@@ -8396,7 +8400,7 @@
         <v>478</v>
       </c>
       <c r="C359" s="24" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D359" s="24" t="s">
         <v>8</v>
@@ -8413,7 +8417,7 @@
         <v>478</v>
       </c>
       <c r="C360" s="24" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D360" s="24" t="s">
         <v>8</v>
@@ -8430,7 +8434,7 @@
         <v>478</v>
       </c>
       <c r="C361" s="24" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D361" s="24" t="s">
         <v>8</v>
@@ -8447,7 +8451,7 @@
         <v>478</v>
       </c>
       <c r="C362" s="24" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D362" s="24" t="s">
         <v>8</v>
@@ -8464,7 +8468,7 @@
         <v>478</v>
       </c>
       <c r="C363" s="24" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D363" s="24" t="s">
         <v>8</v>
@@ -8481,7 +8485,7 @@
         <v>478</v>
       </c>
       <c r="C364" s="24" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D364" s="24" t="s">
         <v>8</v>
@@ -8498,7 +8502,7 @@
         <v>478</v>
       </c>
       <c r="C365" s="24" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D365" s="24" t="s">
         <v>8</v>
@@ -8515,7 +8519,7 @@
         <v>478</v>
       </c>
       <c r="C366" s="24" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D366" s="24" t="s">
         <v>8</v>
@@ -8532,7 +8536,7 @@
         <v>478</v>
       </c>
       <c r="C367" s="24" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D367" s="24" t="s">
         <v>8</v>
@@ -8549,7 +8553,7 @@
         <v>478</v>
       </c>
       <c r="C368" s="24" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D368" s="24" t="s">
         <v>8</v>
@@ -8566,13 +8570,13 @@
         <v>478</v>
       </c>
       <c r="C369" s="24" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="D369" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E369" s="24">
-        <v>185.69758349435509</v>
+        <v>3.3662903906841443E-2</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.4">
@@ -8583,13 +8587,13 @@
         <v>478</v>
       </c>
       <c r="C370" s="24" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D370" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E370" s="24">
-        <v>185.69758349435509</v>
+        <v>3.3662903906841443E-2</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.4">
@@ -8600,13 +8604,13 @@
         <v>478</v>
       </c>
       <c r="C371" s="24" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D371" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E371" s="24">
-        <v>185.69758349435509</v>
+        <v>3.3662903906841443E-2</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.4">
@@ -8617,7 +8621,7 @@
         <v>478</v>
       </c>
       <c r="C372" s="24" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D372" s="24" t="s">
         <v>8</v>
@@ -8634,7 +8638,7 @@
         <v>478</v>
       </c>
       <c r="C373" s="24" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D373" s="24" t="s">
         <v>8</v>
@@ -8651,7 +8655,7 @@
         <v>478</v>
       </c>
       <c r="C374" s="24" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D374" s="24" t="s">
         <v>8</v>
@@ -8668,7 +8672,7 @@
         <v>478</v>
       </c>
       <c r="C375" s="24" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D375" s="24" t="s">
         <v>8</v>
@@ -8685,7 +8689,7 @@
         <v>478</v>
       </c>
       <c r="C376" s="24" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D376" s="24" t="s">
         <v>8</v>
@@ -8702,7 +8706,7 @@
         <v>478</v>
       </c>
       <c r="C377" s="24" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D377" s="24" t="s">
         <v>8</v>
@@ -8719,7 +8723,7 @@
         <v>478</v>
       </c>
       <c r="C378" s="24" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D378" s="24" t="s">
         <v>8</v>
@@ -8736,7 +8740,7 @@
         <v>478</v>
       </c>
       <c r="C379" s="24" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D379" s="24" t="s">
         <v>8</v>
@@ -8753,7 +8757,7 @@
         <v>478</v>
       </c>
       <c r="C380" s="24" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D380" s="24" t="s">
         <v>8</v>
@@ -8770,7 +8774,7 @@
         <v>478</v>
       </c>
       <c r="C381" s="24" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D381" s="24" t="s">
         <v>8</v>
@@ -8787,7 +8791,7 @@
         <v>478</v>
       </c>
       <c r="C382" s="24" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D382" s="24" t="s">
         <v>8</v>
@@ -8804,13 +8808,13 @@
         <v>478</v>
       </c>
       <c r="C383" s="24" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D383" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E383" s="24">
-        <v>3047.4121773829488</v>
+        <v>185.69758349435509</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.4">
@@ -8821,13 +8825,13 @@
         <v>478</v>
       </c>
       <c r="C384" s="24" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D384" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E384" s="24">
-        <v>3047.4121773829488</v>
+        <v>185.69758349435509</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.4">
@@ -8838,13 +8842,13 @@
         <v>478</v>
       </c>
       <c r="C385" s="24" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D385" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E385" s="24">
-        <v>3047.4121773829488</v>
+        <v>185.69758349435509</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.4">
@@ -8855,7 +8859,7 @@
         <v>478</v>
       </c>
       <c r="C386" s="24" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D386" s="24" t="s">
         <v>8</v>
@@ -8872,7 +8876,7 @@
         <v>478</v>
       </c>
       <c r="C387" s="24" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D387" s="24" t="s">
         <v>8</v>
@@ -8889,7 +8893,7 @@
         <v>478</v>
       </c>
       <c r="C388" s="24" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D388" s="24" t="s">
         <v>8</v>
@@ -8906,7 +8910,7 @@
         <v>478</v>
       </c>
       <c r="C389" s="24" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D389" s="24" t="s">
         <v>8</v>
@@ -8923,7 +8927,7 @@
         <v>478</v>
       </c>
       <c r="C390" s="24" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D390" s="24" t="s">
         <v>8</v>
@@ -8940,13 +8944,13 @@
         <v>478</v>
       </c>
       <c r="C391" s="24" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D391" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E391" s="24">
-        <v>3528.885850254635</v>
+        <v>3047.4121773829488</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.4">
@@ -8957,13 +8961,13 @@
         <v>478</v>
       </c>
       <c r="C392" s="24" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D392" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E392" s="24">
-        <v>3528.885850254635</v>
+        <v>3047.4121773829488</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.4">
@@ -8974,13 +8978,13 @@
         <v>478</v>
       </c>
       <c r="C393" s="24" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D393" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E393" s="24">
-        <v>3528.885850254635</v>
+        <v>3047.4121773829488</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.4">
@@ -8991,7 +8995,7 @@
         <v>478</v>
       </c>
       <c r="C394" s="24" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D394" s="24" t="s">
         <v>8</v>
@@ -9008,7 +9012,7 @@
         <v>478</v>
       </c>
       <c r="C395" s="24" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D395" s="24" t="s">
         <v>8</v>
@@ -9025,7 +9029,7 @@
         <v>478</v>
       </c>
       <c r="C396" s="24" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D396" s="24" t="s">
         <v>8</v>
@@ -9042,7 +9046,7 @@
         <v>478</v>
       </c>
       <c r="C397" s="24" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D397" s="24" t="s">
         <v>8</v>
@@ -9059,7 +9063,7 @@
         <v>478</v>
       </c>
       <c r="C398" s="24" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D398" s="24" t="s">
         <v>8</v>
@@ -9076,13 +9080,13 @@
         <v>478</v>
       </c>
       <c r="C399" s="24" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D399" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E399" s="24">
-        <v>0.29887053900547389</v>
+        <v>3528.885850254635</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.4">
@@ -9093,13 +9097,13 @@
         <v>478</v>
       </c>
       <c r="C400" s="24" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D400" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E400" s="24">
-        <v>0.29887053900547389</v>
+        <v>3528.885850254635</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.4">
@@ -9110,13 +9114,13 @@
         <v>478</v>
       </c>
       <c r="C401" s="24" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D401" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E401" s="24">
-        <v>0.29887053900547389</v>
+        <v>3528.885850254635</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.4">
@@ -9127,7 +9131,7 @@
         <v>478</v>
       </c>
       <c r="C402" s="24" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D402" s="24" t="s">
         <v>8</v>
@@ -9144,13 +9148,13 @@
         <v>478</v>
       </c>
       <c r="C403" s="24" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D403" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E403" s="24">
-        <v>5.1888755947493877E-3</v>
+        <v>0.29887053900547389</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.4">
@@ -9161,13 +9165,13 @@
         <v>478</v>
       </c>
       <c r="C404" s="24" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D404" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E404" s="24">
-        <v>5.1888755947493877E-3</v>
+        <v>0.29887053900547389</v>
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.4">
@@ -9178,13 +9182,13 @@
         <v>478</v>
       </c>
       <c r="C405" s="24" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D405" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E405" s="24">
-        <v>5.1888755947493877E-3</v>
+        <v>0.29887053900547389</v>
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.4">
@@ -9195,7 +9199,7 @@
         <v>478</v>
       </c>
       <c r="C406" s="24" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D406" s="24" t="s">
         <v>8</v>
@@ -9212,7 +9216,7 @@
         <v>478</v>
       </c>
       <c r="C407" s="24" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D407" s="24" t="s">
         <v>8</v>
@@ -9229,7 +9233,7 @@
         <v>478</v>
       </c>
       <c r="C408" s="24" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D408" s="24" t="s">
         <v>8</v>
@@ -9246,7 +9250,7 @@
         <v>478</v>
       </c>
       <c r="C409" s="24" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D409" s="24" t="s">
         <v>8</v>
@@ -9263,7 +9267,7 @@
         <v>478</v>
       </c>
       <c r="C410" s="24" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D410" s="24" t="s">
         <v>8</v>
@@ -9280,7 +9284,7 @@
         <v>478</v>
       </c>
       <c r="C411" s="24" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D411" s="24" t="s">
         <v>8</v>
@@ -9297,7 +9301,7 @@
         <v>478</v>
       </c>
       <c r="C412" s="24" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D412" s="24" t="s">
         <v>8</v>
@@ -9314,7 +9318,7 @@
         <v>478</v>
       </c>
       <c r="C413" s="24" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D413" s="24" t="s">
         <v>8</v>
@@ -9331,7 +9335,7 @@
         <v>478</v>
       </c>
       <c r="C414" s="24" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D414" s="24" t="s">
         <v>8</v>
@@ -9348,7 +9352,7 @@
         <v>478</v>
       </c>
       <c r="C415" s="24" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D415" s="24" t="s">
         <v>8</v>
@@ -9365,7 +9369,7 @@
         <v>478</v>
       </c>
       <c r="C416" s="24" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D416" s="24" t="s">
         <v>8</v>
@@ -9382,13 +9386,13 @@
         <v>478</v>
       </c>
       <c r="C417" s="24" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D417" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E417" s="24">
-        <v>2.5277027027027019</v>
+        <v>5.1888755947493877E-3</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.4">
@@ -9399,13 +9403,13 @@
         <v>478</v>
       </c>
       <c r="C418" s="24" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D418" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E418" s="24">
-        <v>2.5277027027027019</v>
+        <v>5.1888755947493877E-3</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.4">
@@ -9416,13 +9420,13 @@
         <v>478</v>
       </c>
       <c r="C419" s="24" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D419" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E419" s="24">
-        <v>2.5277027027027019</v>
+        <v>5.1888755947493877E-3</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.4">
@@ -9433,7 +9437,7 @@
         <v>478</v>
       </c>
       <c r="C420" s="24" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D420" s="24" t="s">
         <v>8</v>
@@ -9450,7 +9454,7 @@
         <v>478</v>
       </c>
       <c r="C421" s="24" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D421" s="24" t="s">
         <v>8</v>
@@ -9459,7 +9463,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A422" s="24" t="s">
         <v>461</v>
       </c>
@@ -9467,7 +9471,7 @@
         <v>478</v>
       </c>
       <c r="C422" s="24" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D422" s="24" t="s">
         <v>8</v>
@@ -9476,7 +9480,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A423" s="24" t="s">
         <v>461</v>
       </c>
@@ -9484,7 +9488,7 @@
         <v>478</v>
       </c>
       <c r="C423" s="24" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D423" s="24" t="s">
         <v>8</v>
@@ -9501,7 +9505,7 @@
         <v>478</v>
       </c>
       <c r="C424" s="24" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D424" s="24" t="s">
         <v>8</v>
@@ -9510,7 +9514,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A425" s="24" t="s">
         <v>461</v>
       </c>
@@ -9518,7 +9522,7 @@
         <v>478</v>
       </c>
       <c r="C425" s="24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D425" s="24" t="s">
         <v>8</v>
@@ -9527,7 +9531,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A426" s="24" t="s">
         <v>461</v>
       </c>
@@ -9535,7 +9539,7 @@
         <v>478</v>
       </c>
       <c r="C426" s="24" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D426" s="24" t="s">
         <v>8</v>
@@ -9552,7 +9556,7 @@
         <v>478</v>
       </c>
       <c r="C427" s="24" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D427" s="24" t="s">
         <v>8</v>
@@ -9569,7 +9573,7 @@
         <v>478</v>
       </c>
       <c r="C428" s="24" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D428" s="24" t="s">
         <v>8</v>
@@ -9586,7 +9590,7 @@
         <v>478</v>
       </c>
       <c r="C429" s="24" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D429" s="24" t="s">
         <v>8</v>
@@ -9595,7 +9599,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A430" s="24" t="s">
         <v>461</v>
       </c>
@@ -9603,7 +9607,7 @@
         <v>478</v>
       </c>
       <c r="C430" s="24" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D430" s="24" t="s">
         <v>8</v>
@@ -9612,7 +9616,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A431" s="24" t="s">
         <v>461</v>
       </c>
@@ -9620,7 +9624,7 @@
         <v>478</v>
       </c>
       <c r="C431" s="24" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D431" s="24" t="s">
         <v>8</v>
@@ -9637,7 +9641,7 @@
         <v>478</v>
       </c>
       <c r="C432" s="24" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D432" s="24" t="s">
         <v>8</v>
@@ -9646,7 +9650,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A433" s="24" t="s">
         <v>461</v>
       </c>
@@ -9654,7 +9658,7 @@
         <v>478</v>
       </c>
       <c r="C433" s="24" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D433" s="24" t="s">
         <v>8</v>
@@ -9663,7 +9667,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A434" s="24" t="s">
         <v>461</v>
       </c>
@@ -9671,7 +9675,7 @@
         <v>478</v>
       </c>
       <c r="C434" s="24" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D434" s="24" t="s">
         <v>8</v>
@@ -9680,7 +9684,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A435" s="24" t="s">
         <v>461</v>
       </c>
@@ -9688,7 +9692,7 @@
         <v>478</v>
       </c>
       <c r="C435" s="24" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D435" s="24" t="s">
         <v>8</v>
@@ -9697,7 +9701,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A436" s="24" t="s">
         <v>461</v>
       </c>
@@ -9705,7 +9709,7 @@
         <v>478</v>
       </c>
       <c r="C436" s="24" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D436" s="24" t="s">
         <v>8</v>
@@ -9714,7 +9718,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A437" s="24" t="s">
         <v>461</v>
       </c>
@@ -9722,7 +9726,7 @@
         <v>478</v>
       </c>
       <c r="C437" s="24" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D437" s="24" t="s">
         <v>8</v>
@@ -9739,7 +9743,7 @@
         <v>478</v>
       </c>
       <c r="C438" s="24" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D438" s="24" t="s">
         <v>8</v>
@@ -9756,7 +9760,7 @@
         <v>478</v>
       </c>
       <c r="C439" s="24" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D439" s="24" t="s">
         <v>8</v>
@@ -9773,7 +9777,7 @@
         <v>478</v>
       </c>
       <c r="C440" s="24" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D440" s="24" t="s">
         <v>8</v>
@@ -9782,7 +9786,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A441" s="24" t="s">
         <v>461</v>
       </c>
@@ -9790,7 +9794,7 @@
         <v>478</v>
       </c>
       <c r="C441" s="24" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D441" s="24" t="s">
         <v>8</v>
@@ -9799,7 +9803,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A442" s="24" t="s">
         <v>461</v>
       </c>
@@ -9807,7 +9811,7 @@
         <v>478</v>
       </c>
       <c r="C442" s="24" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D442" s="24" t="s">
         <v>8</v>
@@ -9816,7 +9820,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A443" s="24" t="s">
         <v>461</v>
       </c>
@@ -9824,7 +9828,7 @@
         <v>478</v>
       </c>
       <c r="C443" s="24" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D443" s="24" t="s">
         <v>8</v>
@@ -9841,7 +9845,7 @@
         <v>478</v>
       </c>
       <c r="C444" s="24" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D444" s="24" t="s">
         <v>8</v>
@@ -9858,7 +9862,7 @@
         <v>478</v>
       </c>
       <c r="C445" s="24" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D445" s="24" t="s">
         <v>8</v>
@@ -9875,7 +9879,7 @@
         <v>478</v>
       </c>
       <c r="C446" s="24" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D446" s="24" t="s">
         <v>8</v>
@@ -9892,7 +9896,7 @@
         <v>478</v>
       </c>
       <c r="C447" s="24" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D447" s="24" t="s">
         <v>8</v>
@@ -9909,7 +9913,7 @@
         <v>478</v>
       </c>
       <c r="C448" s="24" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D448" s="24" t="s">
         <v>8</v>
@@ -9926,7 +9930,7 @@
         <v>478</v>
       </c>
       <c r="C449" s="24" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D449" s="24" t="s">
         <v>8</v>
@@ -9943,7 +9947,7 @@
         <v>478</v>
       </c>
       <c r="C450" s="24" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D450" s="24" t="s">
         <v>8</v>
@@ -9960,7 +9964,7 @@
         <v>478</v>
       </c>
       <c r="C451" s="24" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D451" s="24" t="s">
         <v>8</v>
@@ -9969,7 +9973,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A452" s="24" t="s">
         <v>461</v>
       </c>
@@ -9977,7 +9981,7 @@
         <v>478</v>
       </c>
       <c r="C452" s="24" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D452" s="24" t="s">
         <v>8</v>
@@ -9994,7 +9998,7 @@
         <v>478</v>
       </c>
       <c r="C453" s="24" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D453" s="24" t="s">
         <v>8</v>
@@ -10011,7 +10015,7 @@
         <v>478</v>
       </c>
       <c r="C454" s="24" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D454" s="24" t="s">
         <v>8</v>
@@ -10020,7 +10024,7 @@
         <v>2.5277027027027019</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A455" s="24" t="s">
         <v>461</v>
       </c>
@@ -10028,7 +10032,7 @@
         <v>478</v>
       </c>
       <c r="C455" s="24" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D455" s="24" t="s">
         <v>8</v>
@@ -10045,7 +10049,7 @@
         <v>478</v>
       </c>
       <c r="C456" s="24" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D456" s="24" t="s">
         <v>8</v>
@@ -10062,7 +10066,7 @@
         <v>478</v>
       </c>
       <c r="C457" s="24" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D457" s="24" t="s">
         <v>8</v>
@@ -10079,7 +10083,7 @@
         <v>478</v>
       </c>
       <c r="C458" s="24" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D458" s="24" t="s">
         <v>8</v>
@@ -10096,7 +10100,7 @@
         <v>478</v>
       </c>
       <c r="C459" s="24" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D459" s="24" t="s">
         <v>8</v>
@@ -10113,7 +10117,7 @@
         <v>478</v>
       </c>
       <c r="C460" s="24" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D460" s="24" t="s">
         <v>8</v>
@@ -10130,7 +10134,7 @@
         <v>478</v>
       </c>
       <c r="C461" s="24" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D461" s="24" t="s">
         <v>8</v>
@@ -10147,7 +10151,7 @@
         <v>478</v>
       </c>
       <c r="C462" s="24" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D462" s="24" t="s">
         <v>8</v>
@@ -10164,7 +10168,7 @@
         <v>478</v>
       </c>
       <c r="C463" s="24" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D463" s="24" t="s">
         <v>8</v>
@@ -10181,7 +10185,7 @@
         <v>478</v>
       </c>
       <c r="C464" s="24" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D464" s="24" t="s">
         <v>8</v>
@@ -10198,13 +10202,13 @@
         <v>478</v>
       </c>
       <c r="C465" s="24" t="s">
-        <v>168</v>
+        <v>355</v>
       </c>
       <c r="D465" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E465" s="24">
-        <v>16.306359141081622</v>
+        <v>2.5277027027027019</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.4">
@@ -10215,13 +10219,13 @@
         <v>478</v>
       </c>
       <c r="C466" s="24" t="s">
-        <v>169</v>
+        <v>356</v>
       </c>
       <c r="D466" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E466" s="24">
-        <v>16.306359141081622</v>
+        <v>2.5277027027027019</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.4">
@@ -10232,13 +10236,13 @@
         <v>478</v>
       </c>
       <c r="C467" s="24" t="s">
-        <v>170</v>
+        <v>357</v>
       </c>
       <c r="D467" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E467" s="24">
-        <v>16.306359141081622</v>
+        <v>2.5277027027027019</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.4">
@@ -10249,7 +10253,7 @@
         <v>478</v>
       </c>
       <c r="C468" s="24" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D468" s="24" t="s">
         <v>8</v>
@@ -10266,7 +10270,7 @@
         <v>478</v>
       </c>
       <c r="C469" s="24" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D469" s="24" t="s">
         <v>8</v>
@@ -10283,7 +10287,7 @@
         <v>478</v>
       </c>
       <c r="C470" s="24" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D470" s="24" t="s">
         <v>8</v>
@@ -10292,7 +10296,7 @@
         <v>16.306359141081622</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A471" s="24" t="s">
         <v>461</v>
       </c>
@@ -10300,7 +10304,7 @@
         <v>478</v>
       </c>
       <c r="C471" s="24" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D471" s="24" t="s">
         <v>8</v>
@@ -10309,7 +10313,7 @@
         <v>16.306359141081622</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A472" s="24" t="s">
         <v>461</v>
       </c>
@@ -10317,7 +10321,7 @@
         <v>478</v>
       </c>
       <c r="C472" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D472" s="24" t="s">
         <v>8</v>
@@ -10334,7 +10338,7 @@
         <v>478</v>
       </c>
       <c r="C473" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D473" s="24" t="s">
         <v>8</v>
@@ -10343,7 +10347,7 @@
         <v>16.306359141081622</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A474" s="24" t="s">
         <v>461</v>
       </c>
@@ -10351,7 +10355,7 @@
         <v>478</v>
       </c>
       <c r="C474" s="24" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D474" s="24" t="s">
         <v>8</v>
@@ -10360,7 +10364,7 @@
         <v>16.306359141081622</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A475" s="24" t="s">
         <v>461</v>
       </c>
@@ -10368,7 +10372,7 @@
         <v>478</v>
       </c>
       <c r="C475" s="24" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D475" s="24" t="s">
         <v>8</v>
@@ -10385,7 +10389,7 @@
         <v>478</v>
       </c>
       <c r="C476" s="24" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D476" s="24" t="s">
         <v>8</v>
@@ -10402,7 +10406,7 @@
         <v>478</v>
       </c>
       <c r="C477" s="24" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D477" s="24" t="s">
         <v>8</v>
@@ -10419,7 +10423,7 @@
         <v>478</v>
       </c>
       <c r="C478" s="24" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D478" s="24" t="s">
         <v>8</v>
@@ -10436,7 +10440,7 @@
         <v>478</v>
       </c>
       <c r="C479" s="24" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D479" s="24" t="s">
         <v>8</v>
@@ -10453,7 +10457,7 @@
         <v>478</v>
       </c>
       <c r="C480" s="24" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D480" s="24" t="s">
         <v>8</v>
@@ -10470,7 +10474,7 @@
         <v>478</v>
       </c>
       <c r="C481" s="24" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D481" s="24" t="s">
         <v>8</v>
@@ -10487,7 +10491,7 @@
         <v>478</v>
       </c>
       <c r="C482" s="24" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D482" s="24" t="s">
         <v>8</v>
@@ -10504,7 +10508,7 @@
         <v>478</v>
       </c>
       <c r="C483" s="24" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D483" s="24" t="s">
         <v>8</v>
@@ -10521,7 +10525,7 @@
         <v>478</v>
       </c>
       <c r="C484" s="24" t="s">
-        <v>358</v>
+        <v>184</v>
       </c>
       <c r="D484" s="24" t="s">
         <v>8</v>
@@ -10538,7 +10542,7 @@
         <v>478</v>
       </c>
       <c r="C485" s="24" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D485" s="24" t="s">
         <v>8</v>
@@ -10555,7 +10559,7 @@
         <v>478</v>
       </c>
       <c r="C486" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D486" s="24" t="s">
         <v>8</v>
@@ -10572,7 +10576,7 @@
         <v>478</v>
       </c>
       <c r="C487" s="24" t="s">
-        <v>189</v>
+        <v>358</v>
       </c>
       <c r="D487" s="24" t="s">
         <v>8</v>
@@ -10589,13 +10593,13 @@
         <v>478</v>
       </c>
       <c r="C488" s="24" t="s">
-        <v>359</v>
+        <v>187</v>
       </c>
       <c r="D488" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E488" s="24">
-        <v>16.639550829227119</v>
+        <v>16.306359141081622</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.4">
@@ -10606,13 +10610,13 @@
         <v>478</v>
       </c>
       <c r="C489" s="24" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="D489" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E489" s="24">
-        <v>16.639550829227119</v>
+        <v>16.306359141081622</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.4">
@@ -10623,13 +10627,13 @@
         <v>478</v>
       </c>
       <c r="C490" s="24" t="s">
-        <v>361</v>
+        <v>189</v>
       </c>
       <c r="D490" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E490" s="24">
-        <v>16.639550829227119</v>
+        <v>16.306359141081622</v>
       </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.4">
@@ -10640,7 +10644,7 @@
         <v>478</v>
       </c>
       <c r="C491" s="24" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D491" s="24" t="s">
         <v>8</v>
@@ -10657,7 +10661,7 @@
         <v>478</v>
       </c>
       <c r="C492" s="24" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D492" s="24" t="s">
         <v>8</v>
@@ -10674,7 +10678,7 @@
         <v>478</v>
       </c>
       <c r="C493" s="24" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D493" s="24" t="s">
         <v>8</v>
@@ -10691,7 +10695,7 @@
         <v>478</v>
       </c>
       <c r="C494" s="24" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D494" s="24" t="s">
         <v>8</v>
@@ -10708,7 +10712,7 @@
         <v>478</v>
       </c>
       <c r="C495" s="24" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D495" s="24" t="s">
         <v>8</v>
@@ -10725,7 +10729,7 @@
         <v>478</v>
       </c>
       <c r="C496" s="24" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D496" s="24" t="s">
         <v>8</v>
@@ -10742,13 +10746,13 @@
         <v>478</v>
       </c>
       <c r="C497" s="24" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D497" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E497" s="24">
-        <v>2.2923648648648651</v>
+        <v>16.639550829227119</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.4">
@@ -10759,13 +10763,13 @@
         <v>478</v>
       </c>
       <c r="C498" s="24" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D498" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E498" s="24">
-        <v>2.2923648648648651</v>
+        <v>16.639550829227119</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.4">
@@ -10776,13 +10780,13 @@
         <v>478</v>
       </c>
       <c r="C499" s="24" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D499" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E499" s="24">
-        <v>2.2923648648648651</v>
+        <v>16.639550829227119</v>
       </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.4">
@@ -10793,7 +10797,7 @@
         <v>478</v>
       </c>
       <c r="C500" s="24" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D500" s="24" t="s">
         <v>8</v>
@@ -10810,7 +10814,7 @@
         <v>478</v>
       </c>
       <c r="C501" s="24" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D501" s="24" t="s">
         <v>8</v>
@@ -10827,7 +10831,7 @@
         <v>478</v>
       </c>
       <c r="C502" s="24" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D502" s="24" t="s">
         <v>8</v>
@@ -10844,7 +10848,7 @@
         <v>478</v>
       </c>
       <c r="C503" s="24" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D503" s="24" t="s">
         <v>8</v>
@@ -10861,13 +10865,13 @@
         <v>478</v>
       </c>
       <c r="C504" s="24" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D504" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E504" s="24">
-        <v>8.6578351118679522E-2</v>
+        <v>2.2923648648648651</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.4">
@@ -10878,13 +10882,13 @@
         <v>478</v>
       </c>
       <c r="C505" s="24" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D505" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E505" s="24">
-        <v>8.6578351118679522E-2</v>
+        <v>2.2923648648648651</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.4">
@@ -10895,13 +10899,13 @@
         <v>478</v>
       </c>
       <c r="C506" s="24" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D506" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E506" s="24">
-        <v>8.6578351118679522E-2</v>
+        <v>2.2923648648648651</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.4">
@@ -10912,7 +10916,7 @@
         <v>478</v>
       </c>
       <c r="C507" s="24" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D507" s="24" t="s">
         <v>8</v>
@@ -10929,7 +10933,7 @@
         <v>478</v>
       </c>
       <c r="C508" s="24" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D508" s="24" t="s">
         <v>8</v>
@@ -10946,7 +10950,7 @@
         <v>478</v>
       </c>
       <c r="C509" s="24" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D509" s="24" t="s">
         <v>8</v>
@@ -10963,13 +10967,13 @@
         <v>478</v>
       </c>
       <c r="C510" s="24" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D510" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E510" s="24">
-        <v>50.022439716030298</v>
+        <v>8.6578351118679522E-2</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.4">
@@ -10980,13 +10984,13 @@
         <v>478</v>
       </c>
       <c r="C511" s="24" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D511" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E511" s="24">
-        <v>50.022439716030298</v>
+        <v>8.6578351118679522E-2</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.4">
@@ -10997,13 +11001,13 @@
         <v>478</v>
       </c>
       <c r="C512" s="24" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D512" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E512" s="24">
-        <v>50.022439716030298</v>
+        <v>8.6578351118679522E-2</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.4">
@@ -11014,7 +11018,7 @@
         <v>478</v>
       </c>
       <c r="C513" s="24" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D513" s="24" t="s">
         <v>8</v>
@@ -11031,7 +11035,7 @@
         <v>478</v>
       </c>
       <c r="C514" s="24" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D514" s="24" t="s">
         <v>8</v>
@@ -11048,7 +11052,7 @@
         <v>478</v>
       </c>
       <c r="C515" s="24" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D515" s="24" t="s">
         <v>8</v>
@@ -11065,7 +11069,7 @@
         <v>478</v>
       </c>
       <c r="C516" s="24" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D516" s="24" t="s">
         <v>8</v>
@@ -11082,13 +11086,13 @@
         <v>478</v>
       </c>
       <c r="C517" s="24" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D517" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E517" s="24">
-        <v>5.7228812061140499E-2</v>
+        <v>50.022439716030298</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.4">
@@ -11099,13 +11103,13 @@
         <v>478</v>
       </c>
       <c r="C518" s="24" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D518" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E518" s="24">
-        <v>5.7228812061140499E-2</v>
+        <v>50.022439716030298</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.4">
@@ -11116,13 +11120,13 @@
         <v>478</v>
       </c>
       <c r="C519" s="24" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D519" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E519" s="24">
-        <v>5.7228812061140499E-2</v>
+        <v>50.022439716030298</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.4">
@@ -11133,7 +11137,7 @@
         <v>478</v>
       </c>
       <c r="C520" s="24" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D520" s="24" t="s">
         <v>8</v>
@@ -11150,7 +11154,7 @@
         <v>478</v>
       </c>
       <c r="C521" s="24" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D521" s="24" t="s">
         <v>8</v>
@@ -11167,7 +11171,7 @@
         <v>478</v>
       </c>
       <c r="C522" s="24" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D522" s="24" t="s">
         <v>8</v>
@@ -11184,7 +11188,7 @@
         <v>478</v>
       </c>
       <c r="C523" s="24" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D523" s="24" t="s">
         <v>8</v>
@@ -11201,7 +11205,7 @@
         <v>478</v>
       </c>
       <c r="C524" s="24" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D524" s="24" t="s">
         <v>8</v>
@@ -11218,7 +11222,7 @@
         <v>478</v>
       </c>
       <c r="C525" s="24" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D525" s="24" t="s">
         <v>8</v>
@@ -11235,7 +11239,7 @@
         <v>478</v>
       </c>
       <c r="C526" s="24" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D526" s="24" t="s">
         <v>8</v>
@@ -11252,7 +11256,7 @@
         <v>478</v>
       </c>
       <c r="C527" s="24" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D527" s="24" t="s">
         <v>8</v>
@@ -11269,7 +11273,7 @@
         <v>478</v>
       </c>
       <c r="C528" s="24" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D528" s="24" t="s">
         <v>8</v>
@@ -11286,7 +11290,7 @@
         <v>478</v>
       </c>
       <c r="C529" s="24" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D529" s="24" t="s">
         <v>8</v>
@@ -11303,7 +11307,7 @@
         <v>478</v>
       </c>
       <c r="C530" s="24" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D530" s="24" t="s">
         <v>8</v>
@@ -11320,7 +11324,7 @@
         <v>478</v>
       </c>
       <c r="C531" s="24" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D531" s="24" t="s">
         <v>8</v>
@@ -11337,13 +11341,13 @@
         <v>478</v>
       </c>
       <c r="C532" s="24" t="s">
-        <v>190</v>
+        <v>401</v>
       </c>
       <c r="D532" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E532" s="24">
-        <v>16.620052075727429</v>
+        <v>5.7228812061140499E-2</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.4">
@@ -11354,13 +11358,13 @@
         <v>478</v>
       </c>
       <c r="C533" s="24" t="s">
-        <v>191</v>
+        <v>402</v>
       </c>
       <c r="D533" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E533" s="24">
-        <v>16.620052075727429</v>
+        <v>5.7228812061140499E-2</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.4">
@@ -11371,13 +11375,13 @@
         <v>478</v>
       </c>
       <c r="C534" s="24" t="s">
-        <v>192</v>
+        <v>403</v>
       </c>
       <c r="D534" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E534" s="24">
-        <v>16.620052075727429</v>
+        <v>5.7228812061140499E-2</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.4">
@@ -11388,7 +11392,7 @@
         <v>478</v>
       </c>
       <c r="C535" s="24" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D535" s="24" t="s">
         <v>8</v>
@@ -11405,7 +11409,7 @@
         <v>478</v>
       </c>
       <c r="C536" s="24" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D536" s="24" t="s">
         <v>8</v>
@@ -11422,7 +11426,7 @@
         <v>478</v>
       </c>
       <c r="C537" s="24" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D537" s="24" t="s">
         <v>8</v>
@@ -11431,7 +11435,7 @@
         <v>16.620052075727429</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A538" s="24" t="s">
         <v>461</v>
       </c>
@@ -11439,7 +11443,7 @@
         <v>478</v>
       </c>
       <c r="C538" s="24" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D538" s="24" t="s">
         <v>8</v>
@@ -11448,7 +11452,7 @@
         <v>16.620052075727429</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A539" s="24" t="s">
         <v>461</v>
       </c>
@@ -11456,7 +11460,7 @@
         <v>478</v>
       </c>
       <c r="C539" s="24" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D539" s="24" t="s">
         <v>8</v>
@@ -11473,7 +11477,7 @@
         <v>478</v>
       </c>
       <c r="C540" s="24" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D540" s="24" t="s">
         <v>8</v>
@@ -11482,7 +11486,7 @@
         <v>16.620052075727429</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A541" s="24" t="s">
         <v>461</v>
       </c>
@@ -11490,7 +11494,7 @@
         <v>478</v>
       </c>
       <c r="C541" s="24" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D541" s="24" t="s">
         <v>8</v>
@@ -11499,7 +11503,7 @@
         <v>16.620052075727429</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A542" s="24" t="s">
         <v>461</v>
       </c>
@@ -11507,7 +11511,7 @@
         <v>478</v>
       </c>
       <c r="C542" s="24" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D542" s="24" t="s">
         <v>8</v>
@@ -11524,7 +11528,7 @@
         <v>478</v>
       </c>
       <c r="C543" s="24" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D543" s="24" t="s">
         <v>8</v>
@@ -11541,7 +11545,7 @@
         <v>478</v>
       </c>
       <c r="C544" s="24" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D544" s="24" t="s">
         <v>8</v>
@@ -11558,7 +11562,7 @@
         <v>478</v>
       </c>
       <c r="C545" s="24" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D545" s="24" t="s">
         <v>8</v>
@@ -11575,7 +11579,7 @@
         <v>478</v>
       </c>
       <c r="C546" s="24" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D546" s="24" t="s">
         <v>8</v>
@@ -11592,7 +11596,7 @@
         <v>478</v>
       </c>
       <c r="C547" s="24" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D547" s="24" t="s">
         <v>8</v>
@@ -11609,7 +11613,7 @@
         <v>478</v>
       </c>
       <c r="C548" s="24" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D548" s="24" t="s">
         <v>8</v>
@@ -11626,7 +11630,7 @@
         <v>478</v>
       </c>
       <c r="C549" s="24" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D549" s="24" t="s">
         <v>8</v>
@@ -11634,7 +11638,6 @@
       <c r="E549" s="24">
         <v>16.620052075727429</v>
       </c>
-      <c r="F549" s="62"/>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A550" s="24" t="s">
@@ -11644,7 +11647,7 @@
         <v>478</v>
       </c>
       <c r="C550" s="24" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D550" s="24" t="s">
         <v>8</v>
@@ -11652,7 +11655,6 @@
       <c r="E550" s="24">
         <v>16.620052075727429</v>
       </c>
-      <c r="F550" s="62"/>
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A551" s="24" t="s">
@@ -11662,7 +11664,7 @@
         <v>478</v>
       </c>
       <c r="C551" s="24" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D551" s="24" t="s">
         <v>8</v>
@@ -11670,7 +11672,6 @@
       <c r="E551" s="24">
         <v>16.620052075727429</v>
       </c>
-      <c r="F551" s="62"/>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A552" s="24" t="s">
@@ -11680,7 +11681,7 @@
         <v>478</v>
       </c>
       <c r="C552" s="24" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D552" s="24" t="s">
         <v>8</v>
@@ -11690,7 +11691,7 @@
       </c>
       <c r="F552" s="62"/>
     </row>
-    <row r="553" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A553" s="24" t="s">
         <v>461</v>
       </c>
@@ -11698,7 +11699,7 @@
         <v>478</v>
       </c>
       <c r="C553" s="24" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D553" s="24" t="s">
         <v>8</v>
@@ -11706,8 +11707,9 @@
       <c r="E553" s="24">
         <v>16.620052075727429</v>
       </c>
-    </row>
-    <row r="554" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="F553" s="62"/>
+    </row>
+    <row r="554" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A554" s="24" t="s">
         <v>461</v>
       </c>
@@ -11715,16 +11717,17 @@
         <v>478</v>
       </c>
       <c r="C554" s="24" t="s">
-        <v>405</v>
+        <v>209</v>
       </c>
       <c r="D554" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E554" s="24">
-        <v>1.200133763891887</v>
-      </c>
-    </row>
-    <row r="555" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.4">
+        <v>16.620052075727429</v>
+      </c>
+      <c r="F554" s="62"/>
+    </row>
+    <row r="555" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A555" s="24" t="s">
         <v>461</v>
       </c>
@@ -11732,15 +11735,15 @@
         <v>478</v>
       </c>
       <c r="C555" s="24" t="s">
-        <v>406</v>
+        <v>210</v>
       </c>
       <c r="D555" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E555" s="24">
-        <v>1.200133763891887</v>
-      </c>
-      <c r="F555" s="6"/>
+        <v>16.620052075727429</v>
+      </c>
+      <c r="F555" s="62"/>
     </row>
     <row r="556" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A556" s="24" t="s">
@@ -11750,15 +11753,14 @@
         <v>478</v>
       </c>
       <c r="C556" s="24" t="s">
-        <v>407</v>
+        <v>211</v>
       </c>
       <c r="D556" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E556" s="24">
-        <v>1.200133763891887</v>
-      </c>
-      <c r="F556" s="6"/>
+        <v>16.620052075727429</v>
+      </c>
     </row>
     <row r="557" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A557" s="24" t="s">
@@ -11768,7 +11770,7 @@
         <v>478</v>
       </c>
       <c r="C557" s="24" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D557" s="24" t="s">
         <v>8</v>
@@ -11776,9 +11778,8 @@
       <c r="E557" s="24">
         <v>1.200133763891887</v>
       </c>
-      <c r="F557" s="6"/>
-    </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="558" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A558" s="24" t="s">
         <v>461</v>
       </c>
@@ -11786,7 +11787,7 @@
         <v>478</v>
       </c>
       <c r="C558" s="24" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D558" s="24" t="s">
         <v>8</v>
@@ -11794,8 +11795,9 @@
       <c r="E558" s="24">
         <v>1.200133763891887</v>
       </c>
-    </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F558" s="6"/>
+    </row>
+    <row r="559" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A559" s="24" t="s">
         <v>461</v>
       </c>
@@ -11803,16 +11805,17 @@
         <v>478</v>
       </c>
       <c r="C559" s="24" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D559" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E559" s="24">
-        <v>2.2950826268293949</v>
-      </c>
-    </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1.200133763891887</v>
+      </c>
+      <c r="F559" s="6"/>
+    </row>
+    <row r="560" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A560" s="24" t="s">
         <v>461</v>
       </c>
@@ -11820,14 +11823,15 @@
         <v>478</v>
       </c>
       <c r="C560" s="24" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D560" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E560" s="24">
-        <v>2.2950826268293949</v>
-      </c>
+        <v>1.200133763891887</v>
+      </c>
+      <c r="F560" s="6"/>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A561" s="24" t="s">
@@ -11837,15 +11841,14 @@
         <v>478</v>
       </c>
       <c r="C561" s="24" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D561" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E561" s="24">
-        <v>2.2950826268293949</v>
-      </c>
-      <c r="G561" s="9"/>
+        <v>1.200133763891887</v>
+      </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A562" s="24" t="s">
@@ -11855,7 +11858,7 @@
         <v>478</v>
       </c>
       <c r="C562" s="24" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D562" s="24" t="s">
         <v>8</v>
@@ -11863,7 +11866,6 @@
       <c r="E562" s="24">
         <v>2.2950826268293949</v>
       </c>
-      <c r="G562" s="9"/>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A563" s="24" t="s">
@@ -11873,7 +11875,7 @@
         <v>478</v>
       </c>
       <c r="C563" s="24" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D563" s="24" t="s">
         <v>8</v>
@@ -11881,7 +11883,6 @@
       <c r="E563" s="24">
         <v>2.2950826268293949</v>
       </c>
-      <c r="G563" s="9"/>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A564" s="24" t="s">
@@ -11891,7 +11892,7 @@
         <v>478</v>
       </c>
       <c r="C564" s="24" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D564" s="24" t="s">
         <v>8</v>
@@ -11909,7 +11910,7 @@
         <v>478</v>
       </c>
       <c r="C565" s="24" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D565" s="24" t="s">
         <v>8</v>
@@ -11927,7 +11928,7 @@
         <v>478</v>
       </c>
       <c r="C566" s="24" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D566" s="24" t="s">
         <v>8</v>
@@ -11945,7 +11946,7 @@
         <v>478</v>
       </c>
       <c r="C567" s="24" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D567" s="24" t="s">
         <v>8</v>
@@ -11963,7 +11964,7 @@
         <v>478</v>
       </c>
       <c r="C568" s="24" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D568" s="24" t="s">
         <v>8</v>
@@ -11981,7 +11982,7 @@
         <v>478</v>
       </c>
       <c r="C569" s="24" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D569" s="24" t="s">
         <v>8</v>
@@ -11999,7 +12000,7 @@
         <v>478</v>
       </c>
       <c r="C570" s="24" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D570" s="24" t="s">
         <v>8</v>
@@ -12017,7 +12018,7 @@
         <v>478</v>
       </c>
       <c r="C571" s="24" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D571" s="24" t="s">
         <v>8</v>
@@ -12028,56 +12029,56 @@
       <c r="G571" s="9"/>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A572" s="55" t="s">
-        <v>498</v>
-      </c>
-      <c r="B572" s="56" t="s">
-        <v>477</v>
-      </c>
-      <c r="C572" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="D572" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="E572" s="59">
-        <v>3.65E-7</v>
+      <c r="A572" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="B572" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C572" s="24" t="s">
+        <v>420</v>
+      </c>
+      <c r="D572" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E572" s="24">
+        <v>2.2950826268293949</v>
       </c>
       <c r="G572" s="9"/>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A573" s="55" t="s">
-        <v>498</v>
-      </c>
-      <c r="B573" s="56" t="s">
-        <v>477</v>
-      </c>
-      <c r="C573" s="57" t="s">
-        <v>125</v>
-      </c>
-      <c r="D573" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="E573" s="59">
-        <v>2.28E-7</v>
+      <c r="A573" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="B573" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C573" s="24" t="s">
+        <v>421</v>
+      </c>
+      <c r="D573" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E573" s="24">
+        <v>2.2950826268293949</v>
       </c>
       <c r="G573" s="9"/>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A574" s="55" t="s">
-        <v>498</v>
-      </c>
-      <c r="B574" s="56" t="s">
-        <v>477</v>
-      </c>
-      <c r="C574" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="D574" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="E574" s="59">
-        <v>2.28E-7</v>
+      <c r="A574" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="B574" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C574" s="24" t="s">
+        <v>422</v>
+      </c>
+      <c r="D574" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E574" s="24">
+        <v>2.2950826268293949</v>
       </c>
       <c r="G574" s="9"/>
     </row>
@@ -12089,13 +12090,13 @@
         <v>477</v>
       </c>
       <c r="C575" s="57" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D575" s="58" t="s">
         <v>124</v>
       </c>
       <c r="E575" s="59">
-        <v>2.28E-7</v>
+        <v>3.65E-7</v>
       </c>
       <c r="G575" s="9"/>
     </row>
@@ -12107,7 +12108,7 @@
         <v>477</v>
       </c>
       <c r="C576" s="57" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D576" s="58" t="s">
         <v>124</v>
@@ -12125,7 +12126,7 @@
         <v>477</v>
       </c>
       <c r="C577" s="57" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D577" s="58" t="s">
         <v>124</v>
@@ -12143,7 +12144,7 @@
         <v>477</v>
       </c>
       <c r="C578" s="57" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D578" s="58" t="s">
         <v>124</v>
@@ -12161,7 +12162,7 @@
         <v>477</v>
       </c>
       <c r="C579" s="57" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D579" s="58" t="s">
         <v>124</v>
@@ -12169,6 +12170,7 @@
       <c r="E579" s="59">
         <v>2.28E-7</v>
       </c>
+      <c r="G579" s="9"/>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A580" s="55" t="s">
@@ -12178,14 +12180,15 @@
         <v>477</v>
       </c>
       <c r="C580" s="57" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D580" s="58" t="s">
         <v>124</v>
       </c>
       <c r="E580" s="59">
-        <v>1.2200000000000001E-7</v>
-      </c>
+        <v>2.28E-7</v>
+      </c>
+      <c r="G580" s="9"/>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A581" s="55" t="s">
@@ -12195,14 +12198,15 @@
         <v>477</v>
       </c>
       <c r="C581" s="57" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D581" s="58" t="s">
         <v>124</v>
       </c>
       <c r="E581" s="59">
-        <v>1.2200000000000001E-7</v>
-      </c>
+        <v>2.28E-7</v>
+      </c>
+      <c r="G581" s="9"/>
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A582" s="55" t="s">
@@ -12212,13 +12216,13 @@
         <v>477</v>
       </c>
       <c r="C582" s="57" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D582" s="58" t="s">
         <v>124</v>
       </c>
       <c r="E582" s="59">
-        <v>1.2200000000000001E-7</v>
+        <v>2.28E-7</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.4">
@@ -12229,7 +12233,7 @@
         <v>477</v>
       </c>
       <c r="C583" s="57" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D583" s="58" t="s">
         <v>124</v>
@@ -12246,7 +12250,7 @@
         <v>477</v>
       </c>
       <c r="C584" s="57" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D584" s="58" t="s">
         <v>124</v>
@@ -12263,7 +12267,7 @@
         <v>477</v>
       </c>
       <c r="C585" s="57" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D585" s="58" t="s">
         <v>124</v>
@@ -12280,7 +12284,7 @@
         <v>477</v>
       </c>
       <c r="C586" s="57" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D586" s="58" t="s">
         <v>124</v>
@@ -12297,7 +12301,7 @@
         <v>477</v>
       </c>
       <c r="C587" s="57" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D587" s="58" t="s">
         <v>124</v>
@@ -12314,7 +12318,7 @@
         <v>477</v>
       </c>
       <c r="C588" s="57" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D588" s="58" t="s">
         <v>124</v>
@@ -12331,7 +12335,7 @@
         <v>477</v>
       </c>
       <c r="C589" s="57" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D589" s="58" t="s">
         <v>124</v>
@@ -12348,7 +12352,7 @@
         <v>477</v>
       </c>
       <c r="C590" s="57" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D590" s="58" t="s">
         <v>124</v>
@@ -12365,7 +12369,7 @@
         <v>477</v>
       </c>
       <c r="C591" s="57" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D591" s="58" t="s">
         <v>124</v>
@@ -12382,7 +12386,7 @@
         <v>477</v>
       </c>
       <c r="C592" s="57" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D592" s="58" t="s">
         <v>124</v>
@@ -12399,13 +12403,13 @@
         <v>477</v>
       </c>
       <c r="C593" s="57" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="D593" s="58" t="s">
         <v>124</v>
       </c>
       <c r="E593" s="59">
-        <v>5.2999999999999998E-8</v>
+        <v>1.2200000000000001E-7</v>
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.4">
@@ -12416,13 +12420,13 @@
         <v>477</v>
       </c>
       <c r="C594" s="57" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="D594" s="58" t="s">
         <v>124</v>
       </c>
       <c r="E594" s="59">
-        <v>5.2999999999999998E-8</v>
+        <v>1.2200000000000001E-7</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.4">
@@ -12433,64 +12437,64 @@
         <v>477</v>
       </c>
       <c r="C595" s="57" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="D595" s="58" t="s">
         <v>124</v>
       </c>
       <c r="E595" s="59">
-        <v>5.2999999999999998E-8</v>
+        <v>1.2200000000000001E-7</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A596" s="60" t="s">
-        <v>427</v>
+      <c r="A596" s="55" t="s">
+        <v>498</v>
       </c>
       <c r="B596" s="56" t="s">
         <v>477</v>
       </c>
-      <c r="C596" s="60" t="s">
-        <v>462</v>
+      <c r="C596" s="57" t="s">
+        <v>159</v>
       </c>
       <c r="D596" s="58" t="s">
-        <v>430</v>
+        <v>124</v>
       </c>
       <c r="E596" s="59">
-        <v>5.4624999999999996E-7</v>
+        <v>5.2999999999999998E-8</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A597" s="60" t="s">
-        <v>427</v>
+      <c r="A597" s="55" t="s">
+        <v>498</v>
       </c>
       <c r="B597" s="56" t="s">
         <v>477</v>
       </c>
-      <c r="C597" s="60" t="s">
-        <v>463</v>
+      <c r="C597" s="57" t="s">
+        <v>160</v>
       </c>
       <c r="D597" s="58" t="s">
-        <v>430</v>
+        <v>124</v>
       </c>
       <c r="E597" s="59">
-        <v>4.3700000000000001E-7</v>
+        <v>5.2999999999999998E-8</v>
       </c>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A598" s="60" t="s">
-        <v>427</v>
+      <c r="A598" s="55" t="s">
+        <v>498</v>
       </c>
       <c r="B598" s="56" t="s">
         <v>477</v>
       </c>
-      <c r="C598" s="60" t="s">
-        <v>464</v>
+      <c r="C598" s="57" t="s">
+        <v>161</v>
       </c>
       <c r="D598" s="58" t="s">
-        <v>430</v>
+        <v>124</v>
       </c>
       <c r="E598" s="59">
-        <v>4.752375E-7</v>
+        <v>5.2999999999999998E-8</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.4">
@@ -12501,13 +12505,13 @@
         <v>477</v>
       </c>
       <c r="C599" s="60" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D599" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E599" s="59">
-        <v>1.0105625E-7</v>
+        <v>5.4624999999999996E-7</v>
       </c>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.4">
@@ -12518,13 +12522,13 @@
         <v>477</v>
       </c>
       <c r="C600" s="60" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D600" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E600" s="59">
-        <v>1.0105625E-7</v>
+        <v>4.3700000000000001E-7</v>
       </c>
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.4">
@@ -12535,13 +12539,13 @@
         <v>477</v>
       </c>
       <c r="C601" s="60" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D601" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E601" s="59">
-        <v>1.3656249999999999E-7</v>
+        <v>4.752375E-7</v>
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.4">
@@ -12552,13 +12556,13 @@
         <v>477</v>
       </c>
       <c r="C602" s="60" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D602" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E602" s="59">
-        <v>5.0254999999999996E-7</v>
+        <v>1.0105625E-7</v>
       </c>
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.4">
@@ -12569,13 +12573,13 @@
         <v>477</v>
       </c>
       <c r="C603" s="60" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D603" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E603" s="59">
-        <v>4.9162500000000004E-7</v>
+        <v>1.0105625E-7</v>
       </c>
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.4">
@@ -12586,13 +12590,13 @@
         <v>477</v>
       </c>
       <c r="C604" s="60" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D604" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E604" s="59">
-        <v>4.0375E-7</v>
+        <v>1.3656249999999999E-7</v>
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.4">
@@ -12603,13 +12607,13 @@
         <v>477</v>
       </c>
       <c r="C605" s="60" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D605" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E605" s="59">
-        <v>4.0375E-7</v>
+        <v>5.0254999999999996E-7</v>
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.4">
@@ -12620,13 +12624,13 @@
         <v>477</v>
       </c>
       <c r="C606" s="60" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D606" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E606" s="59">
-        <v>4.0375E-7</v>
+        <v>4.9162500000000004E-7</v>
       </c>
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.4">
@@ -12637,7 +12641,7 @@
         <v>477</v>
       </c>
       <c r="C607" s="60" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D607" s="58" t="s">
         <v>430</v>
@@ -12654,7 +12658,7 @@
         <v>477</v>
       </c>
       <c r="C608" s="60" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D608" s="58" t="s">
         <v>430</v>
@@ -12671,7 +12675,7 @@
         <v>477</v>
       </c>
       <c r="C609" s="60" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D609" s="58" t="s">
         <v>430</v>
@@ -12681,20 +12685,20 @@
       </c>
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A610" s="61" t="s">
+      <c r="A610" s="60" t="s">
         <v>427</v>
       </c>
       <c r="B610" s="56" t="s">
         <v>477</v>
       </c>
-      <c r="C610" s="61" t="s">
-        <v>476</v>
+      <c r="C610" s="60" t="s">
+        <v>473</v>
       </c>
       <c r="D610" s="58" t="s">
         <v>430</v>
       </c>
-      <c r="E610" s="63">
-        <v>3.8000000000000001E-7</v>
+      <c r="E610" s="59">
+        <v>4.0375E-7</v>
       </c>
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.4">
@@ -12705,13 +12709,13 @@
         <v>477</v>
       </c>
       <c r="C611" s="60" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="D611" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E611" s="59">
-        <v>5.4624999999999996E-7</v>
+        <v>4.0375E-7</v>
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.4">
@@ -12722,30 +12726,30 @@
         <v>477</v>
       </c>
       <c r="C612" s="60" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="D612" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E612" s="59">
-        <v>4.369999999999999E-7</v>
+        <v>4.0375E-7</v>
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A613" s="60" t="s">
+      <c r="A613" s="61" t="s">
         <v>427</v>
       </c>
       <c r="B613" s="56" t="s">
         <v>477</v>
       </c>
-      <c r="C613" s="60" t="s">
-        <v>481</v>
+      <c r="C613" s="61" t="s">
+        <v>476</v>
       </c>
       <c r="D613" s="58" t="s">
         <v>430</v>
       </c>
-      <c r="E613" s="59">
-        <v>4.7523749999999994E-7</v>
+      <c r="E613" s="63">
+        <v>3.8000000000000001E-7</v>
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.4">
@@ -12756,13 +12760,13 @@
         <v>477</v>
       </c>
       <c r="C614" s="60" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D614" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E614" s="59">
-        <v>1.0105625000000002E-7</v>
+        <v>5.4624999999999996E-7</v>
       </c>
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.4">
@@ -12773,13 +12777,13 @@
         <v>477</v>
       </c>
       <c r="C615" s="60" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D615" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E615" s="59">
-        <v>5.4624999999999996E-7</v>
+        <v>4.369999999999999E-7</v>
       </c>
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.4">
@@ -12790,13 +12794,13 @@
         <v>477</v>
       </c>
       <c r="C616" s="60" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D616" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E616" s="59">
-        <v>5.2002999999999987E-7</v>
+        <v>4.7523749999999994E-7</v>
       </c>
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.4">
@@ -12807,13 +12811,13 @@
         <v>477</v>
       </c>
       <c r="C617" s="60" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D617" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E617" s="59">
-        <v>6.6642499999999983E-8</v>
+        <v>1.0105625000000002E-7</v>
       </c>
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.4">
@@ -12823,14 +12827,14 @@
       <c r="B618" s="56" t="s">
         <v>477</v>
       </c>
-      <c r="C618" s="61" t="s">
-        <v>486</v>
+      <c r="C618" s="60" t="s">
+        <v>483</v>
       </c>
       <c r="D618" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E618" s="59">
-        <v>1.0105625000000002E-7</v>
+        <v>5.4624999999999996E-7</v>
       </c>
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.4">
@@ -12841,13 +12845,13 @@
         <v>477</v>
       </c>
       <c r="C619" s="60" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D619" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E619" s="59">
-        <v>1.0105625000000002E-7</v>
+        <v>5.2002999999999987E-7</v>
       </c>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.4">
@@ -12858,13 +12862,13 @@
         <v>477</v>
       </c>
       <c r="C620" s="60" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D620" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E620" s="59">
-        <v>1.3656249999999996E-7</v>
+        <v>6.6642499999999983E-8</v>
       </c>
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.4">
@@ -12874,14 +12878,14 @@
       <c r="B621" s="56" t="s">
         <v>477</v>
       </c>
-      <c r="C621" s="60" t="s">
-        <v>489</v>
+      <c r="C621" s="61" t="s">
+        <v>486</v>
       </c>
       <c r="D621" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E621" s="59">
-        <v>5.0254999999999996E-7</v>
+        <v>1.0105625000000002E-7</v>
       </c>
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.4">
@@ -12892,13 +12896,13 @@
         <v>477</v>
       </c>
       <c r="C622" s="60" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D622" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E622" s="59">
-        <v>2.7312499999999993E-7</v>
+        <v>1.0105625000000002E-7</v>
       </c>
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.4">
@@ -12909,13 +12913,13 @@
         <v>477</v>
       </c>
       <c r="C623" s="60" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D623" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E623" s="59">
-        <v>4.9162499999999993E-7</v>
+        <v>1.3656249999999996E-7</v>
       </c>
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.4">
@@ -12926,13 +12930,13 @@
         <v>477</v>
       </c>
       <c r="C624" s="60" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D624" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E624" s="59">
-        <v>4.6431249999999992E-7</v>
+        <v>5.0254999999999996E-7</v>
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.4">
@@ -12943,13 +12947,13 @@
         <v>477</v>
       </c>
       <c r="C625" s="60" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D625" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E625" s="59">
-        <v>4.6431249999999992E-7</v>
+        <v>2.7312499999999993E-7</v>
       </c>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.4">
@@ -12960,13 +12964,13 @@
         <v>477</v>
       </c>
       <c r="C626" s="60" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D626" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E626" s="59">
-        <v>4.0374999999999995E-7</v>
+        <v>4.9162499999999993E-7</v>
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.4">
@@ -12977,13 +12981,13 @@
         <v>477</v>
       </c>
       <c r="C627" s="60" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D627" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E627" s="59">
-        <v>3.7999999999999996E-7</v>
+        <v>4.6431249999999992E-7</v>
       </c>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.4">
@@ -12994,13 +12998,13 @@
         <v>477</v>
       </c>
       <c r="C628" s="60" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D628" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E628" s="59">
-        <v>3.7999999999999996E-7</v>
+        <v>4.6431249999999992E-7</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.4">
@@ -13011,29 +13015,80 @@
         <v>477</v>
       </c>
       <c r="C629" s="60" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D629" s="58" t="s">
         <v>430</v>
       </c>
       <c r="E629" s="59">
+        <v>4.0374999999999995E-7</v>
+      </c>
+    </row>
+    <row r="630" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A630" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B630" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C630" s="60" t="s">
+        <v>495</v>
+      </c>
+      <c r="D630" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E630" s="59">
         <v>3.7999999999999996E-7</v>
       </c>
     </row>
-    <row r="630" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A630" s="47" t="s">
+    <row r="631" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A631" s="60" t="s">
         <v>427</v>
       </c>
-      <c r="B630" s="47" t="s">
+      <c r="B631" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C631" s="60" t="s">
+        <v>496</v>
+      </c>
+      <c r="D631" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E631" s="59">
+        <v>3.7999999999999996E-7</v>
+      </c>
+    </row>
+    <row r="632" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A632" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B632" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C632" s="60" t="s">
+        <v>497</v>
+      </c>
+      <c r="D632" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E632" s="59">
+        <v>3.7999999999999996E-7</v>
+      </c>
+    </row>
+    <row r="633" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A633" s="47" t="s">
+        <v>427</v>
+      </c>
+      <c r="B633" s="47" t="s">
         <v>428</v>
       </c>
-      <c r="C630" s="48" t="s">
+      <c r="C633" s="48" t="s">
         <v>429</v>
       </c>
-      <c r="D630" s="49" t="s">
+      <c r="D633" s="49" t="s">
         <v>430</v>
       </c>
-      <c r="E630" s="50">
+      <c r="E633" s="50">
         <v>1</v>
       </c>
     </row>
@@ -13045,6 +13100,2124 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{449CF900-17C4-4908-B92C-4C3F5E0EDC6A}">
+  <dimension ref="A1:G123"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="24.69140625" style="62" customWidth="1"/>
+    <col min="2" max="2" width="23.3828125" style="62" customWidth="1"/>
+    <col min="3" max="3" width="72.921875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="9" style="62" customWidth="1"/>
+    <col min="5" max="5" width="13.23046875" style="16" customWidth="1"/>
+    <col min="6" max="6" width="9.23046875" style="62" customWidth="1"/>
+    <col min="7" max="16384" width="9.23046875" style="62"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="38" t="s">
+        <v>499</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="41">
+        <v>1.0000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" s="38" t="s">
+        <v>461</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="41">
+        <v>8.2400000000000005E-10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="38" t="s">
+        <v>461</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="41">
+        <v>6.3599999999999998E-10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" s="43" t="s">
+        <v>499</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="46">
+        <v>3E-10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="43" t="s">
+        <v>499</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="46">
+        <v>3E-10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A14" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A15" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A22" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A23" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A24" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A25" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A26" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A27" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A28" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A29" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A30" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A31" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A32" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="D32" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A33" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>520</v>
+      </c>
+      <c r="D33" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A34" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>521</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A35" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="35" t="s">
+        <v>522</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A36" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>523</v>
+      </c>
+      <c r="D36" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A37" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>524</v>
+      </c>
+      <c r="D37" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A38" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>525</v>
+      </c>
+      <c r="D38" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A39" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="D39" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A40" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>527</v>
+      </c>
+      <c r="D40" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A41" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="35" t="s">
+        <v>528</v>
+      </c>
+      <c r="D41" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A42" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="D42" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E42" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A43" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C43" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E43" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A44" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="D44" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E44" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A45" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C45" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E45" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A46" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E46" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A47" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E47" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A48" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B48" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="D48" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E48" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A49" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B49" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="D49" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E49" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A50" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B50" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="D50" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E50" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A51" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B51" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C51" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="D51" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E51" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A52" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B52" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C52" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="D52" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E52" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A53" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B53" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C53" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="D53" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E53" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A54" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B54" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C54" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="D54" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E54" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A55" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B55" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C55" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="D55" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E55" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A56" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B56" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C56" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="D56" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E56" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A57" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C57" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="D57" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E57" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A58" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C58" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="D58" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E58" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A59" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B59" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C59" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="D59" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E59" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A60" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B60" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C60" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="D60" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E60" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A61" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B61" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C61" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="D61" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E61" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A62" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B62" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C62" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="D62" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E62" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A63" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B63" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C63" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="D63" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E63" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A64" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B64" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C64" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="D64" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A65" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B65" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="C65" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="D65" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A66" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B66" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C66" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="D66" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E66" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A67" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B67" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C67" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="D67" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E67" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A68" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B68" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C68" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="D68" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E68" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A69" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B69" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="D69" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E69" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A70" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B70" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C70" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="D70" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E70" s="59">
+        <v>3.65E-7</v>
+      </c>
+      <c r="G70" s="9"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A71" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B71" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C71" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="D71" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E71" s="59">
+        <v>2.28E-7</v>
+      </c>
+      <c r="G71" s="9"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A72" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B72" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C72" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="D72" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E72" s="59">
+        <v>2.28E-7</v>
+      </c>
+      <c r="G72" s="9"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A73" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B73" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C73" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="D73" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E73" s="59">
+        <v>2.28E-7</v>
+      </c>
+      <c r="G73" s="9"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A74" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B74" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C74" s="57" t="s">
+        <v>128</v>
+      </c>
+      <c r="D74" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E74" s="59">
+        <v>2.28E-7</v>
+      </c>
+      <c r="G74" s="9"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A75" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B75" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C75" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="D75" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E75" s="59">
+        <v>2.28E-7</v>
+      </c>
+      <c r="G75" s="9"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A76" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B76" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C76" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="D76" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E76" s="59">
+        <v>2.28E-7</v>
+      </c>
+      <c r="G76" s="9"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A77" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B77" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C77" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="D77" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E77" s="59">
+        <v>2.28E-7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A78" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B78" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C78" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="D78" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E78" s="59">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A79" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B79" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C79" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="D79" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E79" s="59">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A80" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B80" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C80" s="57" t="s">
+        <v>134</v>
+      </c>
+      <c r="D80" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E80" s="59">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A81" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B81" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C81" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="D81" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E81" s="59">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A82" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B82" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C82" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="D82" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E82" s="59">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A83" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B83" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C83" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="D83" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E83" s="59">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A84" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B84" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C84" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="D84" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E84" s="59">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A85" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B85" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C85" s="57" t="s">
+        <v>139</v>
+      </c>
+      <c r="D85" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E85" s="59">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A86" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B86" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C86" s="57" t="s">
+        <v>140</v>
+      </c>
+      <c r="D86" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E86" s="59">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A87" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B87" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C87" s="57" t="s">
+        <v>141</v>
+      </c>
+      <c r="D87" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E87" s="59">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A88" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B88" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C88" s="57" t="s">
+        <v>142</v>
+      </c>
+      <c r="D88" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E88" s="59">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A89" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B89" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C89" s="57" t="s">
+        <v>143</v>
+      </c>
+      <c r="D89" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E89" s="59">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A90" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B90" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C90" s="57" t="s">
+        <v>144</v>
+      </c>
+      <c r="D90" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E90" s="59">
+        <v>1.2200000000000001E-7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A91" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B91" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C91" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="D91" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E91" s="59">
+        <v>5.2999999999999998E-8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A92" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B92" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C92" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="D92" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E92" s="59">
+        <v>5.2999999999999998E-8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A93" s="55" t="s">
+        <v>498</v>
+      </c>
+      <c r="B93" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C93" s="57" t="s">
+        <v>161</v>
+      </c>
+      <c r="D93" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="E93" s="59">
+        <v>5.2999999999999998E-8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A94" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B94" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C94" s="60" t="s">
+        <v>462</v>
+      </c>
+      <c r="D94" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E94" s="59">
+        <v>5.4624999999999996E-7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A95" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B95" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C95" s="60" t="s">
+        <v>463</v>
+      </c>
+      <c r="D95" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E95" s="59">
+        <v>4.3700000000000001E-7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A96" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B96" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C96" s="60" t="s">
+        <v>464</v>
+      </c>
+      <c r="D96" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E96" s="59">
+        <v>4.752375E-7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A97" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B97" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C97" s="60" t="s">
+        <v>465</v>
+      </c>
+      <c r="D97" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E97" s="59">
+        <v>1.0105625E-7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A98" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B98" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C98" s="60" t="s">
+        <v>466</v>
+      </c>
+      <c r="D98" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E98" s="59">
+        <v>1.0105625E-7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A99" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B99" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C99" s="60" t="s">
+        <v>467</v>
+      </c>
+      <c r="D99" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E99" s="59">
+        <v>1.3656249999999999E-7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A100" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B100" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C100" s="60" t="s">
+        <v>468</v>
+      </c>
+      <c r="D100" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E100" s="59">
+        <v>5.0254999999999996E-7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A101" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B101" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C101" s="60" t="s">
+        <v>469</v>
+      </c>
+      <c r="D101" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E101" s="59">
+        <v>4.9162500000000004E-7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A102" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B102" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C102" s="60" t="s">
+        <v>470</v>
+      </c>
+      <c r="D102" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E102" s="59">
+        <v>4.0375E-7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A103" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B103" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C103" s="60" t="s">
+        <v>471</v>
+      </c>
+      <c r="D103" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E103" s="59">
+        <v>4.0375E-7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A104" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B104" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C104" s="60" t="s">
+        <v>472</v>
+      </c>
+      <c r="D104" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E104" s="59">
+        <v>4.0375E-7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A105" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B105" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C105" s="60" t="s">
+        <v>473</v>
+      </c>
+      <c r="D105" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E105" s="59">
+        <v>4.0375E-7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A106" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B106" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C106" s="60" t="s">
+        <v>474</v>
+      </c>
+      <c r="D106" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E106" s="59">
+        <v>4.0375E-7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A107" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B107" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C107" s="60" t="s">
+        <v>475</v>
+      </c>
+      <c r="D107" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E107" s="59">
+        <v>4.0375E-7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A108" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B108" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C108" s="60" t="s">
+        <v>479</v>
+      </c>
+      <c r="D108" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E108" s="59">
+        <v>5.4624999999999996E-7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A109" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B109" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C109" s="60" t="s">
+        <v>480</v>
+      </c>
+      <c r="D109" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E109" s="59">
+        <v>4.369999999999999E-7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A110" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B110" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C110" s="60" t="s">
+        <v>481</v>
+      </c>
+      <c r="D110" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E110" s="59">
+        <v>4.7523749999999994E-7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A111" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B111" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C111" s="60" t="s">
+        <v>482</v>
+      </c>
+      <c r="D111" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E111" s="59">
+        <v>1.0105625000000002E-7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A112" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B112" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C112" s="60" t="s">
+        <v>483</v>
+      </c>
+      <c r="D112" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E112" s="59">
+        <v>5.4624999999999996E-7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A113" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B113" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C113" s="60" t="s">
+        <v>484</v>
+      </c>
+      <c r="D113" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E113" s="59">
+        <v>5.2002999999999987E-7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A114" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B114" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C114" s="60" t="s">
+        <v>485</v>
+      </c>
+      <c r="D114" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E114" s="59">
+        <v>6.6642499999999983E-8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A115" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B115" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C115" s="61" t="s">
+        <v>486</v>
+      </c>
+      <c r="D115" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E115" s="59">
+        <v>1.0105625000000002E-7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A116" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B116" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C116" s="60" t="s">
+        <v>487</v>
+      </c>
+      <c r="D116" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E116" s="59">
+        <v>1.0105625000000002E-7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A117" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B117" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C117" s="60" t="s">
+        <v>488</v>
+      </c>
+      <c r="D117" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E117" s="59">
+        <v>1.3656249999999996E-7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A118" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B118" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C118" s="60" t="s">
+        <v>489</v>
+      </c>
+      <c r="D118" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E118" s="59">
+        <v>5.0254999999999996E-7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A119" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B119" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C119" s="60" t="s">
+        <v>490</v>
+      </c>
+      <c r="D119" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E119" s="59">
+        <v>2.7312499999999993E-7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A120" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B120" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C120" s="60" t="s">
+        <v>491</v>
+      </c>
+      <c r="D120" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E120" s="59">
+        <v>4.9162499999999993E-7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A121" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B121" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C121" s="60" t="s">
+        <v>492</v>
+      </c>
+      <c r="D121" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E121" s="59">
+        <v>4.6431249999999992E-7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A122" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B122" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C122" s="60" t="s">
+        <v>493</v>
+      </c>
+      <c r="D122" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E122" s="59">
+        <v>4.6431249999999992E-7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A123" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B123" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="C123" s="60" t="s">
+        <v>494</v>
+      </c>
+      <c r="D123" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="E123" s="59">
+        <v>4.0374999999999995E-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F173"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -16039,7 +18212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F206"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -19615,7 +21788,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -21243,7 +23416,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -21338,7 +23511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>

--- a/data/facteurs de caractérisation.xlsx
+++ b/data/facteurs de caractérisation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\CIRED\PlaneFR\Code\Module_PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEDE94C-F4ED-4BF9-820F-28BCBB3326F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B41DDA-AE9F-41D6-95DA-FAB24B48A2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="8002" windowWidth="14595" windowHeight="8745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="synthèse" sheetId="1" r:id="rId1"/>
@@ -5127,8 +5127,8 @@
         <v>148</v>
       </c>
       <c r="E167" s="21">
-        <f t="shared" ref="E167:E173" si="0">(0.110407441507011+0.0165)*1000000000</f>
-        <v>126907441.507011</v>
+        <f>(0.110407441507011+0.0165+0.772897890121685)*1000000000</f>
+        <v>899805331.62869608</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.4">
@@ -5145,8 +5145,8 @@
         <v>148</v>
       </c>
       <c r="E168" s="21">
-        <f t="shared" si="0"/>
-        <v>126907441.507011</v>
+        <f t="shared" ref="E168:E173" si="0">(0.110407441507011+0.0165+0.772897890121685)*1000000000</f>
+        <v>899805331.62869608</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.4">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="E169" s="21">
         <f t="shared" si="0"/>
-        <v>126907441.507011</v>
+        <v>899805331.62869608</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.4">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="E170" s="21">
         <f t="shared" si="0"/>
-        <v>126907441.507011</v>
+        <v>899805331.62869608</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.4">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="E171" s="21">
         <f t="shared" si="0"/>
-        <v>126907441.507011</v>
+        <v>899805331.62869608</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.4">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="E172" s="21">
         <f t="shared" si="0"/>
-        <v>126907441.507011</v>
+        <v>899805331.62869608</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.4">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="E173" s="21">
         <f t="shared" si="0"/>
-        <v>126907441.507011</v>
+        <v>899805331.62869608</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.4">
@@ -7058,7 +7058,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="14.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:5" ht="14.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A281" s="18" t="s">
         <v>15</v>
       </c>
@@ -7075,7 +7075,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="14.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:5" ht="14.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A282" s="18" t="s">
         <v>15</v>
       </c>
@@ -7449,7 +7449,7 @@
         <v>306.2</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:5" ht="13.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A304" s="18" t="s">
         <v>15</v>
       </c>
